--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -17717,10 +17717,1699 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Атлас — предложени класи по оригинално име</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Atlas — Proposed Grades by Original Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Класите на Атласот на потенција (номинала ± толеранција), директно од potency_dataset.json. Секоја серија ја носи декларацијата на својата класа.  |  The Potency Atlas's grades (nominal ± tolerance), straight from potency_dataset.json. Every batch carries its tier's declaration.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Сорта | Strain</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Класа | Tier</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Номинала % | Nominal %</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Толеранција % | Tolerance %</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Опсег — долно | Range — low</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Опсег — горно | Range — high</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Бр. серии | # Batches</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Серии | Batches</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>Основа | Basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>ACC102501</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Apple and Banana</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="inlineStr">
+        <is>
+          <t>AB092501</t>
+        </is>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Blue Gelato</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>BG1024</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>BSS052501, BSS1024_01/1</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>BSS1024</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>CJ052501/02</t>
+        </is>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>CJ082501/2, CJ062501/2, CJ062501/1</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>W-3</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="13" t="inlineStr">
+        <is>
+          <t>CJ092501, CJ1024, CJ072501, CJ052501/01, CJ082501/1</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>CC012603, CC112501</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>CC012601/1</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>CF102501</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t>CLE072501</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>FB012601/1, FB112501</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>FB012603V, FB012602, FB012603</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>GG1024, GG012601</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="13" t="inlineStr">
+        <is>
+          <t>GG1024_02, GG012603, GG112501, GG1024_01</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>GP082501/2, GP052501</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" s="13" t="inlineStr">
+        <is>
+          <t>GP072501/2, GP082501/1, GP072501/1, GP0824_02</t>
+        </is>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>W-3</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>GP062501, GP0824_03, GP092501</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>GRC102501/1</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>GRC102501/2</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="13" t="inlineStr">
+        <is>
+          <t>HPA1024, HPA052501</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="D28" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>HPA1024_01</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="13" t="inlineStr">
+        <is>
+          <t>JD012603/02V, JD012603/01</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>JD012601, JD112501, JD012603/02</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>J31102501, J31112501</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>J31122501</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="inlineStr">
+        <is>
+          <t>KC102501</t>
+        </is>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>MB0824_05, MB0824_04</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>OPM122501, OPM112501</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>OPM092501</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>W-3</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="13" t="inlineStr">
+        <is>
+          <t>OPM052501, OMP1024_01</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>W-4</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D38" s="12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E38" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>OPM1024_03, OPM1024_02</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>W-5</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="13" t="inlineStr">
+        <is>
+          <t>OPM1024</t>
+        </is>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>PM072501</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="G41" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="13" t="inlineStr">
+        <is>
+          <t>PM092501, PM112501</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>PUM102501</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E43" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F43" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G43" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>SCR112501, SCR012603, SCR012601</t>
+        </is>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>SCR022601</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G45" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="13" t="inlineStr">
+        <is>
+          <t>SJ112501, SJ092501</t>
+        </is>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>SJ102501</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D47" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E47" s="13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>WED102501</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E48" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>WC082501, WC072501</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -17735,28 +19424,28 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Атлас — предложени класи по оригинално име</t>
+          <t>Атлас — предложени класи по ново име</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Atlas — Proposed Grades by Original Name</t>
+          <t>Atlas — Proposed Grades by New Name</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Класите на Атласот на потенција (номинала ± толеранција), директно од potency_dataset.json. Секоја серија ја носи декларацијата на својата класа. Класа со само 1 тестирана серија нема статистичка основа за D+U прозорецот, па наместо тоа се декларира со фиксна политика: номинала ± 10% од номиналата.  |  The Potency Atlas's grades (nominal ± tolerance), straight from potency_dataset.json. Every batch carries its tier's declaration. A tier backed by only 1 tested batch has no statistical basis for the D+U window, so it is declared instead by a flat policy: nominal ± 10% of the nominal.</t>
+          <t>Истите докажани опсези, преклучирани по НОВОТО спецификациско име (01_Portfolio_Master). Пресметката е идентична со финалната табела на Атласот.  |  The same evidenced ranges, re-keyed to the NEW specification name (01_Portfolio_Master). Computation is identical to the Atlas's final board.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Сорта | Strain</t>
+          <t>Ново име | New Strain Name</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
@@ -17801,14 +19490,14 @@
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>Основа на толеранцијата | Tolerance basis</t>
+          <t>Оригинално(и) име(иња) | Original name(s)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Amnesia Core Cut</t>
+          <t>Amnesia Core</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
@@ -17843,14 +19532,14 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Amnesia Core Cut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Apple and Banana</t>
+          <t>Appels &amp; Bananas</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -17885,7 +19574,7 @@
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Appels &amp; Bananas</t>
         </is>
       </c>
     </row>
@@ -17927,14 +19616,14 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Blue Gelato</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Calmino</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -17943,23 +19632,23 @@
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>19.8</v>
+        <v>8.1</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>24.2</v>
+        <v>9.9</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>BSS052501, BSS1024_01/1</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="I9" s="13" t="inlineStr">
@@ -17969,39 +19658,39 @@
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Cherry Chocolate</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>22.5</v>
+        <v>16.2</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>27.5</v>
+        <v>19.8</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>BSS1024</t>
+          <t>GG112501</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -18011,14 +19700,14 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>GG4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Citrus Bloom</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -18027,23 +19716,23 @@
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>13.5</v>
+        <v>7.2</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>16.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G11" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>OPM122501</t>
         </is>
       </c>
       <c r="I11" s="13" t="inlineStr">
@@ -18053,14 +19742,14 @@
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Citrus Bloom</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
@@ -18069,23 +19758,23 @@
         </is>
       </c>
       <c r="C12" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D12" s="12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="G12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>CJ082501/2, CJ062501/2, CJ062501/1</t>
+          <t>OPM052501, OMP1024_01</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -18095,39 +19784,39 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Cap Junky</t>
+          <t>Clemosa</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>20.7</v>
+        <v>7.2</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>25.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G13" s="13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>CJ092501, CJ1024, CJ072501, CJ052501/01, CJ082501/1</t>
+          <t>CLE072501</t>
         </is>
       </c>
       <c r="I13" s="13" t="inlineStr">
@@ -18137,14 +19826,14 @@
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Clemosa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Cookie Kush</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
@@ -18153,23 +19842,23 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>11.7</v>
+        <v>16.2</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>14.3</v>
+        <v>19.8</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>CC012603, CC112501</t>
+          <t>CJ082501/2</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -18179,14 +19868,14 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Cookie Kush</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -18195,23 +19884,23 @@
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>16.2</v>
+        <v>20.7</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>19.8</v>
+        <v>25.3</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>CJ092501, CJ1024, CJ072501, CJ052501/01, CJ082501/1</t>
         </is>
       </c>
       <c r="I15" s="13" t="inlineStr">
@@ -18221,14 +19910,14 @@
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Daywalker</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -18237,65 +19926,65 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>FB012601/1</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Daywalker</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>7.2</v>
+        <v>17.1</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>20.9</v>
       </c>
       <c r="G17" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>FB012603V, FB012603</t>
         </is>
       </c>
       <c r="I17" s="13" t="inlineStr">
@@ -18305,14 +19994,14 @@
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Fat Sofa</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -18321,23 +20010,23 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E18" s="12" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>17.6</v>
+        <v>19.8</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>FB012601/1, FB112501</t>
+          <t>FB112501, FB012602</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -18347,39 +20036,39 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Formula 1</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>17.1</v>
+        <v>9</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>20.9</v>
+        <v>11</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>FB012603V, FB012602, FB012603</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="I19" s="13" t="inlineStr">
@@ -18389,39 +20078,39 @@
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Formula 1</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>GG1024, GG012601</t>
+          <t>PM092501, PM112501</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -18431,39 +20120,39 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D21" s="13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>GG1024_02, GG012603, GG112501, GG1024_01</t>
+          <t>GG012601, GG012603</t>
         </is>
       </c>
       <c r="I21" s="13" t="inlineStr">
@@ -18473,14 +20162,14 @@
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>GG4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Gang</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -18489,23 +20178,23 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E22" s="12" t="n">
-        <v>15.3</v>
+        <v>11.7</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>18.7</v>
+        <v>14.3</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>GP082501/2, GP052501</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -18515,14 +20204,14 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Gang</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -18531,23 +20220,23 @@
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D23" s="13" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>18.9</v>
+        <v>15.3</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>23.1</v>
+        <v>18.7</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>GP072501/2, GP082501/1, GP072501/1, GP0824_02</t>
+          <t>GG1024_02, GG1024_01</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
@@ -18557,7 +20246,7 @@
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
     </row>
@@ -18569,27 +20258,27 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>GP062501, GP0824_03, GP092501</t>
+          <t>GP0824_02, GP0824_03, GP092501</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -18599,14 +20288,14 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Grape Pie</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Hazy Daze</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -18615,65 +20304,65 @@
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D25" s="13" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>6.3</v>
+        <v>18</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>GRC102501/1</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="E26" s="12" t="n">
-        <v>10.8</v>
+        <v>15.3</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>13.2</v>
+        <v>18.7</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -18683,14 +20372,14 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -18699,23 +20388,23 @@
         </is>
       </c>
       <c r="C27" s="13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>17.1</v>
+        <v>13.5</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>20.9</v>
+        <v>16.5</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>HPA1024, HPA052501</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="I27" s="13" t="inlineStr">
@@ -18725,14 +20414,14 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -18741,23 +20430,23 @@
         </is>
       </c>
       <c r="C28" s="12" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>19.8</v>
+        <v>17.1</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>24.2</v>
+        <v>20.9</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>HPA1024_01</t>
+          <t>JD012601, JD112501, JD012603/02</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -18767,14 +20456,14 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -18783,23 +20472,23 @@
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>14.4</v>
+        <v>17.1</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>17.6</v>
+        <v>20.9</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>JD012603/02V, JD012603/01</t>
+          <t>J31102501, J31112501</t>
         </is>
       </c>
       <c r="I29" s="13" t="inlineStr">
@@ -18809,14 +20498,14 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -18825,23 +20514,23 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="E30" s="12" t="n">
-        <v>17.1</v>
+        <v>19.8</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>20.9</v>
+        <v>24.2</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>JD012601, JD112501, JD012603/02</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -18851,14 +20540,14 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
@@ -18867,23 +20556,23 @@
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D31" s="13" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="13" t="inlineStr">
         <is>
-          <t>J31102501, J31112501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="I31" s="13" t="inlineStr">
@@ -18893,56 +20582,56 @@
       </c>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Lifeguard</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>19.8</v>
+        <v>14.4</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>24.2</v>
+        <v>17.6</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>NY Diesel</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
@@ -18963,11 +20652,11 @@
         <v>18.7</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>MB0824_05, MB0824_04</t>
         </is>
       </c>
       <c r="I33" s="13" t="inlineStr">
@@ -18977,14 +20666,14 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Motor Breath</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -18993,23 +20682,23 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>15.3</v>
+        <v>13.5</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>18.7</v>
+        <v>16.5</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>MB0824_05, MB0824_04</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -19019,39 +20708,39 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D35" s="13" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>7.2</v>
+        <v>18</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="G35" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>OPM122501, OPM112501</t>
+          <t>CJ062501/2, CJ062501/1</t>
         </is>
       </c>
       <c r="I35" s="13" t="inlineStr">
@@ -19061,39 +20750,39 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Orange Dream</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>8.1</v>
+        <v>18</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>9.9</v>
+        <v>22</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -19103,39 +20792,39 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D37" s="13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="G37" s="13" t="n">
         <v>2</v>
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>OPM052501, OMP1024_01</t>
+          <t>CC012603, CC112501</t>
         </is>
       </c>
       <c r="I37" s="13" t="inlineStr">
@@ -19145,39 +20834,39 @@
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>CashCow</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>W-4</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>OPM1024_03, OPM1024_02</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -19187,81 +20876,81 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>CashCow</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>W-5</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D39" s="13" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>18</v>
+        <v>6.3</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>22</v>
+        <v>7.7</v>
       </c>
       <c r="G39" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="13" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>11</v>
+        <v>13.2</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -19271,39 +20960,39 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Rainbow Sherbet</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D41" s="13" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>11.7</v>
+        <v>19.8</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>14.3</v>
+        <v>24.2</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>PM092501, PM112501</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
@@ -19313,14 +21002,14 @@
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Scrambler</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -19329,40 +21018,40 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Scrambler</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Shark Tank</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
@@ -19371,65 +21060,65 @@
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D43" s="13" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>18.7</v>
+        <v>11</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>19.8</v>
+        <v>9.9</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>24.2</v>
+        <v>12.1</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -19439,14 +21128,14 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
@@ -19455,23 +21144,23 @@
         </is>
       </c>
       <c r="C45" s="13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D45" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G45" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E45" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>2</v>
-      </c>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>SJ112501, SJ092501</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="I45" s="13" t="inlineStr">
@@ -19481,14 +21170,14 @@
       </c>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
@@ -19497,23 +21186,23 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="E46" s="12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F46" s="12" t="n">
         <v>9.9</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>12.1</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -19523,14 +21212,14 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Strawberry Cupcakes</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
@@ -19539,23 +21228,23 @@
         </is>
       </c>
       <c r="C47" s="13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D47" s="13" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>19.8</v>
+        <v>15.3</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>24.2</v>
+        <v>18.7</v>
       </c>
       <c r="G47" s="13" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="I47" s="13" t="inlineStr">
@@ -19565,14 +21254,14 @@
       </c>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Sunset Sherbet</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -19581,33 +21270,327 @@
         </is>
       </c>
       <c r="C48" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="E48" s="12" t="n">
-        <v>18.9</v>
+        <v>19.8</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
+          <t>BSS052501, BSS1024_01/1</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D49" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E49" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F49" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>BSS1024</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Tangie Queen</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>OPM1024_03, OPM1024_02</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>Tropic Cake</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E51" s="13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F51" s="13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="13" t="inlineStr">
+        <is>
+          <t>WED102501</t>
+        </is>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E52" s="12" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>GP082501/2, GP052501</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G53" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="13" t="inlineStr">
+        <is>
+          <t>GP072501/2, GP082501/1, GP072501/1</t>
+        </is>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>W-3</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="D54" s="12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E54" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E55" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="G55" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="13" t="inlineStr">
+        <is>
           <t>WC082501, WC072501</t>
         </is>
       </c>
-      <c r="I48" s="12" t="inlineStr">
+      <c r="I55" s="13" t="inlineStr">
         <is>
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
+      <c r="J55" s="13" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
         </is>
       </c>
     </row>
@@ -19616,2466 +21599,6 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K55"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>Атлас — предложени класи по ново име</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Atlas — Proposed Grades by New Name</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>Истите докажани опсези, преклучирани по НОВОТО спецификациско име (01_Portfolio_Master). Пресметката е идентична со finalRangesRenamed() во build_potency_html.py — вкрстено проверена: 36 имиња, 31 дефинитивно, 5 провизорно, 0 без сидро. Класа со само 1 тестирана серија: номинала ± 10%.  |  The same evidenced ranges, re-keyed to the NEW specification name (01_Portfolio_Master). Computation is identical to finalRangesRenamed() in build_potency_html.py — cross-checked: 36 names, 31 definitive, 5 provisional, 0 without an anchor. A tier with only 1 tested batch: nominal ± 10%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Ново име | New Strain Name</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Класа | Tier</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Номинала % | Nominal %</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Толеранција % | Tolerance %</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Опсег — долно | Range — low</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
-        <is>
-          <t>Опсег — горно | Range — high</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>Бр. серии | # Batches</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Серии | Batches</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>Основа | Basis</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>Основа на толеранцијата | Tolerance basis</t>
-        </is>
-      </c>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>Оригинално(и) име(иња) | Original name(s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Amnesia Core</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>ACC102501</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Amnesia Core Cut</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Appels &amp; Bananas</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>AB092501</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>Appels &amp; Bananas</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Blue Gelato</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>BG1024</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Blue Gelato</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Calmino</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
-        <is>
-          <t>SJ112501</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>Sleepy Joe</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Cherry Chocolate</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>GG112501</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J10" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K10" s="12" t="inlineStr">
-        <is>
-          <t>GG4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Citrus Bloom</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="13" t="inlineStr">
-        <is>
-          <t>OPM122501</t>
-        </is>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Citrus Bloom</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="12" t="inlineStr">
-        <is>
-          <t>OPM052501, OMP1024_01</t>
-        </is>
-      </c>
-      <c r="I12" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Clemosa</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="13" t="inlineStr">
-        <is>
-          <t>CLE072501</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>Clemosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Cookie Kush</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="12" t="inlineStr">
-        <is>
-          <t>CJ082501/2</t>
-        </is>
-      </c>
-      <c r="I14" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
-        <is>
-          <t>Cap Junkie</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Cookie Kush</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>CJ092501, CJ1024, CJ072501, CJ052501/01, CJ082501/1</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K15" s="13" t="inlineStr">
-        <is>
-          <t>Cap Junkie</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Daywalker</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="12" t="inlineStr">
-        <is>
-          <t>FB012601/1</t>
-        </is>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>Daywalker</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>FB012603V, FB012603</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Fat Sofa</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>FB112501, FB012602</t>
-        </is>
-      </c>
-      <c r="I18" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
-        <is>
-          <t>Fat Bastard</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Formula 1</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="F19" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="G19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>PM072501</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K19" s="13" t="inlineStr">
-        <is>
-          <t>Permanent Marker</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Formula 1</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>PM092501, PM112501</t>
-        </is>
-      </c>
-      <c r="I20" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
-        <is>
-          <t>Permanent Marker</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>GG4</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E21" s="13" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>GG012601, GG012603</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>GG4</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Gorilla Gang</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>GG1024</t>
-        </is>
-      </c>
-      <c r="I22" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Gorilla Gang</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G23" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>GG1024_02, GG1024_01</t>
-        </is>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>GP0824_02, GP0824_03, GP092501</t>
-        </is>
-      </c>
-      <c r="I24" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Hazy Daze</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G25" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>HPA052501, HPA1024_01</t>
-        </is>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>HPA1024</t>
-        </is>
-      </c>
-      <c r="I26" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J26" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K26" s="12" t="inlineStr">
-        <is>
-          <t>High Pro Amnesia</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G27" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="13" t="inlineStr">
-        <is>
-          <t>JD012603/02V</t>
-        </is>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E28" s="12" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>JD012601, JD112501, JD012603/02</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="D29" s="13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E29" s="13" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="G29" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>J31102501, J31112501</t>
-        </is>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
-      <c r="B30" s="12" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="D30" s="12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E30" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="12" t="inlineStr">
-        <is>
-          <t>J31122501</t>
-        </is>
-      </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J30" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Kush Crasher</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>KC102501</t>
-        </is>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>Kush Crasher</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Lifeguard</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E32" s="12" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F32" s="12" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="G32" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="12" t="inlineStr">
-        <is>
-          <t>PUM102501</t>
-        </is>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J32" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K32" s="12" t="inlineStr">
-        <is>
-          <t>Pure Michigen</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>NY Diesel</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H33" s="13" t="inlineStr">
-        <is>
-          <t>MB0824_05, MB0824_04</t>
-        </is>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>Motor Breath</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>OG Banana's</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>CJ052501/02</t>
-        </is>
-      </c>
-      <c r="I34" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J34" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>Cap Junkie</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>OG Banana's</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H35" s="13" t="inlineStr">
-        <is>
-          <t>CJ062501/2, CJ062501/1</t>
-        </is>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>Cap Junkie</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Orange Dream</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>OPM1024</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J36" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K36" s="12" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>Payday</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="13" t="inlineStr">
-        <is>
-          <t>CC012603, CC112501</t>
-        </is>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>CashCow</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Payday</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E38" s="12" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="G38" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>CC012601/1</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J38" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K38" s="12" t="inlineStr">
-        <is>
-          <t>CashCow</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>Plum Tarte</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D39" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E39" s="13" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G39" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="13" t="inlineStr">
-        <is>
-          <t>GRC102501/1</t>
-        </is>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>Grapes and Cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>Plum Tarte</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>GRC102501/2</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>Grapes and Cream</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Rainbow Sherbet</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="D41" s="13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E41" s="13" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G41" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>SCR022601</t>
-        </is>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D42" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>Scrambler</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
-        <is>
-          <t>Shark Tank</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C43" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="D43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="F43" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="G43" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="13" t="inlineStr">
-        <is>
-          <t>CF102501</t>
-        </is>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>Chem Flyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>Sleepy Joe</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="D44" s="12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E44" s="12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>SJ092501, SJ102501</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Sleepy Joe</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>Soft Citrus Bloom</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C45" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="D45" s="13" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E45" s="13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="G45" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" s="13" t="inlineStr">
-        <is>
-          <t>OPM112501</t>
-        </is>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Soft Citrus Bloom</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="D46" s="12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E46" s="12" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>OPM092501</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>Strawberry Cupcakes</t>
-        </is>
-      </c>
-      <c r="B47" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D47" s="13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E47" s="13" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F47" s="13" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G47" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>JD012603/01</t>
-        </is>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Sunset Sherbet</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C48" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="D48" s="12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E48" s="12" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>BSS052501, BSS1024_01/1</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J48" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
-        <is>
-          <t>Blue Sunset Sherbet</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>Sunset Sherbet</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="D49" s="13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E49" s="13" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G49" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="13" t="inlineStr">
-        <is>
-          <t>BSS1024</t>
-        </is>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>Blue Sunset Sherbet</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Tangie Queen</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>OPM1024_03, OPM1024_02</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>Tropic Cake</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="D51" s="13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E51" s="13" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G51" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>WED102501</t>
-        </is>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>Wedding Cake</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>Vanilla Grapes</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C52" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D52" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="E52" s="12" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F52" s="12" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="G52" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H52" s="12" t="inlineStr">
-        <is>
-          <t>GP082501/2, GP052501</t>
-        </is>
-      </c>
-      <c r="I52" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J52" s="12" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>Vanilla Grapes</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="inlineStr">
-        <is>
-          <t>W-2</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D53" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F53" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G53" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="13" t="inlineStr">
-        <is>
-          <t>GP072501/2, GP082501/1, GP072501/1</t>
-        </is>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="12" t="inlineStr">
-        <is>
-          <t>Vanilla Grapes</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>W-3</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E54" s="12" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F54" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" s="12" t="inlineStr">
-        <is>
-          <t>GP062501</t>
-        </is>
-      </c>
-      <c r="I54" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J54" s="12" t="inlineStr">
-        <is>
-          <t>±10% политика (n=1) | ±10% policy (n=1)</t>
-        </is>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>Wedding Crusher</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="C55" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="D55" s="13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E55" s="13" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="F55" s="13" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="G55" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" s="13" t="inlineStr">
-        <is>
-          <t>WC082501, WC072501</t>
-        </is>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J55" s="13" t="inlineStr">
-        <is>
-          <t>D+U, ограничено на ±10% | D+U, capped at ±10%</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>Wedding Crusher</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -17807,7 +17807,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C6" s="12" t="n">
@@ -17844,7 +17844,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -17881,7 +17881,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -17992,7 +17992,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
@@ -18288,7 +18288,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
@@ -18325,7 +18325,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
@@ -18362,7 +18362,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
@@ -18399,7 +18399,7 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
@@ -18436,7 +18436,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
@@ -18584,7 +18584,7 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
@@ -18658,7 +18658,7 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
@@ -18695,7 +18695,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
@@ -18732,7 +18732,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C31" s="13" t="n">
@@ -18769,7 +18769,7 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C35" s="13" t="n">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
@@ -18991,7 +18991,7 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>W-4</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
@@ -19028,7 +19028,7 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>W-5</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
@@ -19065,7 +19065,7 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -19139,7 +19139,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -19213,7 +19213,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
@@ -19287,7 +19287,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
@@ -19324,7 +19324,7 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
@@ -19361,7 +19361,7 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C6" s="12" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
@@ -19670,7 +19670,7 @@
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -19712,7 +19712,7 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -19838,7 +19838,7 @@
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
@@ -19922,7 +19922,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
@@ -20048,7 +20048,7 @@
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
@@ -20090,7 +20090,7 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
@@ -20132,7 +20132,7 @@
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C21" s="13" t="n">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C27" s="13" t="n">
@@ -20426,7 +20426,7 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C28" s="12" t="n">
@@ -20468,7 +20468,7 @@
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C30" s="12" t="n">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C31" s="13" t="n">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C32" s="12" t="n">
@@ -20636,7 +20636,7 @@
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
@@ -20720,7 +20720,7 @@
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C35" s="13" t="n">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C36" s="12" t="n">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
@@ -20846,7 +20846,7 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C38" s="12" t="n">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
@@ -20930,7 +20930,7 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C40" s="12" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
@@ -21056,7 +21056,7 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
@@ -21098,7 +21098,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C44" s="12" t="n">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C45" s="13" t="n">
@@ -21182,7 +21182,7 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C46" s="12" t="n">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C47" s="13" t="n">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C48" s="12" t="n">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C50" s="12" t="n">
@@ -21392,7 +21392,7 @@
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C51" s="13" t="n">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C52" s="12" t="n">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C53" s="13" t="n">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C54" s="12" t="n">
@@ -21560,7 +21560,7 @@
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C55" s="13" t="n">
@@ -21806,7 +21806,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I6" s="12" t="n">
@@ -21886,7 +21886,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I7" s="13" t="n">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I8" s="12" t="n">
@@ -22046,7 +22046,7 @@
       </c>
       <c r="H9" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I9" s="13" t="n">
@@ -22087,7 +22087,7 @@
       </c>
       <c r="S9" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T9" s="13" t="n">
@@ -22209,7 +22209,7 @@
       </c>
       <c r="H11" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I11" s="13" t="n">
@@ -22250,7 +22250,7 @@
       </c>
       <c r="S11" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T11" s="13" t="n">
@@ -22299,7 +22299,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I12" s="12" t="n">
@@ -22340,7 +22340,7 @@
       </c>
       <c r="S12" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T12" s="12" t="n">
@@ -22389,7 +22389,7 @@
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I13" s="13" t="n">
@@ -22430,7 +22430,7 @@
       </c>
       <c r="S13" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T13" s="13" t="n">
@@ -22479,7 +22479,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I14" s="12" t="n">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="S14" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T14" s="12" t="n">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="H15" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I15" s="13" t="n">
@@ -22610,7 +22610,7 @@
       </c>
       <c r="S15" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T15" s="13" t="n">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I16" s="12" t="n">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="S16" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T16" s="12" t="n">
@@ -22749,7 +22749,7 @@
       </c>
       <c r="H17" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I17" s="13" t="n">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="S17" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T17" s="13" t="n">
@@ -22839,7 +22839,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I18" s="12" t="n">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="S18" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T18" s="12" t="n">
@@ -22929,7 +22929,7 @@
       </c>
       <c r="H19" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I19" s="13" t="n">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="S19" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T19" s="13" t="n">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I20" s="12" t="n">
@@ -23060,7 +23060,7 @@
       </c>
       <c r="S20" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T20" s="12" t="n">
@@ -23109,7 +23109,7 @@
       </c>
       <c r="H21" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I21" s="13" t="n">
@@ -23150,7 +23150,7 @@
       </c>
       <c r="S21" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T21" s="13" t="n">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I22" s="12" t="n">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="S22" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T22" s="12" t="n">
@@ -23289,7 +23289,7 @@
       </c>
       <c r="H23" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I23" s="13" t="n">
@@ -23330,7 +23330,7 @@
       </c>
       <c r="S23" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T23" s="13" t="n">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I24" s="12" t="n">
@@ -23420,7 +23420,7 @@
       </c>
       <c r="S24" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T24" s="12" t="n">
@@ -23469,7 +23469,7 @@
       </c>
       <c r="H25" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I25" s="13" t="n">
@@ -23510,7 +23510,7 @@
       </c>
       <c r="S25" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T25" s="13" t="n">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I26" s="12" t="n">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T26" s="12" t="n">
@@ -23646,7 +23646,7 @@
       </c>
       <c r="H27" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I27" s="13" t="n">
@@ -23726,7 +23726,7 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I28" s="12" t="n">
@@ -23767,7 +23767,7 @@
       </c>
       <c r="S28" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T28" s="12" t="n">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="H29" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I29" s="13" t="n">
@@ -23857,7 +23857,7 @@
       </c>
       <c r="S29" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T29" s="13" t="n">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I30" s="12" t="n">
@@ -23947,7 +23947,7 @@
       </c>
       <c r="S30" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T30" s="12" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I32" s="12" t="n">
@@ -24107,7 +24107,7 @@
       </c>
       <c r="S32" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T32" s="12" t="n">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H33" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I33" s="13" t="n">
@@ -24197,7 +24197,7 @@
       </c>
       <c r="S33" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T33" s="13" t="n">
@@ -24246,7 +24246,7 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I34" s="12" t="n">
@@ -24287,7 +24287,7 @@
       </c>
       <c r="S34" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T34" s="12" t="n">
@@ -24336,7 +24336,7 @@
       </c>
       <c r="H35" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I35" s="13" t="n">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I36" s="12" t="n">
@@ -24457,7 +24457,7 @@
       </c>
       <c r="S36" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T36" s="12" t="n">
@@ -24506,7 +24506,7 @@
       </c>
       <c r="H37" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I37" s="13" t="n">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I38" s="12" t="n">
@@ -24627,7 +24627,7 @@
       </c>
       <c r="S38" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T38" s="12" t="n">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I40" s="12" t="n">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="S40" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T40" s="12" t="n">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I41" s="13" t="n">
@@ -24880,7 +24880,7 @@
       </c>
       <c r="S41" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T41" s="13" t="n">
@@ -24929,7 +24929,7 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I42" s="12" t="n">
@@ -25228,7 +25228,7 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I46" s="12" t="n">
@@ -25308,7 +25308,7 @@
       </c>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I47" s="13" t="n">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="S47" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T47" s="13" t="n">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I48" s="12" t="n">
@@ -25439,7 +25439,7 @@
       </c>
       <c r="S48" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T48" s="12" t="n">
@@ -25488,7 +25488,7 @@
       </c>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I49" s="13" t="n">
@@ -25568,7 +25568,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I50" s="12" t="n">
@@ -25721,7 +25721,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I52" s="12" t="n">
@@ -25762,7 +25762,7 @@
       </c>
       <c r="S52" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T52" s="12" t="n">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I53" s="13" t="n">
@@ -25852,7 +25852,7 @@
       </c>
       <c r="S53" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T53" s="13" t="n">
@@ -25901,7 +25901,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I54" s="12" t="n">
@@ -25942,7 +25942,7 @@
       </c>
       <c r="S54" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T54" s="12" t="n">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I55" s="13" t="n">
@@ -26032,7 +26032,7 @@
       </c>
       <c r="S55" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T55" s="13" t="n">
@@ -26081,7 +26081,7 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I56" s="12" t="n">
@@ -26122,7 +26122,7 @@
       </c>
       <c r="S56" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T56" s="12" t="n">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I57" s="13" t="n">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I58" s="12" t="n">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I59" s="13" t="n">
@@ -26372,7 +26372,7 @@
       </c>
       <c r="S59" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T59" s="13" t="n">
@@ -26421,7 +26421,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I60" s="12" t="n">
@@ -26462,7 +26462,7 @@
       </c>
       <c r="S60" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T60" s="12" t="n">
@@ -26511,7 +26511,7 @@
       </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I61" s="13" t="n">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I62" s="12" t="n">
@@ -26632,7 +26632,7 @@
       </c>
       <c r="S62" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T62" s="12" t="n">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I63" s="13" t="n">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="S63" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T63" s="13" t="n">
@@ -26771,7 +26771,7 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I64" s="12" t="n">
@@ -26851,7 +26851,7 @@
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I65" s="13" t="n">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="S65" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T65" s="13" t="n">
@@ -26941,7 +26941,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I66" s="12" t="n">
@@ -27021,7 +27021,7 @@
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I67" s="13" t="n">
@@ -27101,7 +27101,7 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I68" s="12" t="n">
@@ -27181,7 +27181,7 @@
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I69" s="13" t="n">
@@ -27261,7 +27261,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I70" s="12" t="n">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I71" s="13" t="n">
@@ -27494,7 +27494,7 @@
       </c>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I73" s="13" t="n">
@@ -27574,7 +27574,7 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I74" s="12" t="n">
@@ -27654,7 +27654,7 @@
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I75" s="13" t="n">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I76" s="12" t="n">
@@ -27814,7 +27814,7 @@
       </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I77" s="13" t="n">
@@ -27894,7 +27894,7 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I78" s="12" t="n">
@@ -27974,7 +27974,7 @@
       </c>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I79" s="13" t="n">
@@ -28054,7 +28054,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I80" s="12" t="n">
@@ -28095,7 +28095,7 @@
       </c>
       <c r="S80" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T80" s="12" t="n">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I81" s="13" t="n">
@@ -28185,7 +28185,7 @@
       </c>
       <c r="S81" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T81" s="13" t="n">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I82" s="12" t="n">
@@ -28275,7 +28275,7 @@
       </c>
       <c r="S82" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T82" s="12" t="n">
@@ -28324,7 +28324,7 @@
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I83" s="13" t="n">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="S83" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T83" s="13" t="n">
@@ -28414,7 +28414,7 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>W-3</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I84" s="12" t="n">
@@ -28455,7 +28455,7 @@
       </c>
       <c r="S84" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T84" s="12" t="n">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>W-5</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="I85" s="13" t="n">
@@ -28545,7 +28545,7 @@
       </c>
       <c r="S85" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T85" s="13" t="n">
@@ -28594,7 +28594,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>W-4</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I86" s="12" t="n">
@@ -28635,7 +28635,7 @@
       </c>
       <c r="S86" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T86" s="12" t="n">
@@ -28684,7 +28684,7 @@
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I87" s="13" t="n">
@@ -28725,7 +28725,7 @@
       </c>
       <c r="S87" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T87" s="13" t="n">
@@ -28774,7 +28774,7 @@
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I88" s="12" t="n">
@@ -28815,7 +28815,7 @@
       </c>
       <c r="S88" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T88" s="12" t="n">
@@ -28864,7 +28864,7 @@
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I89" s="13" t="n">
@@ -28905,7 +28905,7 @@
       </c>
       <c r="S89" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T89" s="13" t="n">
@@ -28954,7 +28954,7 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>W-5</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="I90" s="12" t="n">
@@ -28995,7 +28995,7 @@
       </c>
       <c r="S90" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T90" s="12" t="n">
@@ -29044,7 +29044,7 @@
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>W-4</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I91" s="13" t="n">
@@ -29085,7 +29085,7 @@
       </c>
       <c r="S91" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T91" s="13" t="n">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>W-4</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I92" s="12" t="n">
@@ -29175,7 +29175,7 @@
       </c>
       <c r="S92" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T92" s="12" t="n">
@@ -29224,7 +29224,7 @@
       </c>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I93" s="13" t="n">
@@ -29265,7 +29265,7 @@
       </c>
       <c r="S93" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T93" s="13" t="n">
@@ -29314,7 +29314,7 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I94" s="12" t="n">
@@ -29355,7 +29355,7 @@
       </c>
       <c r="S94" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T94" s="12" t="n">
@@ -29404,7 +29404,7 @@
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I95" s="13" t="n">
@@ -29445,7 +29445,7 @@
       </c>
       <c r="S95" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T95" s="13" t="n">
@@ -29494,7 +29494,7 @@
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I96" s="12" t="n">
@@ -29535,7 +29535,7 @@
       </c>
       <c r="S96" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T96" s="12" t="n">
@@ -29584,7 +29584,7 @@
       </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I97" s="13" t="n">
@@ -29625,7 +29625,7 @@
       </c>
       <c r="S97" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T97" s="13" t="n">
@@ -29674,7 +29674,7 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I98" s="12" t="n">
@@ -29754,7 +29754,7 @@
       </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I99" s="13" t="n">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I100" s="12" t="n">
@@ -29914,7 +29914,7 @@
       </c>
       <c r="H101" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I101" s="13" t="n">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="S101" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T101" s="13" t="n">
@@ -30004,7 +30004,7 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I102" s="12" t="n">
@@ -30084,7 +30084,7 @@
       </c>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I103" s="13" t="n">
@@ -30164,7 +30164,7 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I104" s="12" t="n">

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -17930,23 +17930,23 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>24.2</v>
-      </c>
       <c r="G9" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>BSS052501, BSS1024_01/1</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -17970,20 +17970,20 @@
         <v>25</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.7900000000000007</v>
+        <v>2.5</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>24.21</v>
+        <v>22.5</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>25.79</v>
+        <v>27.5</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>BSS1024</t>
+          <t>BSS1024_01/1, BSS1024</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -18004,16 +18004,16 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>1</v>
@@ -18041,23 +18041,23 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" s="13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G12" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>CJ082501/2, CJ062501/2, CJ062501/1</t>
+          <t>CJ082501/2, CJ062501/2</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -18078,23 +18078,23 @@
         </is>
       </c>
       <c r="C13" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>22.01</v>
+        <v>20.7</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>CJ092501, CJ1024, CJ072501, CJ052501/01, CJ082501/1</t>
+          <t>CJ062501/1, CJ092501, CJ1024, CJ072501, CJ052501/01, CJ082501/1</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -18263,23 +18263,23 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>17.6</v>
+        <v>15.4</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>FB012601/1, FB112501</t>
+          <t>FB012601/1</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -18300,23 +18300,23 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>FB012603V, FB012602, FB012603</t>
+          <t>FB112501, FB012603V, FB012602</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -18328,32 +18328,32 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>12.6</v>
+        <v>20.7</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>15.4</v>
+        <v>25.3</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>GG1024, GG012601</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -18370,27 +18370,27 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>15.41</v>
+        <v>11.7</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>18.59</v>
+        <v>14.3</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>GG1024_02, GG012603, GG112501</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -18407,27 +18407,27 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>0.4000000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>19.4</v>
+        <v>18.7</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>GG1024_01</t>
+          <t>GG012601, GG1024_02, GG012603, GG112501, GG1024_01</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -18522,16 +18522,16 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>1.889999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>23.11</v>
+        <v>23.4</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>26.89</v>
+        <v>28.6</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>3</v>
@@ -18633,23 +18633,23 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>HPA1024, HPA052501</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -18670,23 +18670,23 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.090000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>20.91</v>
+        <v>18.9</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>HPA1024_01</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -18781,23 +18781,23 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>J31102501, J31112501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -18818,23 +18818,23 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>1.090000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>20.91</v>
+        <v>18.9</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>J31112501, J31122501</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -18892,16 +18892,16 @@
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>2</v>
@@ -19003,23 +19003,23 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>16.5</v>
+        <v>14.3</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>OPM052501, OMP1024_01</t>
+          <t>OPM052501</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -19040,23 +19040,23 @@
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>16.51</v>
+        <v>14.4</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>19.49</v>
+        <v>17.6</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>OPM1024_03, OPM1024_02</t>
+          <t>OMP1024_01, OPM1024_03</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -19080,20 +19080,20 @@
         <v>20</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>0.5000000000000016</v>
+        <v>2</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>OPM1024_02, OPM1024</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -19225,16 +19225,16 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>3</v>
@@ -19265,13 +19265,13 @@
         <v>22</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>19.81</v>
+        <v>19.8</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>24.19</v>
+        <v>24.2</v>
       </c>
       <c r="G45" s="14" t="n">
         <v>1</v>
@@ -19299,23 +19299,23 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D46" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="F46" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>SJ112501, SJ092501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -19339,20 +19339,20 @@
         <v>12</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>11.01</v>
+        <v>10.8</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>12.99</v>
+        <v>13.2</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>SJ102501</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -19451,7 +19451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20013,16 +20013,16 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>18</v>
+        <v>17.1</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>2</v>
@@ -20055,23 +20055,23 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>16.2</v>
+        <v>14.4</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>19.8</v>
+        <v>17.6</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>FB112501, FB012602</t>
+          <t>FB112501</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -20088,32 +20088,32 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Formula 1</t>
+          <t>Fat Sofa</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>FB012602</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -20123,7 +20123,7 @@
       </c>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
     </row>
@@ -20135,27 +20135,27 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>11.7</v>
+        <v>9</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>PM092501, PM112501</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -20172,32 +20172,32 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Formula 1</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>14.4</v>
+        <v>11.7</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>17.6</v>
+        <v>14.3</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>2</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>GG012601, GG012603</t>
+          <t>PM092501, PM112501</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -20207,14 +20207,14 @@
       </c>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Gorilla Gang</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -20223,23 +20223,23 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>11.7</v>
+        <v>14.4</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>14.3</v>
+        <v>17.6</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>GG012601, GG012603</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>GG4</t>
         </is>
       </c>
     </row>
@@ -20261,27 +20261,27 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>15.3</v>
+        <v>11.7</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>18.7</v>
+        <v>14.3</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>GG1024_02, GG1024_01</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -20298,32 +20298,32 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Gang</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>21.6</v>
+        <v>14.4</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>26.4</v>
+        <v>17.6</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>GP0824_02, GP0824_03, GP092501</t>
+          <t>GG1024_02</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -20333,39 +20333,39 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Hazy Daze</t>
+          <t>Gorilla Gang</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>HPA052501, HPA1024_01</t>
+          <t>GG1024_01</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -20375,14 +20375,14 @@
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -20391,23 +20391,23 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>15.3</v>
+        <v>18.9</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>GP0824_02</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -20417,39 +20417,39 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Grape Pie</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>13.5</v>
+        <v>23.4</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>16.5</v>
+        <v>28.6</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>JD012603/02V</t>
+          <t>GP0824_03, GP092501</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -20459,39 +20459,39 @@
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Grape Pie</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Hazy Daze</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>17.1</v>
+        <v>18.9</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>JD012601, JD112501, JD012603/02</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -20501,14 +20501,14 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -20517,23 +20517,23 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>J31102501, J31112501</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -20543,39 +20543,39 @@
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>1.090000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>20.91</v>
+        <v>13.5</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>23.09</v>
+        <v>16.5</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>J31122501</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -20585,39 +20585,39 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>15.3</v>
+        <v>18</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>JD012601, JD112501, JD012603/02</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -20627,14 +20627,14 @@
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Lifeguard</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -20643,65 +20643,65 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>NY Diesel</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>16.2</v>
+        <v>18.9</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>19.8</v>
+        <v>23.1</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>2</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>MB0824_05, MB0824_04</t>
+          <t>J31112501, J31122501</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -20711,14 +20711,14 @@
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>OG Banana's</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -20727,23 +20727,23 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>13.5</v>
+        <v>15.3</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>16.5</v>
+        <v>18.7</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -20753,56 +20753,56 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>OG Banana's</t>
+          <t>Lifeguard</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>18</v>
+        <v>14.4</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>22</v>
+        <v>17.6</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>CJ062501/2, CJ062501/1</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Orange Dream</t>
+          <t>NY Diesel</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -20811,23 +20811,23 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D36" s="13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G36" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E36" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>MB0824_05, MB0824_04</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -20837,14 +20837,14 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Motor Breath</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -20853,23 +20853,23 @@
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>11.7</v>
+        <v>13.5</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>14.3</v>
+        <v>16.5</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>CC012603, CC112501</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -20879,14 +20879,14 @@
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -20895,23 +20895,23 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="D38" s="13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E38" s="13" t="n">
-        <v>16.2</v>
-      </c>
       <c r="F38" s="13" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>CJ062501/2, CJ062501/1</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -20921,14 +20921,14 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Plum Tarte</t>
+          <t>Orange Dream</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -20937,65 +20937,65 @@
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>6.3</v>
+        <v>18</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>7.7</v>
+        <v>22</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>GRC102501/1</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Plum Tarte</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>10.8</v>
+        <v>11.7</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>13.2</v>
+        <v>14.3</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>CC012603, CC112501</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -21005,39 +21005,39 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>CashCow</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Rainbow Sherbet</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="E41" s="15" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F41" s="15" t="n">
         <v>19.8</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>24.2</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -21047,14 +21047,14 @@
       </c>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>CashCow</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -21063,82 +21063,82 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>16.2</v>
+        <v>6.3</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>19.8</v>
+        <v>7.7</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Shark Tank</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>11</v>
+        <v>13.2</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Rainbow Sherbet</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -21147,23 +21147,23 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>9.9</v>
+        <v>19.8</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>12.1</v>
+        <v>24.2</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>SJ092501, SJ102501</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -21173,14 +21173,14 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Scrambler</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Soft Citrus Bloom</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -21189,23 +21189,23 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>7.2</v>
+        <v>16.2</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -21215,19 +21215,19 @@
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Scrambler</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Soft Citrus Bloom</t>
+          <t>Shark Tank</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
@@ -21247,24 +21247,24 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Strawberry Cupcakes</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -21273,40 +21273,40 @@
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>15.3</v>
+        <v>9.9</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>18.7</v>
+        <v>12.1</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Sunset Sherbet</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -21315,23 +21315,23 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>19.8</v>
+        <v>7.2</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>24.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>BSS052501, BSS1024_01/1</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
@@ -21341,14 +21341,14 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Sunset Sherbet</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -21357,23 +21357,23 @@
         </is>
       </c>
       <c r="C49" s="15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>0.7900000000000007</v>
+        <v>1</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>24.21</v>
+        <v>9</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>25.79</v>
+        <v>11</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>BSS1024</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -21383,14 +21383,14 @@
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Tangie Queen</t>
+          <t>Strawberry Cupcakes</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
@@ -21411,28 +21411,28 @@
         <v>18.7</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>OPM1024_03, OPM1024_02</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Tropic Cake</t>
+          <t>Sunset Sherbet</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -21441,65 +21441,65 @@
         </is>
       </c>
       <c r="C51" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="F51" s="15" t="n">
         <v>22</v>
-      </c>
-      <c r="D51" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F51" s="15" t="n">
-        <v>24.2</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Vanilla Grapes</t>
+          <t>Sunset Sherbet</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>15.3</v>
+        <v>22.5</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>18.7</v>
+        <v>27.5</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>GP082501/2, GP052501</t>
+          <t>BSS1024_01/1, BSS1024</t>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr">
@@ -21509,39 +21509,39 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Vanilla Grapes</t>
+          <t>Tangie Queen</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C53" s="15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>18.9</v>
+        <v>15.3</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>23.1</v>
+        <v>18.7</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>GP072501/2, GP082501/1, GP072501/1</t>
+          <t>OPM1024_03, OPM1024_02</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
@@ -21551,89 +21551,215 @@
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Vanilla Grapes</t>
+          <t>Tropic Cake</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>1.889999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>23.11</v>
+        <v>19.8</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>26.89</v>
+        <v>24.2</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>GP082501/2</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="C57" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G57" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
           <t>Wedding Crusher</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B58" s="12" t="inlineStr">
         <is>
           <t>Pot.-1</t>
         </is>
       </c>
-      <c r="C55" s="15" t="n">
+      <c r="C58" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D58" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="E55" s="15" t="n">
+      <c r="E58" s="13" t="n">
         <v>19.8</v>
       </c>
-      <c r="F55" s="15" t="n">
+      <c r="F58" s="13" t="n">
         <v>24.2</v>
       </c>
-      <c r="G55" s="14" t="n">
+      <c r="G58" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="H58" s="12" t="inlineStr">
         <is>
           <t>WC082501, WC072501</t>
         </is>
       </c>
-      <c r="I55" s="14" t="inlineStr">
+      <c r="I58" s="12" t="inlineStr">
         <is>
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="J58" s="12" t="inlineStr">
         <is>
           <t>Wedding Crusher</t>
         </is>
@@ -22098,13 +22224,13 @@
         <v>25</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>0.7900000000000007</v>
+        <v>2.5</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>24.21</v>
+        <v>22.5</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>25.79</v>
+        <v>27.5</v>
       </c>
       <c r="M9" s="14">
         <f>IF(AND(C9&gt;=K9,C9&lt;=L9),"Да | Yes","НЕ | NO")</f>
@@ -22139,10 +22265,10 @@
         <v>25</v>
       </c>
       <c r="U9" s="15" t="n">
-        <v>24.21</v>
+        <v>22.5</v>
       </c>
       <c r="V9" s="15" t="n">
-        <v>25.79</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="10">
@@ -22261,13 +22387,13 @@
         <v>25</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>0.7900000000000007</v>
+        <v>2.5</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>24.21</v>
+        <v>22.5</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>25.79</v>
+        <v>27.5</v>
       </c>
       <c r="M11" s="14">
         <f>IF(AND(C11&gt;=K11,C11&lt;=L11),"Да | Yes","НЕ | NO")</f>
@@ -22302,10 +22428,10 @@
         <v>25</v>
       </c>
       <c r="U11" s="15" t="n">
-        <v>24.21</v>
+        <v>22.5</v>
       </c>
       <c r="V11" s="15" t="n">
-        <v>25.79</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="12">
@@ -22348,16 +22474,16 @@
         </is>
       </c>
       <c r="I12" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="L12" s="13" t="n">
         <v>22</v>
-      </c>
-      <c r="J12" s="13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>24.2</v>
       </c>
       <c r="M12" s="12">
         <f>IF(AND(C12&gt;=K12,C12&lt;=L12),"Да | Yes","НЕ | NO")</f>
@@ -22389,13 +22515,13 @@
         </is>
       </c>
       <c r="T12" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="U12" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="V12" s="13" t="n">
         <v>22</v>
-      </c>
-      <c r="U12" s="13" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="V12" s="13" t="n">
-        <v>24.2</v>
       </c>
     </row>
     <row r="13">
@@ -22438,16 +22564,16 @@
         </is>
       </c>
       <c r="I13" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>22.01</v>
+        <v>20.7</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="M13" s="14">
         <f>IF(AND(C13&gt;=K13,C13&lt;=L13),"Да | Yes","НЕ | NO")</f>
@@ -22528,16 +22654,16 @@
         </is>
       </c>
       <c r="I14" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="M14" s="12">
         <f>IF(AND(C14&gt;=K14,C14&lt;=L14),"Да | Yes","НЕ | NO")</f>
@@ -22618,16 +22744,16 @@
         </is>
       </c>
       <c r="I15" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="M15" s="14">
         <f>IF(AND(C15&gt;=K15,C15&lt;=L15),"Да | Yes","НЕ | NO")</f>
@@ -22708,16 +22834,16 @@
         </is>
       </c>
       <c r="I16" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>22.01</v>
+        <v>20.7</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="M16" s="12">
         <f>IF(AND(C16&gt;=K16,C16&lt;=L16),"Да | Yes","НЕ | NO")</f>
@@ -22798,16 +22924,16 @@
         </is>
       </c>
       <c r="I17" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>13.5</v>
+        <v>12.6</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>16.5</v>
+        <v>15.4</v>
       </c>
       <c r="M17" s="14">
         <f>IF(AND(C17&gt;=K17,C17&lt;=L17),"Да | Yes","НЕ | NO")</f>
@@ -22888,16 +23014,16 @@
         </is>
       </c>
       <c r="I18" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>22.01</v>
+        <v>20.7</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="M18" s="12">
         <f>IF(AND(C18&gt;=K18,C18&lt;=L18),"Да | Yes","НЕ | NO")</f>
@@ -22978,16 +23104,16 @@
         </is>
       </c>
       <c r="I19" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="M19" s="14">
         <f>IF(AND(C19&gt;=K19,C19&lt;=L19),"Да | Yes","НЕ | NO")</f>
@@ -23068,16 +23194,16 @@
         </is>
       </c>
       <c r="I20" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>22.01</v>
+        <v>20.7</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="M20" s="12">
         <f>IF(AND(C20&gt;=K20,C20&lt;=L20),"Да | Yes","НЕ | NO")</f>
@@ -23154,20 +23280,20 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I21" s="15" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>18</v>
+        <v>20.7</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>22</v>
+        <v>25.3</v>
       </c>
       <c r="M21" s="14">
         <f>IF(AND(C21&gt;=K21,C21&lt;=L21),"Да | Yes","НЕ | NO")</f>
@@ -23248,16 +23374,16 @@
         </is>
       </c>
       <c r="I22" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="M22" s="12">
         <f>IF(AND(C22&gt;=K22,C22&lt;=L22),"Да | Yes","НЕ | NO")</f>
@@ -23338,16 +23464,16 @@
         </is>
       </c>
       <c r="I23" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>22.01</v>
+        <v>20.7</v>
       </c>
       <c r="L23" s="15" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="M23" s="14">
         <f>IF(AND(C23&gt;=K23,C23&lt;=L23),"Да | Yes","НЕ | NO")</f>
@@ -23428,16 +23554,16 @@
         </is>
       </c>
       <c r="I24" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>22.01</v>
+        <v>20.7</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>25.99</v>
+        <v>25.3</v>
       </c>
       <c r="M24" s="12">
         <f>IF(AND(C24&gt;=K24,C24&lt;=L24),"Да | Yes","НЕ | NO")</f>
@@ -23775,16 +23901,16 @@
         </is>
       </c>
       <c r="I28" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="M28" s="12">
         <f>IF(AND(C28&gt;=K28,C28&lt;=L28),"Да | Yes","НЕ | NO")</f>
@@ -23812,17 +23938,17 @@
       </c>
       <c r="S28" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T28" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="U28" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="U28" s="13" t="n">
-        <v>16.2</v>
-      </c>
       <c r="V28" s="13" t="n">
-        <v>19.8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -23861,20 +23987,20 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I29" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>17.6</v>
+        <v>19.8</v>
       </c>
       <c r="M29" s="14">
         <f>IF(AND(C29&gt;=K29,C29&lt;=L29),"Да | Yes","НЕ | NO")</f>
@@ -23906,13 +24032,13 @@
         </is>
       </c>
       <c r="T29" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U29" s="15" t="n">
-        <v>16.2</v>
+        <v>14.4</v>
       </c>
       <c r="V29" s="15" t="n">
-        <v>19.8</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="30">
@@ -23955,16 +24081,16 @@
         </is>
       </c>
       <c r="I30" s="13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>14.4</v>
+        <v>12.6</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>17.6</v>
+        <v>15.4</v>
       </c>
       <c r="M30" s="12">
         <f>IF(AND(C30&gt;=K30,C30&lt;=L30),"Да | Yes","НЕ | NO")</f>
@@ -24111,20 +24237,20 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I32" s="13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>18</v>
+        <v>20.7</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>22</v>
+        <v>25.3</v>
       </c>
       <c r="M32" s="12">
         <f>IF(AND(C32&gt;=K32,C32&lt;=L32),"Да | Yes","НЕ | NO")</f>
@@ -24156,13 +24282,13 @@
         </is>
       </c>
       <c r="T32" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>18</v>
+        <v>17.1</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="33">
@@ -24205,16 +24331,16 @@
         </is>
       </c>
       <c r="I33" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
       <c r="M33" s="14">
         <f>IF(AND(C33&gt;=K33,C33&lt;=L33),"Да | Yes","НЕ | NO")</f>
@@ -24246,13 +24372,13 @@
         </is>
       </c>
       <c r="T33" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U33" s="15" t="n">
-        <v>18</v>
+        <v>17.1</v>
       </c>
       <c r="V33" s="15" t="n">
-        <v>22</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="34">
@@ -24291,20 +24417,20 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I34" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>0.4000000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>19.4</v>
+        <v>18.7</v>
       </c>
       <c r="M34" s="12">
         <f>IF(AND(C34&gt;=K34,C34&lt;=L34),"Да | Yes","НЕ | NO")</f>
@@ -24332,17 +24458,17 @@
       </c>
       <c r="S34" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T34" s="13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>15.3</v>
+        <v>18</v>
       </c>
       <c r="V34" s="13" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -24388,13 +24514,13 @@
         <v>17</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>15.41</v>
+        <v>15.3</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>18.59</v>
+        <v>18.7</v>
       </c>
       <c r="M35" s="14">
         <f>IF(AND(C35&gt;=K35,C35&lt;=L35),"Да | Yes","НЕ | NO")</f>
@@ -24468,13 +24594,13 @@
         <v>17</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>15.41</v>
+        <v>15.3</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>18.59</v>
+        <v>18.7</v>
       </c>
       <c r="M36" s="12">
         <f>IF(AND(C36&gt;=K36,C36&lt;=L36),"Да | Yes","НЕ | NO")</f>
@@ -24551,20 +24677,20 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I37" s="15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>12.6</v>
+        <v>15.3</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>15.4</v>
+        <v>18.7</v>
       </c>
       <c r="M37" s="14">
         <f>IF(AND(C37&gt;=K37,C37&lt;=L37),"Да | Yes","НЕ | NO")</f>
@@ -24631,20 +24757,20 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0.4000000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>19.4</v>
+        <v>18.7</v>
       </c>
       <c r="M38" s="12">
         <f>IF(AND(C38&gt;=K38,C38&lt;=L38),"Да | Yes","НЕ | NO")</f>
@@ -24672,17 +24798,17 @@
       </c>
       <c r="S38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T38" s="13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>15.3</v>
+        <v>18</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -24801,13 +24927,13 @@
         <v>17</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>15.41</v>
+        <v>15.3</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>18.59</v>
+        <v>18.7</v>
       </c>
       <c r="M40" s="12">
         <f>IF(AND(C40&gt;=K40,C40&lt;=L40),"Да | Yes","НЕ | NO")</f>
@@ -24839,13 +24965,13 @@
         </is>
       </c>
       <c r="T40" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U40" s="13" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="V40" s="13" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="41">
@@ -24888,16 +25014,16 @@
         </is>
       </c>
       <c r="I41" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>12.6</v>
+        <v>11.7</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>15.4</v>
+        <v>14.3</v>
       </c>
       <c r="M41" s="14">
         <f>IF(AND(C41&gt;=K41,C41&lt;=L41),"Да | Yes","НЕ | NO")</f>
@@ -24981,13 +25107,13 @@
         <v>17</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>15.41</v>
+        <v>15.3</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>18.59</v>
+        <v>18.7</v>
       </c>
       <c r="M42" s="12">
         <f>IF(AND(C42&gt;=K42,C42&lt;=L42),"Да | Yes","НЕ | NO")</f>
@@ -25394,17 +25520,17 @@
       </c>
       <c r="S47" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T47" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>15.3</v>
+        <v>18</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -25488,13 +25614,13 @@
         </is>
       </c>
       <c r="T48" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="V48" s="13" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="49">
@@ -25617,16 +25743,16 @@
         </is>
       </c>
       <c r="I50" s="13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>1.889999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>23.11</v>
+        <v>23.4</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>26.89</v>
+        <v>28.6</v>
       </c>
       <c r="M50" s="12">
         <f>IF(AND(C50&gt;=K50,C50&lt;=L50),"Да | Yes","НЕ | NO")</f>
@@ -25807,17 +25933,17 @@
       </c>
       <c r="S52" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T52" s="13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>15.3</v>
+        <v>18</v>
       </c>
       <c r="V52" s="13" t="n">
-        <v>18.7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -25901,13 +26027,13 @@
         </is>
       </c>
       <c r="T53" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U53" s="15" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="V53" s="15" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -25991,13 +26117,13 @@
         </is>
       </c>
       <c r="T54" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="V54" s="13" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -26081,13 +26207,13 @@
         </is>
       </c>
       <c r="T55" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U55" s="15" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="V55" s="15" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -26171,13 +26297,13 @@
         </is>
       </c>
       <c r="T56" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="V56" s="13" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="57">
@@ -26220,16 +26346,16 @@
         </is>
       </c>
       <c r="I57" s="15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>1.889999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>23.11</v>
+        <v>23.4</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>26.89</v>
+        <v>28.6</v>
       </c>
       <c r="M57" s="14">
         <f>IF(AND(C57&gt;=K57,C57&lt;=L57),"Да | Yes","НЕ | NO")</f>
@@ -26380,16 +26506,16 @@
         </is>
       </c>
       <c r="I59" s="15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>1.889999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>23.11</v>
+        <v>23.4</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>26.89</v>
+        <v>28.6</v>
       </c>
       <c r="M59" s="14">
         <f>IF(AND(C59&gt;=K59,C59&lt;=L59),"Да | Yes","НЕ | NO")</f>
@@ -26424,10 +26550,10 @@
         <v>25</v>
       </c>
       <c r="U59" s="15" t="n">
-        <v>23.11</v>
+        <v>22.5</v>
       </c>
       <c r="V59" s="15" t="n">
-        <v>26.89</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="60">
@@ -26560,16 +26686,16 @@
         </is>
       </c>
       <c r="I61" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="M61" s="14">
         <f>IF(AND(C61&gt;=K61,C61&lt;=L61),"Да | Yes","НЕ | NO")</f>
@@ -26640,16 +26766,16 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>1.090000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>20.91</v>
+        <v>18.9</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="M62" s="12">
         <f>IF(AND(C62&gt;=K62,C62&lt;=L62),"Да | Yes","НЕ | NO")</f>
@@ -26726,20 +26852,20 @@
       </c>
       <c r="H63" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I63" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>17.1</v>
+        <v>18.9</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="M63" s="14">
         <f>IF(AND(C63&gt;=K63,C63&lt;=L63),"Да | Yes","НЕ | NO")</f>
@@ -26820,16 +26946,16 @@
         </is>
       </c>
       <c r="I64" s="13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="M64" s="12">
         <f>IF(AND(C64&gt;=K64,C64&lt;=L64),"Да | Yes","НЕ | NO")</f>
@@ -26900,16 +27026,16 @@
         </is>
       </c>
       <c r="I65" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J65" s="15" t="n">
-        <v>1.090000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="K65" s="15" t="n">
-        <v>20.91</v>
+        <v>18.9</v>
       </c>
       <c r="L65" s="15" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="M65" s="14">
         <f>IF(AND(C65&gt;=K65,C65&lt;=L65),"Да | Yes","НЕ | NO")</f>
@@ -27543,16 +27669,16 @@
         </is>
       </c>
       <c r="I73" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="M73" s="14">
         <f>IF(AND(C73&gt;=K73,C73&lt;=L73),"Да | Yes","НЕ | NO")</f>
@@ -27619,20 +27745,20 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I74" s="13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>17.1</v>
+        <v>18.9</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="M74" s="12">
         <f>IF(AND(C74&gt;=K74,C74&lt;=L74),"Да | Yes","НЕ | NO")</f>
@@ -27703,16 +27829,16 @@
         </is>
       </c>
       <c r="I75" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>17.1</v>
+        <v>15.3</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>20.9</v>
+        <v>18.7</v>
       </c>
       <c r="M75" s="14">
         <f>IF(AND(C75&gt;=K75,C75&lt;=L75),"Да | Yes","НЕ | NO")</f>
@@ -27779,20 +27905,20 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I76" s="13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>17.1</v>
+        <v>18.9</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>20.9</v>
+        <v>23.1</v>
       </c>
       <c r="M76" s="12">
         <f>IF(AND(C76&gt;=K76,C76&lt;=L76),"Да | Yes","НЕ | NO")</f>
@@ -27863,16 +27989,16 @@
         </is>
       </c>
       <c r="I77" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>1.090000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>20.91</v>
+        <v>18.9</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="M77" s="14">
         <f>IF(AND(C77&gt;=K77,C77&lt;=L77),"Да | Yes","НЕ | NO")</f>
@@ -27943,16 +28069,16 @@
         </is>
       </c>
       <c r="I78" s="13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>1.090000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>20.91</v>
+        <v>18.9</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>23.09</v>
+        <v>23.1</v>
       </c>
       <c r="M78" s="12">
         <f>IF(AND(C78&gt;=K78,C78&lt;=L78),"Да | Yes","НЕ | NO")</f>
@@ -28103,16 +28229,16 @@
         </is>
       </c>
       <c r="I80" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J80" s="13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="M80" s="12">
         <f>IF(AND(C80&gt;=K80,C80&lt;=L80),"Да | Yes","НЕ | NO")</f>
@@ -28144,13 +28270,13 @@
         </is>
       </c>
       <c r="T80" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U80" s="13" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="V80" s="13" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="81">
@@ -28193,16 +28319,16 @@
         </is>
       </c>
       <c r="I81" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K81" s="15" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="L81" s="15" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="M81" s="14">
         <f>IF(AND(C81&gt;=K81,C81&lt;=L81),"Да | Yes","НЕ | NO")</f>
@@ -28234,13 +28360,13 @@
         </is>
       </c>
       <c r="T81" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U81" s="15" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="V81" s="15" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="82">
@@ -28373,16 +28499,16 @@
         </is>
       </c>
       <c r="I83" s="15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>13.5</v>
+        <v>11.7</v>
       </c>
       <c r="L83" s="15" t="n">
-        <v>16.5</v>
+        <v>14.3</v>
       </c>
       <c r="M83" s="14">
         <f>IF(AND(C83&gt;=K83,C83&lt;=L83),"Да | Yes","НЕ | NO")</f>
@@ -28459,20 +28585,20 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I84" s="13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="M84" s="12">
         <f>IF(AND(C84&gt;=K84,C84&lt;=L84),"Да | Yes","НЕ | NO")</f>
@@ -28556,13 +28682,13 @@
         <v>20</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>0.5000000000000016</v>
+        <v>2</v>
       </c>
       <c r="K85" s="15" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="L85" s="15" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
       <c r="M85" s="14">
         <f>IF(AND(C85&gt;=K85,C85&lt;=L85),"Да | Yes","НЕ | NO")</f>
@@ -28639,20 +28765,20 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="I86" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="J86" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K86" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="J86" s="13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="K86" s="13" t="n">
-        <v>16.51</v>
-      </c>
       <c r="L86" s="13" t="n">
-        <v>19.49</v>
+        <v>22</v>
       </c>
       <c r="M86" s="12">
         <f>IF(AND(C86&gt;=K86,C86&lt;=L86),"Да | Yes","НЕ | NO")</f>
@@ -29006,13 +29132,13 @@
         <v>20</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>0.5000000000000016</v>
+        <v>2</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>20.5</v>
+        <v>22</v>
       </c>
       <c r="M90" s="12">
         <f>IF(AND(C90&gt;=K90,C90&lt;=L90),"Да | Yes","НЕ | NO")</f>
@@ -29089,20 +29215,20 @@
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="I91" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="J91" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="J91" s="15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="K91" s="15" t="n">
-        <v>16.51</v>
-      </c>
       <c r="L91" s="15" t="n">
-        <v>19.49</v>
+        <v>22</v>
       </c>
       <c r="M91" s="14">
         <f>IF(AND(C91&gt;=K91,C91&lt;=L91),"Да | Yes","НЕ | NO")</f>
@@ -29183,16 +29309,16 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>16.51</v>
+        <v>14.4</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>19.49</v>
+        <v>17.6</v>
       </c>
       <c r="M92" s="12">
         <f>IF(AND(C92&gt;=K92,C92&lt;=L92),"Да | Yes","НЕ | NO")</f>
@@ -29636,13 +29762,13 @@
         <v>22</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="K97" s="15" t="n">
-        <v>19.81</v>
+        <v>19.8</v>
       </c>
       <c r="L97" s="15" t="n">
-        <v>24.19</v>
+        <v>24.2</v>
       </c>
       <c r="M97" s="14">
         <f>IF(AND(C97&gt;=K97,C97&lt;=L97),"Да | Yes","НЕ | NO")</f>
@@ -29723,16 +29849,16 @@
         </is>
       </c>
       <c r="I98" s="13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J98" s="13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="M98" s="12">
         <f>IF(AND(C98&gt;=K98,C98&lt;=L98),"Да | Yes","НЕ | NO")</f>
@@ -29803,16 +29929,16 @@
         </is>
       </c>
       <c r="I99" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="L99" s="15" t="n">
-        <v>19.8</v>
+        <v>18.7</v>
       </c>
       <c r="M99" s="14">
         <f>IF(AND(C99&gt;=K99,C99&lt;=L99),"Да | Yes","НЕ | NO")</f>
@@ -29886,13 +30012,13 @@
         <v>12</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>11.01</v>
+        <v>10.8</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>12.99</v>
+        <v>13.2</v>
       </c>
       <c r="M100" s="12">
         <f>IF(AND(C100&gt;=K100,C100&lt;=L100),"Да | Yes","НЕ | NO")</f>
@@ -29963,16 +30089,16 @@
         </is>
       </c>
       <c r="I101" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K101" s="15" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="L101" s="15" t="n">
-        <v>11</v>
+        <v>9.9</v>
       </c>
       <c r="M101" s="14">
         <f>IF(AND(C101&gt;=K101,C101&lt;=L101),"Да | Yes","НЕ | NO")</f>
@@ -30049,20 +30175,20 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I102" s="13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>11</v>
+        <v>13.2</v>
       </c>
       <c r="M102" s="12">
         <f>IF(AND(C102&gt;=K102,C102&lt;=L102),"Да | Yes","НЕ | NO")</f>

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -17725,7 +17725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17737,6 +17737,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -17756,7 +17757,7 @@
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Класите на Атласот на потенција (номинала ± толеранција), директно од potency_dataset.json. Секоја серија ја носи декларацијата на својата класа.  |  The Potency Atlas's grades (nominal ± tolerance), straight from potency_dataset.json. Every batch carries its tier's declaration.</t>
+          <t>Класите на Атласот на потенција (номинала ± толеранција), директно од potency_dataset.json. Секоја серија ја носи декларацијата на својата класа. Соседните класи на иста сорта немаат празен простор меѓу себе, освен кога тоа е означено во „Забелешка“.  |  The Potency Atlas's grades (nominal ± tolerance), straight from potency_dataset.json. Every batch carries its tier's declaration. Adjacent tiers of the same strain carry no blind gap between them, except where flagged in "Note".</t>
         </is>
       </c>
     </row>
@@ -17806,6 +17807,11 @@
           <t>Основа | Basis</t>
         </is>
       </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Забелешка | Note</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -17843,6 +17849,7 @@
           <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
+      <c r="J6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -17880,6 +17887,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -17917,6 +17925,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -17933,13 +17942,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>1</v>
@@ -17954,6 +17963,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -17967,16 +17977,16 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>22.5</v>
+        <v>21.81</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>27.5</v>
+        <v>26.19</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>2</v>
@@ -17991,6 +18001,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -18004,16 +18015,16 @@
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>15.4</v>
+        <v>17.2</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>1</v>
@@ -18028,6 +18039,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -18041,16 +18053,16 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>16.2</v>
+        <v>17.21</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>19.8</v>
+        <v>20.79</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>2</v>
@@ -18065,6 +18077,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -18081,13 +18094,13 @@
         <v>23</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>6</v>
@@ -18102,6 +18115,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -18115,30 +18129,31 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1.3</v>
+        <v>0.64</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>11.7</v>
+        <v>11.36</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>14.3</v>
+        <v>12.64</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>CC012603, CC112501</t>
+          <t>CC012603</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -18152,23 +18167,23 @@
         </is>
       </c>
       <c r="C15" s="15" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>16.2</v>
+        <v>12.65</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>19.8</v>
+        <v>15.35</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -18176,48 +18191,50 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Cash Cow</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>9</v>
+        <v>15.36</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>11</v>
+        <v>18.64</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -18226,35 +18243,36 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Clemosa a bud</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -18263,23 +18281,23 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>12.6</v>
+        <v>7.2</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>15.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>FB012601/1</t>
+          <t>CLE072501</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -18287,6 +18305,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -18296,27 +18315,27 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>16.2</v>
+        <v>13.65</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>19.8</v>
+        <v>16.35</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>FB112501, FB012603V, FB012602</t>
+          <t>FB012601/1</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -18324,6 +18343,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -18333,27 +18353,27 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>2.3</v>
+        <v>1.64</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>20.7</v>
+        <v>16.36</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>25.3</v>
+        <v>19.64</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>FB112501, FB012603V, FB012602</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -18361,36 +18381,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>11.7</v>
+        <v>19.65</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>14.3</v>
+        <v>22.35</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -18398,6 +18419,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -18407,27 +18429,27 @@
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="E22" s="13" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F22" s="13" t="n">
         <v>15.3</v>
       </c>
-      <c r="F22" s="13" t="n">
-        <v>18.7</v>
-      </c>
       <c r="G22" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>GG012601, GG1024_02, GG012603, GG112501, GG1024_01</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -18435,36 +18457,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C23" s="15" t="n">
         <v>17</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>GP082501/2, GP052501</t>
+          <t>GG012601, GG1024_02, GG012603, GG112501, GG1024_01</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -18472,6 +18495,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -18481,27 +18505,27 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>18.9</v>
+        <v>15.65</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>23.1</v>
+        <v>18.35</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>GP072501/2, GP082501/1, GP072501/1, GP0824_02</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -18509,6 +18533,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -18518,27 +18543,27 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>23.4</v>
+        <v>18.36</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>28.6</v>
+        <v>21.64</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>GP062501, GP0824_03, GP092501</t>
+          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -18546,43 +18571,45 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>0.7</v>
+        <v>2.35</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>6.3</v>
+        <v>21.65</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>7.7</v>
+        <v>26.35</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/1</t>
+          <t>GP0824_02, GP062501, GP0824_03, GP092501</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -18592,64 +18619,69 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>10.8</v>
+        <v>6.3</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>13.2</v>
+        <v>7.7</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 7.70%–10.80% | NO GRADE 7.70%–10.80%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>15.3</v>
+        <v>10.8</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>18.7</v>
+        <v>13.2</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -18657,6 +18689,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -18666,27 +18699,27 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>18.9</v>
+        <v>16.65</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>23.1</v>
+        <v>19.35</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>HPA052501, HPA1024_01</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -18694,36 +18727,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>14.4</v>
+        <v>19.36</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>17.6</v>
+        <v>22.64</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>JD012603/02V, JD012603/01</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -18731,6 +18765,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -18740,27 +18775,27 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D31" s="15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>14.73</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="G31" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>3</v>
-      </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>JD012601, JD112501, JD012603/02</t>
+          <t>JD012603/02V, JD012603/01</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -18768,36 +18803,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>15.3</v>
+        <v>17.28</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>18.7</v>
+        <v>20.72</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>JD012601, JD112501, JD012603/02</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -18805,6 +18841,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -18814,27 +18851,27 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>2.1</v>
+        <v>1.35</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>18.9</v>
+        <v>16.65</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>23.1</v>
+        <v>19.35</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>J31112501, J31122501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -18842,36 +18879,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>15.3</v>
+        <v>19.36</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>18.7</v>
+        <v>22.64</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>J31112501, J31122501</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -18879,11 +18917,12 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -18904,11 +18943,11 @@
         <v>18.7</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>MB0824_05, MB0824_04</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -18916,11 +18955,12 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J35" s="14" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
@@ -18929,23 +18969,23 @@
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>7.2</v>
+        <v>15.3</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>18.7</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>OPM122501, OPM112501</t>
+          <t>MB0824_05, MB0824_04</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -18953,6 +18993,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -18962,27 +19003,27 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>9</v>
+        <v>7.67</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>11</v>
+        <v>8.33</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>OPM122501, OPM112501</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -18990,6 +19031,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
@@ -18999,32 +19041,37 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.3</v>
+        <v>0.66</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>11.7</v>
+        <v>8.34</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>14.3</v>
+        <v>9.66</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>OPM052501</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 9.66%–14.10% | NO GRADE 9.66%–14.10%</t>
         </is>
       </c>
     </row>
@@ -19036,27 +19083,27 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>17.6</v>
+        <v>15.9</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>2</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>OMP1024_01, OPM1024_03</t>
+          <t>OPM052501, OMP1024_01</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -19064,6 +19111,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -19073,27 +19121,27 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-5</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>18</v>
+        <v>15.91</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>22</v>
+        <v>18.09</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>OPM1024_02, OPM1024</t>
+          <t>OPM1024_03, OPM1024_02</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -19101,36 +19149,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>9</v>
+        <v>18.1</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>11</v>
+        <v>21.9</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -19138,6 +19187,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J41" s="14" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -19147,27 +19197,27 @@
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>1.3</v>
+        <v>1.05</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>11.7</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>14.3</v>
+        <v>12.05</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>PM092501, PM112501</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -19175,48 +19225,50 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>1.6</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>14.4</v>
+        <v>12.06</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>17.6</v>
+        <v>13.94</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>PM092501, PM112501</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -19225,30 +19277,31 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -19258,27 +19311,27 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>19.8</v>
+        <v>16.21</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>24.2</v>
+        <v>19.79</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -19286,36 +19339,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J45" s="14" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>8.1</v>
+        <v>19.8</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>9.9</v>
+        <v>24.2</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -19323,6 +19377,7 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -19332,27 +19387,27 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>10.8</v>
+        <v>8.1</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>13.2</v>
+        <v>9.9</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>SJ092501, SJ102501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -19360,48 +19415,50 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>2.2</v>
+        <v>1.09</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>19.8</v>
+        <v>9.91</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>24.2</v>
+        <v>12.09</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -19422,24 +19479,63 @@
         <v>24.2</v>
       </c>
       <c r="G49" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>WED102501</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D50" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G50" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>WC082501, WC072501</t>
         </is>
       </c>
-      <c r="I49" s="14" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
+      <c r="J50" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19451,7 +19547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19464,6 +19560,7 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -19538,6 +19635,11 @@
           <t>Оригинално(и) име(иња) | Original name(s)</t>
         </is>
       </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>Забелешка | Note</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -19580,6 +19682,7 @@
           <t>Amnesia Core Cut</t>
         </is>
       </c>
+      <c r="K6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
@@ -19622,6 +19725,7 @@
           <t>Appels &amp; Bananas</t>
         </is>
       </c>
+      <c r="K7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -19664,6 +19768,7 @@
           <t>Blue Gelato</t>
         </is>
       </c>
+      <c r="K8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
@@ -19706,6 +19811,7 @@
           <t>Sleepy Joe</t>
         </is>
       </c>
+      <c r="K9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -19748,6 +19854,7 @@
           <t>GG4</t>
         </is>
       </c>
+      <c r="K10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -19790,6 +19897,11 @@
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
+      <c r="K11" s="14" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 8.80%–13.50% | NO GRADE 8.80%–13.50%</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -19832,6 +19944,7 @@
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
+      <c r="K12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -19874,6 +19987,7 @@
           <t>Clemosa</t>
         </is>
       </c>
+      <c r="K13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -19887,16 +20001,16 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="13" t="n">
         <v>1.8</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>19.8</v>
+        <v>20.8</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>1</v>
@@ -19916,6 +20030,7 @@
           <t>Cap Junkie</t>
         </is>
       </c>
+      <c r="K14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -19929,16 +20044,16 @@
         </is>
       </c>
       <c r="C15" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>21.6</v>
+        <v>20.81</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>26.4</v>
+        <v>25.19</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>5</v>
@@ -19958,6 +20073,7 @@
           <t>Cap Junkie</t>
         </is>
       </c>
+      <c r="K15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -19974,13 +20090,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>13.5</v>
+        <v>13.65</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>16.5</v>
+        <v>16.35</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
@@ -20000,6 +20116,7 @@
           <t>Fat Bastard</t>
         </is>
       </c>
+      <c r="K16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -20013,23 +20130,23 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>17.1</v>
+        <v>16.36</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>20.9</v>
+        <v>19.64</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>FB012603V, FB012603</t>
+          <t>FB012603V</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -20042,36 +20159,37 @@
           <t>Fat Bastard</t>
         </is>
       </c>
+      <c r="K17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Fat Sofa</t>
+          <t>Daywalker</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>14.4</v>
+        <v>19.65</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>17.6</v>
+        <v>22.35</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>FB112501</t>
+          <t>FB012603</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -20084,6 +20202,7 @@
           <t>Fat Bastard</t>
         </is>
       </c>
+      <c r="K18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -20093,27 +20212,27 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G19" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F19" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="G19" s="14" t="n">
-        <v>1</v>
-      </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>FB012602</t>
+          <t>FB112501, FB012602</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -20126,6 +20245,7 @@
           <t>Fat Bastard</t>
         </is>
       </c>
+      <c r="K19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -20139,16 +20259,16 @@
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>9</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>11</v>
+        <v>12.05</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1</v>
@@ -20168,6 +20288,7 @@
           <t>Permanent Marker</t>
         </is>
       </c>
+      <c r="K20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -20184,13 +20305,13 @@
         <v>13</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>11.7</v>
+        <v>12.06</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>2</v>
@@ -20210,6 +20331,7 @@
           <t>Permanent Marker</t>
         </is>
       </c>
+      <c r="K21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
@@ -20252,6 +20374,7 @@
           <t>GG4</t>
         </is>
       </c>
+      <c r="K22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -20265,16 +20388,16 @@
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>1</v>
@@ -20294,6 +20417,7 @@
           <t>Gorilla Glue</t>
         </is>
       </c>
+      <c r="K23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
@@ -20307,23 +20431,23 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>14.4</v>
+        <v>15.31</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>17.6</v>
+        <v>18.69</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>GG1024_02</t>
+          <t>GG1024_02, GG1024_01</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -20336,36 +20460,37 @@
           <t>Gorilla Glue</t>
         </is>
       </c>
+      <c r="K24" s="12" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Gorilla Gang</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>18</v>
+        <v>22.5</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>22</v>
+        <v>27.5</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>GG1024_01</t>
+          <t>GP0824_02, GP0824_03, GP092501</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -20375,14 +20500,15 @@
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
-        </is>
-      </c>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Hazy Daze</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -20403,11 +20529,11 @@
         <v>23.1</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>GP0824_02</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -20417,39 +20543,40 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="K26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>23.4</v>
+        <v>15.3</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>28.6</v>
+        <v>18.7</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>GP0824_03, GP092501</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -20459,14 +20586,15 @@
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Hazy Daze</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -20475,23 +20603,23 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>18.9</v>
+        <v>14.73</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>23.1</v>
+        <v>17.27</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>HPA052501, HPA1024_01</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -20501,39 +20629,40 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
-        </is>
-      </c>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="K28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>15.3</v>
+        <v>17.28</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>18.7</v>
+        <v>20.72</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>JD012601, JD112501, JD012603/02</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -20543,14 +20672,15 @@
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
-        </is>
-      </c>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -20559,23 +20689,23 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>13.5</v>
+        <v>16.65</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>16.5</v>
+        <v>19.35</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>JD012603/02V</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -20585,14 +20715,15 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="K30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -20601,23 +20732,23 @@
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31" s="15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>22.64</v>
+      </c>
+      <c r="G31" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="F31" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="G31" s="14" t="n">
-        <v>3</v>
-      </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>JD012601, JD112501, JD012603/02</t>
+          <t>J31112501, J31122501</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -20627,14 +20758,15 @@
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
-        </is>
-      </c>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -20659,7 +20791,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -20669,56 +20801,58 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="K32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Lifeguard</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>23.1</v>
+        <v>17.6</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>J31112501, J31122501</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
-        </is>
-      </c>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="K33" s="14" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>NY Diesel</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -20739,11 +20873,11 @@
         <v>18.7</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>MB0824_05, MB0824_04</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -20753,14 +20887,15 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
-        </is>
-      </c>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="K34" s="12" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Lifeguard</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -20769,65 +20904,66 @@
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>17.6</v>
+        <v>16.2</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
-        </is>
-      </c>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+      <c r="K35" s="14" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>NY Diesel</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>15.3</v>
+        <v>16.21</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>18.7</v>
+        <v>19.79</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>MB0824_05, MB0824_04</t>
+          <t>CJ062501/2</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -20837,9 +20973,10 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
-        </is>
-      </c>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+      <c r="K36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -20849,27 +20986,27 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>13.5</v>
+        <v>19.8</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>16.5</v>
+        <v>24.2</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -20882,16 +21019,17 @@
           <t>Cap Junkie</t>
         </is>
       </c>
+      <c r="K37" s="14" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>OG Banana's</t>
+          <t>Orange Dream</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C38" s="13" t="n">
@@ -20907,11 +21045,11 @@
         <v>22</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>CJ062501/2, CJ062501/1</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -20921,14 +21059,15 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
-        </is>
-      </c>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="K38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Orange Dream</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -20937,35 +21076,36 @@
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>2</v>
+        <v>0.64</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>18</v>
+        <v>11.36</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>22</v>
+        <v>12.64</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>CC012603</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
-        </is>
-      </c>
+          <t>CashCow</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -20975,27 +21115,27 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>11.7</v>
+        <v>12.65</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>14.3</v>
+        <v>15.35</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>CC012603, CC112501</t>
+          <t>CC112501</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -21008,6 +21148,7 @@
           <t>CashCow</t>
         </is>
       </c>
+      <c r="K40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -21017,20 +21158,20 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>16.2</v>
+        <v>15.36</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>19.8</v>
+        <v>18.64</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
@@ -21050,6 +21191,7 @@
           <t>CashCow</t>
         </is>
       </c>
+      <c r="K41" s="14" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
@@ -21092,6 +21234,11 @@
           <t>Grapes and Cream</t>
         </is>
       </c>
+      <c r="K42" s="12" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 7.70%–10.80% | NO GRADE 7.70%–10.80%</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
@@ -21134,6 +21281,7 @@
           <t>Grapes and Cream</t>
         </is>
       </c>
+      <c r="K43" s="14" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
@@ -21176,6 +21324,7 @@
           <t>Scrambler</t>
         </is>
       </c>
+      <c r="K44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -21218,6 +21367,7 @@
           <t>Scrambler</t>
         </is>
       </c>
+      <c r="K45" s="14" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
@@ -21260,6 +21410,7 @@
           <t>Chem Flyer</t>
         </is>
       </c>
+      <c r="K46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
@@ -21302,6 +21453,7 @@
           <t>Sleepy Joe</t>
         </is>
       </c>
+      <c r="K47" s="14" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
@@ -21318,13 +21470,13 @@
         <v>8</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
@@ -21344,6 +21496,7 @@
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
+      <c r="K48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
@@ -21357,16 +21510,16 @@
         </is>
       </c>
       <c r="C49" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>9</v>
+        <v>8.34</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>11</v>
+        <v>9.66</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>1</v>
@@ -21386,6 +21539,7 @@
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
+      <c r="K49" s="14" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
@@ -21428,6 +21582,7 @@
           <t>Jelly Donuts</t>
         </is>
       </c>
+      <c r="K50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
@@ -21444,13 +21599,13 @@
         <v>20</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>1</v>
@@ -21470,6 +21625,7 @@
           <t>Blue Sunset Sherbet</t>
         </is>
       </c>
+      <c r="K51" s="14" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
@@ -21483,16 +21639,16 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>22.5</v>
+        <v>21.81</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>27.5</v>
+        <v>26.19</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>2</v>
@@ -21512,6 +21668,7 @@
           <t>Blue Sunset Sherbet</t>
         </is>
       </c>
+      <c r="K52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
@@ -21554,6 +21711,7 @@
           <t>Orange Punch Mimosa</t>
         </is>
       </c>
+      <c r="K53" s="14" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
@@ -21596,6 +21754,7 @@
           <t>Wedding Cake</t>
         </is>
       </c>
+      <c r="K54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -21609,16 +21768,16 @@
         </is>
       </c>
       <c r="C55" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>14.4</v>
+        <v>15.65</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>17.6</v>
+        <v>18.35</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>1</v>
@@ -21638,6 +21797,7 @@
           <t>Grape Pie</t>
         </is>
       </c>
+      <c r="K55" s="14" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
@@ -21654,13 +21814,13 @@
         <v>20</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>18</v>
+        <v>18.36</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>22</v>
+        <v>21.64</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>4</v>
@@ -21680,6 +21840,7 @@
           <t>Grape Pie</t>
         </is>
       </c>
+      <c r="K56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
@@ -21693,16 +21854,16 @@
         </is>
       </c>
       <c r="C57" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>22.5</v>
+        <v>21.65</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>27.5</v>
+        <v>26.35</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>1</v>
@@ -21722,6 +21883,7 @@
           <t>Grape Pie</t>
         </is>
       </c>
+      <c r="K57" s="14" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
@@ -21764,12 +21926,13 @@
           <t>Wedding Crusher</t>
         </is>
       </c>
+      <c r="K58" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A3:K3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22221,16 +22384,16 @@
         </is>
       </c>
       <c r="I9" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>22.5</v>
+        <v>21.81</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>27.5</v>
+        <v>26.19</v>
       </c>
       <c r="M9" s="14">
         <f>IF(AND(C9&gt;=K9,C9&lt;=L9),"Да | Yes","НЕ | NO")</f>
@@ -22262,13 +22425,13 @@
         </is>
       </c>
       <c r="T9" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U9" s="15" t="n">
-        <v>22.5</v>
+        <v>21.81</v>
       </c>
       <c r="V9" s="15" t="n">
-        <v>27.5</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="10">
@@ -22384,16 +22547,16 @@
         </is>
       </c>
       <c r="I11" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>22.5</v>
+        <v>21.81</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>27.5</v>
+        <v>26.19</v>
       </c>
       <c r="M11" s="14">
         <f>IF(AND(C11&gt;=K11,C11&lt;=L11),"Да | Yes","НЕ | NO")</f>
@@ -22425,13 +22588,13 @@
         </is>
       </c>
       <c r="T11" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U11" s="15" t="n">
-        <v>22.5</v>
+        <v>21.81</v>
       </c>
       <c r="V11" s="15" t="n">
-        <v>27.5</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="12">
@@ -22477,13 +22640,13 @@
         <v>20</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="M12" s="12">
         <f>IF(AND(C12&gt;=K12,C12&lt;=L12),"Да | Yes","НЕ | NO")</f>
@@ -22518,10 +22681,10 @@
         <v>20</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="13">
@@ -22567,13 +22730,13 @@
         <v>23</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="M13" s="14">
         <f>IF(AND(C13&gt;=K13,C13&lt;=L13),"Да | Yes","НЕ | NO")</f>
@@ -22605,13 +22768,13 @@
         </is>
       </c>
       <c r="T13" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U13" s="15" t="n">
-        <v>21.6</v>
+        <v>20.81</v>
       </c>
       <c r="V13" s="15" t="n">
-        <v>26.4</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="14">
@@ -22654,16 +22817,16 @@
         </is>
       </c>
       <c r="I14" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>16.2</v>
+        <v>17.21</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>19.8</v>
+        <v>20.79</v>
       </c>
       <c r="M14" s="12">
         <f>IF(AND(C14&gt;=K14,C14&lt;=L14),"Да | Yes","НЕ | NO")</f>
@@ -22695,13 +22858,13 @@
         </is>
       </c>
       <c r="T14" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>18</v>
+        <v>16.21</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>22</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="15">
@@ -22744,16 +22907,16 @@
         </is>
       </c>
       <c r="I15" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>16.2</v>
+        <v>17.21</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>19.8</v>
+        <v>20.79</v>
       </c>
       <c r="M15" s="14">
         <f>IF(AND(C15&gt;=K15,C15&lt;=L15),"Да | Yes","НЕ | NO")</f>
@@ -22785,13 +22948,13 @@
         </is>
       </c>
       <c r="T15" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U15" s="15" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="V15" s="15" t="n">
-        <v>19.8</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="16">
@@ -22837,13 +23000,13 @@
         <v>23</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="M16" s="12">
         <f>IF(AND(C16&gt;=K16,C16&lt;=L16),"Да | Yes","НЕ | NO")</f>
@@ -22875,13 +23038,13 @@
         </is>
       </c>
       <c r="T16" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U16" s="13" t="n">
-        <v>21.6</v>
+        <v>20.81</v>
       </c>
       <c r="V16" s="13" t="n">
-        <v>26.4</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="17">
@@ -22924,16 +23087,16 @@
         </is>
       </c>
       <c r="I17" s="15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>12.6</v>
+        <v>14.8</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>15.4</v>
+        <v>17.2</v>
       </c>
       <c r="M17" s="14">
         <f>IF(AND(C17&gt;=K17,C17&lt;=L17),"Да | Yes","НЕ | NO")</f>
@@ -22968,10 +23131,10 @@
         <v>15</v>
       </c>
       <c r="U17" s="15" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="V17" s="15" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="18">
@@ -23017,13 +23180,13 @@
         <v>23</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="M18" s="12">
         <f>IF(AND(C18&gt;=K18,C18&lt;=L18),"Да | Yes","НЕ | NO")</f>
@@ -23055,13 +23218,13 @@
         </is>
       </c>
       <c r="T18" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>21.6</v>
+        <v>20.81</v>
       </c>
       <c r="V18" s="13" t="n">
-        <v>26.4</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="19">
@@ -23104,16 +23267,16 @@
         </is>
       </c>
       <c r="I19" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>16.2</v>
+        <v>17.21</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>19.8</v>
+        <v>20.79</v>
       </c>
       <c r="M19" s="14">
         <f>IF(AND(C19&gt;=K19,C19&lt;=L19),"Да | Yes","НЕ | NO")</f>
@@ -23145,13 +23308,13 @@
         </is>
       </c>
       <c r="T19" s="15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="V19" s="15" t="n">
-        <v>19.8</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="20">
@@ -23197,13 +23360,13 @@
         <v>23</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="M20" s="12">
         <f>IF(AND(C20&gt;=K20,C20&lt;=L20),"Да | Yes","НЕ | NO")</f>
@@ -23235,13 +23398,13 @@
         </is>
       </c>
       <c r="T20" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>21.6</v>
+        <v>20.81</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>26.4</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="21">
@@ -23287,13 +23450,13 @@
         <v>23</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="M21" s="14">
         <f>IF(AND(C21&gt;=K21,C21&lt;=L21),"Да | Yes","НЕ | NO")</f>
@@ -23321,17 +23484,17 @@
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T21" s="15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U21" s="15" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="V21" s="15" t="n">
-        <v>22</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="22">
@@ -23374,16 +23537,16 @@
         </is>
       </c>
       <c r="I22" s="13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>16.2</v>
+        <v>17.21</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>19.8</v>
+        <v>20.79</v>
       </c>
       <c r="M22" s="12">
         <f>IF(AND(C22&gt;=K22,C22&lt;=L22),"Да | Yes","НЕ | NO")</f>
@@ -23415,13 +23578,13 @@
         </is>
       </c>
       <c r="T22" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>18</v>
+        <v>16.21</v>
       </c>
       <c r="V22" s="13" t="n">
-        <v>22</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="23">
@@ -23467,13 +23630,13 @@
         <v>23</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L23" s="15" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="M23" s="14">
         <f>IF(AND(C23&gt;=K23,C23&lt;=L23),"Да | Yes","НЕ | NO")</f>
@@ -23505,13 +23668,13 @@
         </is>
       </c>
       <c r="T23" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U23" s="15" t="n">
-        <v>21.6</v>
+        <v>20.81</v>
       </c>
       <c r="V23" s="15" t="n">
-        <v>26.4</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="24">
@@ -23557,13 +23720,13 @@
         <v>23</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="M24" s="12">
         <f>IF(AND(C24&gt;=K24,C24&lt;=L24),"Да | Yes","НЕ | NO")</f>
@@ -23595,13 +23758,13 @@
         </is>
       </c>
       <c r="T24" s="13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U24" s="13" t="n">
-        <v>21.6</v>
+        <v>20.81</v>
       </c>
       <c r="V24" s="13" t="n">
-        <v>26.4</v>
+        <v>25.19</v>
       </c>
     </row>
     <row r="25">
@@ -23640,20 +23803,20 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I25" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>16.2</v>
+        <v>15.36</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>19.8</v>
+        <v>18.64</v>
       </c>
       <c r="M25" s="14">
         <f>IF(AND(C25&gt;=K25,C25&lt;=L25),"Да | Yes","НЕ | NO")</f>
@@ -23681,17 +23844,17 @@
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T25" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U25" s="15" t="n">
-        <v>16.2</v>
+        <v>15.36</v>
       </c>
       <c r="V25" s="15" t="n">
-        <v>19.8</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="26">
@@ -23730,20 +23893,20 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I26" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>11.7</v>
+        <v>12.65</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>14.3</v>
+        <v>15.35</v>
       </c>
       <c r="M26" s="12">
         <f>IF(AND(C26&gt;=K26,C26&lt;=L26),"Да | Yes","НЕ | NO")</f>
@@ -23768,17 +23931,17 @@
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T26" s="13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>11.7</v>
+        <v>12.65</v>
       </c>
       <c r="V26" s="13" t="n">
-        <v>14.3</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="27">
@@ -23904,13 +24067,13 @@
         <v>18</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>16.2</v>
+        <v>16.36</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>19.8</v>
+        <v>19.64</v>
       </c>
       <c r="M28" s="12">
         <f>IF(AND(C28&gt;=K28,C28&lt;=L28),"Да | Yes","НЕ | NO")</f>
@@ -23938,17 +24101,17 @@
       </c>
       <c r="S28" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T28" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U28" s="13" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="V28" s="13" t="n">
-        <v>22</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="29">
@@ -23994,13 +24157,13 @@
         <v>18</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>16.2</v>
+        <v>16.36</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>19.8</v>
+        <v>19.64</v>
       </c>
       <c r="M29" s="14">
         <f>IF(AND(C29&gt;=K29,C29&lt;=L29),"Да | Yes","НЕ | NO")</f>
@@ -24032,13 +24195,13 @@
         </is>
       </c>
       <c r="T29" s="15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="U29" s="15" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="V29" s="15" t="n">
-        <v>17.6</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="30">
@@ -24081,16 +24244,16 @@
         </is>
       </c>
       <c r="I30" s="13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>12.6</v>
+        <v>13.65</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>15.4</v>
+        <v>16.35</v>
       </c>
       <c r="M30" s="12">
         <f>IF(AND(C30&gt;=K30,C30&lt;=L30),"Да | Yes","НЕ | NO")</f>
@@ -24125,10 +24288,10 @@
         <v>15</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>13.5</v>
+        <v>13.65</v>
       </c>
       <c r="V30" s="13" t="n">
-        <v>16.5</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="31">
@@ -24241,16 +24404,16 @@
         </is>
       </c>
       <c r="I32" s="13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>20.7</v>
+        <v>19.65</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>25.3</v>
+        <v>22.35</v>
       </c>
       <c r="M32" s="12">
         <f>IF(AND(C32&gt;=K32,C32&lt;=L32),"Да | Yes","НЕ | NO")</f>
@@ -24278,17 +24441,17 @@
       </c>
       <c r="S32" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T32" s="13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>17.1</v>
+        <v>19.65</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>20.9</v>
+        <v>22.35</v>
       </c>
     </row>
     <row r="33">
@@ -24334,13 +24497,13 @@
         <v>18</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>16.2</v>
+        <v>16.36</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>19.8</v>
+        <v>19.64</v>
       </c>
       <c r="M33" s="14">
         <f>IF(AND(C33&gt;=K33,C33&lt;=L33),"Да | Yes","НЕ | NO")</f>
@@ -24372,13 +24535,13 @@
         </is>
       </c>
       <c r="T33" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U33" s="15" t="n">
-        <v>17.1</v>
+        <v>16.36</v>
       </c>
       <c r="V33" s="15" t="n">
-        <v>20.9</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="34">
@@ -24424,13 +24587,13 @@
         <v>17</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="M34" s="12">
         <f>IF(AND(C34&gt;=K34,C34&lt;=L34),"Да | Yes","НЕ | NO")</f>
@@ -24458,17 +24621,17 @@
       </c>
       <c r="S34" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T34" s="13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>18</v>
+        <v>15.31</v>
       </c>
       <c r="V34" s="13" t="n">
-        <v>22</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="35">
@@ -24514,13 +24677,13 @@
         <v>17</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="M35" s="14">
         <f>IF(AND(C35&gt;=K35,C35&lt;=L35),"Да | Yes","НЕ | NO")</f>
@@ -24594,13 +24757,13 @@
         <v>17</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="M36" s="12">
         <f>IF(AND(C36&gt;=K36,C36&lt;=L36),"Да | Yes","НЕ | NO")</f>
@@ -24684,13 +24847,13 @@
         <v>17</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="M37" s="14">
         <f>IF(AND(C37&gt;=K37,C37&lt;=L37),"Да | Yes","НЕ | NO")</f>
@@ -24764,13 +24927,13 @@
         <v>17</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="M38" s="12">
         <f>IF(AND(C38&gt;=K38,C38&lt;=L38),"Да | Yes","НЕ | NO")</f>
@@ -24798,17 +24961,17 @@
       </c>
       <c r="S38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T38" s="13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>18</v>
+        <v>15.31</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>22</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="39">
@@ -24927,13 +25090,13 @@
         <v>17</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="M40" s="12">
         <f>IF(AND(C40&gt;=K40,C40&lt;=L40),"Да | Yes","НЕ | NO")</f>
@@ -24965,13 +25128,13 @@
         </is>
       </c>
       <c r="T40" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U40" s="13" t="n">
-        <v>14.4</v>
+        <v>15.31</v>
       </c>
       <c r="V40" s="13" t="n">
-        <v>17.6</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="41">
@@ -25014,16 +25177,16 @@
         </is>
       </c>
       <c r="I41" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J41" s="15" t="n">
         <v>1.3</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="M41" s="14">
         <f>IF(AND(C41&gt;=K41,C41&lt;=L41),"Да | Yes","НЕ | NO")</f>
@@ -25055,13 +25218,13 @@
         </is>
       </c>
       <c r="T41" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U41" s="15" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
       <c r="V41" s="15" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="42">
@@ -25107,13 +25270,13 @@
         <v>17</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>15.3</v>
+        <v>15.31</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>18.7</v>
+        <v>18.69</v>
       </c>
       <c r="M42" s="12">
         <f>IF(AND(C42&gt;=K42,C42&lt;=L42),"Да | Yes","НЕ | NO")</f>
@@ -25399,20 +25562,20 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I46" s="13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>18.9</v>
+        <v>21.65</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>23.1</v>
+        <v>26.35</v>
       </c>
       <c r="M46" s="12">
         <f>IF(AND(C46&gt;=K46,C46&lt;=L46),"Да | Yes","НЕ | NO")</f>
@@ -25479,20 +25642,20 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I47" s="15" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>15.3</v>
+        <v>18.36</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>18.7</v>
+        <v>21.64</v>
       </c>
       <c r="M47" s="14">
         <f>IF(AND(C47&gt;=K47,C47&lt;=L47),"Да | Yes","НЕ | NO")</f>
@@ -25527,10 +25690,10 @@
         <v>20</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>18</v>
+        <v>18.36</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>22</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="48">
@@ -25576,13 +25739,13 @@
         <v>17</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>15.3</v>
+        <v>15.65</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="M48" s="12">
         <f>IF(AND(C48&gt;=K48,C48&lt;=L48),"Да | Yes","НЕ | NO")</f>
@@ -25614,13 +25777,13 @@
         </is>
       </c>
       <c r="T48" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>14.4</v>
+        <v>15.65</v>
       </c>
       <c r="V48" s="13" t="n">
-        <v>17.6</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="49">
@@ -25659,20 +25822,20 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I49" s="15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>18.9</v>
+        <v>21.65</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>23.1</v>
+        <v>26.35</v>
       </c>
       <c r="M49" s="14">
         <f>IF(AND(C49&gt;=K49,C49&lt;=L49),"Да | Yes","НЕ | NO")</f>
@@ -25743,16 +25906,16 @@
         </is>
       </c>
       <c r="I50" s="13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>23.4</v>
+        <v>21.65</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>28.6</v>
+        <v>26.35</v>
       </c>
       <c r="M50" s="12">
         <f>IF(AND(C50&gt;=K50,C50&lt;=L50),"Да | Yes","НЕ | NO")</f>
@@ -25892,20 +26055,20 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I52" s="13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>15.3</v>
+        <v>18.36</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>18.7</v>
+        <v>21.64</v>
       </c>
       <c r="M52" s="12">
         <f>IF(AND(C52&gt;=K52,C52&lt;=L52),"Да | Yes","НЕ | NO")</f>
@@ -25940,10 +26103,10 @@
         <v>20</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>18</v>
+        <v>18.36</v>
       </c>
       <c r="V52" s="13" t="n">
-        <v>22</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="53">
@@ -25986,16 +26149,16 @@
         </is>
       </c>
       <c r="I53" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>18.9</v>
+        <v>18.36</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>23.1</v>
+        <v>21.64</v>
       </c>
       <c r="M53" s="14">
         <f>IF(AND(C53&gt;=K53,C53&lt;=L53),"Да | Yes","НЕ | NO")</f>
@@ -26030,10 +26193,10 @@
         <v>20</v>
       </c>
       <c r="U53" s="15" t="n">
-        <v>18</v>
+        <v>18.36</v>
       </c>
       <c r="V53" s="15" t="n">
-        <v>22</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="54">
@@ -26076,16 +26239,16 @@
         </is>
       </c>
       <c r="I54" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>18.9</v>
+        <v>18.36</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>23.1</v>
+        <v>21.64</v>
       </c>
       <c r="M54" s="12">
         <f>IF(AND(C54&gt;=K54,C54&lt;=L54),"Да | Yes","НЕ | NO")</f>
@@ -26120,10 +26283,10 @@
         <v>20</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>18</v>
+        <v>18.36</v>
       </c>
       <c r="V54" s="13" t="n">
-        <v>22</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="55">
@@ -26166,16 +26329,16 @@
         </is>
       </c>
       <c r="I55" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>18.9</v>
+        <v>18.36</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>23.1</v>
+        <v>21.64</v>
       </c>
       <c r="M55" s="14">
         <f>IF(AND(C55&gt;=K55,C55&lt;=L55),"Да | Yes","НЕ | NO")</f>
@@ -26210,10 +26373,10 @@
         <v>20</v>
       </c>
       <c r="U55" s="15" t="n">
-        <v>18</v>
+        <v>18.36</v>
       </c>
       <c r="V55" s="15" t="n">
-        <v>22</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="56">
@@ -26259,13 +26422,13 @@
         <v>17</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>15.3</v>
+        <v>15.65</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>18.7</v>
+        <v>18.35</v>
       </c>
       <c r="M56" s="12">
         <f>IF(AND(C56&gt;=K56,C56&lt;=L56),"Да | Yes","НЕ | NO")</f>
@@ -26297,13 +26460,13 @@
         </is>
       </c>
       <c r="T56" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>14.4</v>
+        <v>15.65</v>
       </c>
       <c r="V56" s="13" t="n">
-        <v>17.6</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="57">
@@ -26346,16 +26509,16 @@
         </is>
       </c>
       <c r="I57" s="15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>23.4</v>
+        <v>21.65</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>28.6</v>
+        <v>26.35</v>
       </c>
       <c r="M57" s="14">
         <f>IF(AND(C57&gt;=K57,C57&lt;=L57),"Да | Yes","НЕ | NO")</f>
@@ -26422,20 +26585,20 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>18.9</v>
+        <v>21.65</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>23.1</v>
+        <v>26.35</v>
       </c>
       <c r="M58" s="12">
         <f>IF(AND(C58&gt;=K58,C58&lt;=L58),"Да | Yes","НЕ | NO")</f>
@@ -26506,16 +26669,16 @@
         </is>
       </c>
       <c r="I59" s="15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>23.4</v>
+        <v>21.65</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>28.6</v>
+        <v>26.35</v>
       </c>
       <c r="M59" s="14">
         <f>IF(AND(C59&gt;=K59,C59&lt;=L59),"Да | Yes","НЕ | NO")</f>
@@ -26547,13 +26710,13 @@
         </is>
       </c>
       <c r="T59" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U59" s="15" t="n">
-        <v>22.5</v>
+        <v>21.65</v>
       </c>
       <c r="V59" s="15" t="n">
-        <v>27.5</v>
+        <v>26.35</v>
       </c>
     </row>
     <row r="60">
@@ -26686,16 +26849,16 @@
         </is>
       </c>
       <c r="I61" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>15.3</v>
+        <v>16.65</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>18.7</v>
+        <v>19.35</v>
       </c>
       <c r="M61" s="14">
         <f>IF(AND(C61&gt;=K61,C61&lt;=L61),"Да | Yes","НЕ | NO")</f>
@@ -26769,13 +26932,13 @@
         <v>21</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>18.9</v>
+        <v>19.36</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>23.1</v>
+        <v>22.64</v>
       </c>
       <c r="M62" s="12">
         <f>IF(AND(C62&gt;=K62,C62&lt;=L62),"Да | Yes","НЕ | NO")</f>
@@ -26859,13 +27022,13 @@
         <v>21</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>18.9</v>
+        <v>19.36</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>23.1</v>
+        <v>22.64</v>
       </c>
       <c r="M63" s="14">
         <f>IF(AND(C63&gt;=K63,C63&lt;=L63),"Да | Yes","НЕ | NO")</f>
@@ -26946,16 +27109,16 @@
         </is>
       </c>
       <c r="I64" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>15.3</v>
+        <v>16.65</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>18.7</v>
+        <v>19.35</v>
       </c>
       <c r="M64" s="12">
         <f>IF(AND(C64&gt;=K64,C64&lt;=L64),"Да | Yes","НЕ | NO")</f>
@@ -27029,13 +27192,13 @@
         <v>21</v>
       </c>
       <c r="J65" s="15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K65" s="15" t="n">
-        <v>18.9</v>
+        <v>19.36</v>
       </c>
       <c r="L65" s="15" t="n">
-        <v>23.1</v>
+        <v>22.64</v>
       </c>
       <c r="M65" s="14">
         <f>IF(AND(C65&gt;=K65,C65&lt;=L65),"Да | Yes","НЕ | NO")</f>
@@ -27116,16 +27279,16 @@
         </is>
       </c>
       <c r="I66" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>18</v>
+        <v>17.28</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>22</v>
+        <v>20.72</v>
       </c>
       <c r="M66" s="12">
         <f>IF(AND(C66&gt;=K66,C66&lt;=L66),"Да | Yes","НЕ | NO")</f>
@@ -27196,16 +27359,16 @@
         </is>
       </c>
       <c r="I67" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>18</v>
+        <v>17.28</v>
       </c>
       <c r="L67" s="15" t="n">
-        <v>22</v>
+        <v>20.72</v>
       </c>
       <c r="M67" s="14">
         <f>IF(AND(C67&gt;=K67,C67&lt;=L67),"Да | Yes","НЕ | NO")</f>
@@ -27276,16 +27439,16 @@
         </is>
       </c>
       <c r="I68" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J68" s="13" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>18</v>
+        <v>17.28</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>22</v>
+        <v>20.72</v>
       </c>
       <c r="M68" s="12">
         <f>IF(AND(C68&gt;=K68,C68&lt;=L68),"Да | Yes","НЕ | NO")</f>
@@ -27356,16 +27519,16 @@
         </is>
       </c>
       <c r="I69" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>18</v>
+        <v>17.28</v>
       </c>
       <c r="L69" s="15" t="n">
-        <v>22</v>
+        <v>20.72</v>
       </c>
       <c r="M69" s="14">
         <f>IF(AND(C69&gt;=K69,C69&lt;=L69),"Да | Yes","НЕ | NO")</f>
@@ -27436,16 +27599,16 @@
         </is>
       </c>
       <c r="I70" s="13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>18</v>
+        <v>17.28</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>22</v>
+        <v>20.72</v>
       </c>
       <c r="M70" s="12">
         <f>IF(AND(C70&gt;=K70,C70&lt;=L70),"Да | Yes","НЕ | NO")</f>
@@ -27519,13 +27682,13 @@
         <v>16</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>1.6</v>
+        <v>1.27</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>14.4</v>
+        <v>14.73</v>
       </c>
       <c r="L71" s="15" t="n">
-        <v>17.6</v>
+        <v>17.27</v>
       </c>
       <c r="M71" s="14">
         <f>IF(AND(C71&gt;=K71,C71&lt;=L71),"Да | Yes","НЕ | NO")</f>
@@ -27669,16 +27832,16 @@
         </is>
       </c>
       <c r="I73" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>15.3</v>
+        <v>16.65</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>18.7</v>
+        <v>19.35</v>
       </c>
       <c r="M73" s="14">
         <f>IF(AND(C73&gt;=K73,C73&lt;=L73),"Да | Yes","НЕ | NO")</f>
@@ -27752,13 +27915,13 @@
         <v>21</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>18.9</v>
+        <v>19.36</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>23.1</v>
+        <v>22.64</v>
       </c>
       <c r="M74" s="12">
         <f>IF(AND(C74&gt;=K74,C74&lt;=L74),"Да | Yes","НЕ | NO")</f>
@@ -27829,16 +27992,16 @@
         </is>
       </c>
       <c r="I75" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>15.3</v>
+        <v>16.65</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>18.7</v>
+        <v>19.35</v>
       </c>
       <c r="M75" s="14">
         <f>IF(AND(C75&gt;=K75,C75&lt;=L75),"Да | Yes","НЕ | NO")</f>
@@ -27912,13 +28075,13 @@
         <v>21</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>18.9</v>
+        <v>19.36</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>23.1</v>
+        <v>22.64</v>
       </c>
       <c r="M76" s="12">
         <f>IF(AND(C76&gt;=K76,C76&lt;=L76),"Да | Yes","НЕ | NO")</f>
@@ -27992,13 +28155,13 @@
         <v>21</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>18.9</v>
+        <v>19.36</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>23.1</v>
+        <v>22.64</v>
       </c>
       <c r="M77" s="14">
         <f>IF(AND(C77&gt;=K77,C77&lt;=L77),"Да | Yes","НЕ | NO")</f>
@@ -28072,13 +28235,13 @@
         <v>21</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>2.1</v>
+        <v>1.64</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>18.9</v>
+        <v>19.36</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>23.1</v>
+        <v>22.64</v>
       </c>
       <c r="M78" s="12">
         <f>IF(AND(C78&gt;=K78,C78&lt;=L78),"Да | Yes","НЕ | NO")</f>
@@ -28412,13 +28575,13 @@
         <v>8</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="M82" s="12">
         <f>IF(AND(C82&gt;=K82,C82&lt;=L82),"Да | Yes","НЕ | NO")</f>
@@ -28453,10 +28616,10 @@
         <v>8</v>
       </c>
       <c r="U82" s="13" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="V82" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="83">
@@ -28499,16 +28662,16 @@
         </is>
       </c>
       <c r="I83" s="15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>11.7</v>
+        <v>14.1</v>
       </c>
       <c r="L83" s="15" t="n">
-        <v>14.3</v>
+        <v>15.9</v>
       </c>
       <c r="M83" s="14">
         <f>IF(AND(C83&gt;=K83,C83&lt;=L83),"Да | Yes","НЕ | NO")</f>
@@ -28585,20 +28748,20 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I84" s="13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>17.6</v>
+        <v>15.9</v>
       </c>
       <c r="M84" s="12">
         <f>IF(AND(C84&gt;=K84,C84&lt;=L84),"Да | Yes","НЕ | NO")</f>
@@ -28682,13 +28845,13 @@
         <v>20</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K85" s="15" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="L85" s="15" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="M85" s="14">
         <f>IF(AND(C85&gt;=K85,C85&lt;=L85),"Да | Yes","НЕ | NO")</f>
@@ -28765,20 +28928,20 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Pot.-5</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I86" s="13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>18</v>
+        <v>15.91</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>22</v>
+        <v>18.09</v>
       </c>
       <c r="M86" s="12">
         <f>IF(AND(C86&gt;=K86,C86&lt;=L86),"Да | Yes","НЕ | NO")</f>
@@ -28862,13 +29025,13 @@
         <v>8</v>
       </c>
       <c r="J87" s="15" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="K87" s="15" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="L87" s="15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="M87" s="14">
         <f>IF(AND(C87&gt;=K87,C87&lt;=L87),"Да | Yes","НЕ | NO")</f>
@@ -28952,13 +29115,13 @@
         <v>8</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>0.8</v>
+        <v>0.33</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>7.2</v>
+        <v>7.67</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="M88" s="12">
         <f>IF(AND(C88&gt;=K88,C88&lt;=L88),"Да | Yes","НЕ | NO")</f>
@@ -29039,16 +29202,16 @@
         </is>
       </c>
       <c r="I89" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>1</v>
+        <v>0.66</v>
       </c>
       <c r="K89" s="15" t="n">
-        <v>9</v>
+        <v>8.34</v>
       </c>
       <c r="L89" s="15" t="n">
-        <v>11</v>
+        <v>9.66</v>
       </c>
       <c r="M89" s="14">
         <f>IF(AND(C89&gt;=K89,C89&lt;=L89),"Да | Yes","НЕ | NO")</f>
@@ -29080,13 +29243,13 @@
         </is>
       </c>
       <c r="T89" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U89" s="15" t="n">
-        <v>9</v>
+        <v>8.34</v>
       </c>
       <c r="V89" s="15" t="n">
-        <v>11</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="90">
@@ -29132,13 +29295,13 @@
         <v>20</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="M90" s="12">
         <f>IF(AND(C90&gt;=K90,C90&lt;=L90),"Да | Yes","НЕ | NO")</f>
@@ -29215,20 +29378,20 @@
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>Pot.-5</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I91" s="15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>18</v>
+        <v>15.91</v>
       </c>
       <c r="L91" s="15" t="n">
-        <v>22</v>
+        <v>18.09</v>
       </c>
       <c r="M91" s="14">
         <f>IF(AND(C91&gt;=K91,C91&lt;=L91),"Да | Yes","НЕ | NO")</f>
@@ -29309,16 +29472,16 @@
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>14.4</v>
+        <v>15.91</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>17.6</v>
+        <v>18.09</v>
       </c>
       <c r="M92" s="12">
         <f>IF(AND(C92&gt;=K92,C92&lt;=L92),"Да | Yes","НЕ | NO")</f>
@@ -29402,13 +29565,13 @@
         <v>13</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>11.7</v>
+        <v>12.06</v>
       </c>
       <c r="L93" s="15" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
       <c r="M93" s="14">
         <f>IF(AND(C93&gt;=K93,C93&lt;=L93),"Да | Yes","НЕ | NO")</f>
@@ -29443,10 +29606,10 @@
         <v>13</v>
       </c>
       <c r="U93" s="15" t="n">
-        <v>11.7</v>
+        <v>12.06</v>
       </c>
       <c r="V93" s="15" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="94">
@@ -29492,13 +29655,13 @@
         <v>13</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>11.7</v>
+        <v>12.06</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
       <c r="M94" s="12">
         <f>IF(AND(C94&gt;=K94,C94&lt;=L94),"Да | Yes","НЕ | NO")</f>
@@ -29533,10 +29696,10 @@
         <v>13</v>
       </c>
       <c r="U94" s="13" t="n">
-        <v>11.7</v>
+        <v>12.06</v>
       </c>
       <c r="V94" s="13" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="95">
@@ -29582,13 +29745,13 @@
         <v>13</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>1.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>11.7</v>
+        <v>12.06</v>
       </c>
       <c r="L95" s="15" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
       <c r="M95" s="14">
         <f>IF(AND(C95&gt;=K95,C95&lt;=L95),"Да | Yes","НЕ | NO")</f>
@@ -29623,10 +29786,10 @@
         <v>13</v>
       </c>
       <c r="U95" s="15" t="n">
-        <v>11.7</v>
+        <v>12.06</v>
       </c>
       <c r="V95" s="15" t="n">
-        <v>14.3</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="96">
@@ -29669,16 +29832,16 @@
         </is>
       </c>
       <c r="I96" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>9</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>11</v>
+        <v>12.05</v>
       </c>
       <c r="M96" s="12">
         <f>IF(AND(C96&gt;=K96,C96&lt;=L96),"Да | Yes","НЕ | NO")</f>
@@ -29710,13 +29873,13 @@
         </is>
       </c>
       <c r="T96" s="13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="U96" s="13" t="n">
-        <v>9</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="V96" s="13" t="n">
-        <v>11</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="97">
@@ -29849,16 +30012,16 @@
         </is>
       </c>
       <c r="I98" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J98" s="13" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="K98" s="13" t="n">
-        <v>15.3</v>
+        <v>16.21</v>
       </c>
       <c r="L98" s="13" t="n">
-        <v>18.7</v>
+        <v>19.79</v>
       </c>
       <c r="M98" s="12">
         <f>IF(AND(C98&gt;=K98,C98&lt;=L98),"Да | Yes","НЕ | NO")</f>
@@ -29929,16 +30092,16 @@
         </is>
       </c>
       <c r="I99" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="K99" s="15" t="n">
-        <v>15.3</v>
+        <v>16.21</v>
       </c>
       <c r="L99" s="15" t="n">
-        <v>18.7</v>
+        <v>19.79</v>
       </c>
       <c r="M99" s="14">
         <f>IF(AND(C99&gt;=K99,C99&lt;=L99),"Да | Yes","НЕ | NO")</f>
@@ -30009,16 +30172,16 @@
         </is>
       </c>
       <c r="I100" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>10.8</v>
+        <v>9.91</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>13.2</v>
+        <v>12.09</v>
       </c>
       <c r="M100" s="12">
         <f>IF(AND(C100&gt;=K100,C100&lt;=L100),"Да | Yes","НЕ | NO")</f>
@@ -30179,16 +30342,16 @@
         </is>
       </c>
       <c r="I102" s="13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>10.8</v>
+        <v>9.91</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>13.2</v>
+        <v>12.09</v>
       </c>
       <c r="M102" s="12">
         <f>IF(AND(C102&gt;=K102,C102&lt;=L102),"Да | Yes","НЕ | NO")</f>

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -17942,13 +17942,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>18.2</v>
+        <v>18.41</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>21.8</v>
+        <v>21.59</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>1</v>
@@ -17980,13 +17980,13 @@
         <v>24</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>21.81</v>
+        <v>21.6</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>26.19</v>
+        <v>26.4</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>2</v>
@@ -18018,13 +18018,13 @@
         <v>16</v>
       </c>
       <c r="D11" s="15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>1</v>
@@ -18056,13 +18056,13 @@
         <v>19</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>17.21</v>
+        <v>17.31</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>20.79</v>
+        <v>20.69</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>2</v>
@@ -18094,13 +18094,13 @@
         <v>23</v>
       </c>
       <c r="D13" s="15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>6</v>
@@ -18132,13 +18132,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.64</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>11.36</v>
+        <v>11.3</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>12.64</v>
+        <v>12.7</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>1</v>
@@ -18170,13 +18170,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>12.65</v>
+        <v>12.71</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>15.35</v>
+        <v>15.29</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>1</v>
@@ -18208,13 +18208,13 @@
         <v>17</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>15.36</v>
+        <v>15.3</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>18.64</v>
+        <v>18.7</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
@@ -18322,13 +18322,13 @@
         <v>15</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>13.65</v>
+        <v>13.5</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>16.35</v>
+        <v>16.5</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>1</v>
@@ -18360,13 +18360,13 @@
         <v>18</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>16.36</v>
+        <v>16.51</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>19.64</v>
+        <v>19.49</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
@@ -18398,13 +18398,13 @@
         <v>21</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>19.65</v>
+        <v>19.5</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>22.35</v>
+        <v>22.5</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>1</v>
@@ -18436,13 +18436,13 @@
         <v>14</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>12.7</v>
+        <v>12.71</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>15.3</v>
+        <v>15.29</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>1</v>
@@ -18474,13 +18474,13 @@
         <v>17</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>5</v>
@@ -18512,13 +18512,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>15.65</v>
+        <v>15.6</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>18.35</v>
+        <v>18.4</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>1</v>
@@ -18550,13 +18550,13 @@
         <v>20</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>4</v>
@@ -18588,13 +18588,13 @@
         <v>24</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>4</v>
@@ -18706,13 +18706,13 @@
         <v>18</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.35</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>16.65</v>
+        <v>17.11</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>19.35</v>
+        <v>18.89</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>1</v>
@@ -18744,13 +18744,13 @@
         <v>21</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>2</v>
@@ -18782,13 +18782,13 @@
         <v>16</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>14.73</v>
+        <v>14.91</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>17.27</v>
+        <v>17.09</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>2</v>
@@ -18820,13 +18820,13 @@
         <v>19</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>17.28</v>
+        <v>17.1</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>20.72</v>
+        <v>20.9</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>3</v>
@@ -18858,13 +18858,13 @@
         <v>18</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>1.35</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>16.65</v>
+        <v>17.11</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>19.35</v>
+        <v>18.89</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>1</v>
@@ -18896,13 +18896,13 @@
         <v>21</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>2</v>
@@ -19010,13 +19010,13 @@
         <v>8</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>7.67</v>
+        <v>7.91</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>2</v>
@@ -19048,13 +19048,13 @@
         <v>9</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>8.34</v>
+        <v>8.1</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>9.66</v>
+        <v>9.9</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>1</v>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>НЕМА КЛАСА 9.66%–14.10% | NO GRADE 9.66%–14.10%</t>
+          <t>НЕМА КЛАСА 9.90%–14.05% | NO GRADE 9.90%–14.05%</t>
         </is>
       </c>
     </row>
@@ -19090,13 +19090,13 @@
         <v>15</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>0.9</v>
+        <v>0.9500000000000008</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>14.1</v>
+        <v>14.05</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>15.9</v>
+        <v>15.95</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>2</v>
@@ -19128,13 +19128,13 @@
         <v>17</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>15.91</v>
+        <v>15.96</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>18.09</v>
+        <v>18.04</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>2</v>
@@ -19166,13 +19166,13 @@
         <v>20</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>18.1</v>
+        <v>18.05</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>21.9</v>
+        <v>21.95</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
@@ -19204,13 +19204,13 @@
         <v>11</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>1.05</v>
+        <v>0.9900000000000002</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>9.949999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>12.05</v>
+        <v>11.99</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>1</v>
@@ -19242,13 +19242,13 @@
         <v>13</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>2</v>
@@ -19394,13 +19394,13 @@
         <v>9</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>8.1</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>1</v>
@@ -19432,13 +19432,13 @@
         <v>11</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>12.09</v>
+        <v>12.1</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>2</v>
@@ -20004,13 +20004,13 @@
         <v>19</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>17.2</v>
+        <v>17.31</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>20.8</v>
+        <v>20.69</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>1</v>
@@ -20047,13 +20047,13 @@
         <v>23</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>20.81</v>
+        <v>20.7</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>25.19</v>
+        <v>25.3</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>5</v>
@@ -20090,13 +20090,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>13.65</v>
+        <v>13.5</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>16.35</v>
+        <v>16.5</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
@@ -20133,13 +20133,13 @@
         <v>18</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>16.36</v>
+        <v>16.51</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>19.64</v>
+        <v>19.49</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>1</v>
@@ -20176,13 +20176,13 @@
         <v>21</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>19.65</v>
+        <v>19.5</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>22.35</v>
+        <v>22.5</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>1</v>
@@ -20262,13 +20262,13 @@
         <v>11</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1.05</v>
+        <v>0.9900000000000002</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>9.949999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>12.05</v>
+        <v>11.99</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>1</v>
@@ -20305,13 +20305,13 @@
         <v>13</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>2</v>
@@ -20391,13 +20391,13 @@
         <v>14</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>12.7</v>
+        <v>12.71</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.3</v>
+        <v>15.29</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>1</v>
@@ -20434,13 +20434,13 @@
         <v>17</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>2</v>
@@ -20606,13 +20606,13 @@
         <v>16</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>14.73</v>
+        <v>14.91</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>17.27</v>
+        <v>17.09</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>1</v>
@@ -20649,13 +20649,13 @@
         <v>19</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>17.28</v>
+        <v>17.1</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>20.72</v>
+        <v>20.9</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>3</v>
@@ -20692,13 +20692,13 @@
         <v>18</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>1.35</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>16.65</v>
+        <v>17.11</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>19.35</v>
+        <v>18.89</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>1</v>
@@ -20735,13 +20735,13 @@
         <v>21</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>2</v>
@@ -21079,13 +21079,13 @@
         <v>12</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>0.64</v>
+        <v>0.6999999999999997</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>11.36</v>
+        <v>11.3</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>12.64</v>
+        <v>12.7</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1</v>
@@ -21122,13 +21122,13 @@
         <v>14</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>12.65</v>
+        <v>12.71</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>15.35</v>
+        <v>15.29</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>1</v>
@@ -21165,13 +21165,13 @@
         <v>17</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>15.36</v>
+        <v>15.3</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>18.64</v>
+        <v>18.7</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
@@ -21470,13 +21470,13 @@
         <v>8</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>7.67</v>
+        <v>7.91</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
@@ -21513,13 +21513,13 @@
         <v>9</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>8.34</v>
+        <v>8.1</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>9.66</v>
+        <v>9.9</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>1</v>
@@ -21599,13 +21599,13 @@
         <v>20</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>18.2</v>
+        <v>18.41</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>21.8</v>
+        <v>21.59</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>1</v>
@@ -21642,13 +21642,13 @@
         <v>24</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>21.81</v>
+        <v>21.6</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>26.19</v>
+        <v>26.4</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>2</v>
@@ -21771,13 +21771,13 @@
         <v>17</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>15.65</v>
+        <v>15.6</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>18.35</v>
+        <v>18.4</v>
       </c>
       <c r="G55" s="14" t="n">
         <v>1</v>
@@ -21814,13 +21814,13 @@
         <v>20</v>
       </c>
       <c r="D56" s="13" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="E56" s="13" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="F56" s="13" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
       <c r="G56" s="12" t="n">
         <v>4</v>
@@ -21857,13 +21857,13 @@
         <v>24</v>
       </c>
       <c r="D57" s="15" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="F57" s="15" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="G57" s="14" t="n">
         <v>1</v>
@@ -22387,13 +22387,13 @@
         <v>24</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>21.81</v>
+        <v>21.6</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>26.19</v>
+        <v>26.4</v>
       </c>
       <c r="M9" s="14">
         <f>IF(AND(C9&gt;=K9,C9&lt;=L9),"Да | Yes","НЕ | NO")</f>
@@ -22428,10 +22428,10 @@
         <v>24</v>
       </c>
       <c r="U9" s="15" t="n">
-        <v>21.81</v>
+        <v>21.6</v>
       </c>
       <c r="V9" s="15" t="n">
-        <v>26.19</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="10">
@@ -22550,13 +22550,13 @@
         <v>24</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>21.81</v>
+        <v>21.6</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>26.19</v>
+        <v>26.4</v>
       </c>
       <c r="M11" s="14">
         <f>IF(AND(C11&gt;=K11,C11&lt;=L11),"Да | Yes","НЕ | NO")</f>
@@ -22591,10 +22591,10 @@
         <v>24</v>
       </c>
       <c r="U11" s="15" t="n">
-        <v>21.81</v>
+        <v>21.6</v>
       </c>
       <c r="V11" s="15" t="n">
-        <v>26.19</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="12">
@@ -22640,13 +22640,13 @@
         <v>20</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>18.2</v>
+        <v>18.41</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>21.8</v>
+        <v>21.59</v>
       </c>
       <c r="M12" s="12">
         <f>IF(AND(C12&gt;=K12,C12&lt;=L12),"Да | Yes","НЕ | NO")</f>
@@ -22681,10 +22681,10 @@
         <v>20</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>18.2</v>
+        <v>18.41</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>21.8</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="13">
@@ -22730,13 +22730,13 @@
         <v>23</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L13" s="15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="M13" s="14">
         <f>IF(AND(C13&gt;=K13,C13&lt;=L13),"Да | Yes","НЕ | NO")</f>
@@ -22771,10 +22771,10 @@
         <v>23</v>
       </c>
       <c r="U13" s="15" t="n">
-        <v>20.81</v>
+        <v>20.7</v>
       </c>
       <c r="V13" s="15" t="n">
-        <v>25.19</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="14">
@@ -22820,13 +22820,13 @@
         <v>19</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>17.21</v>
+        <v>17.31</v>
       </c>
       <c r="L14" s="13" t="n">
-        <v>20.79</v>
+        <v>20.69</v>
       </c>
       <c r="M14" s="12">
         <f>IF(AND(C14&gt;=K14,C14&lt;=L14),"Да | Yes","НЕ | NO")</f>
@@ -22910,13 +22910,13 @@
         <v>19</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>17.21</v>
+        <v>17.31</v>
       </c>
       <c r="L15" s="15" t="n">
-        <v>20.79</v>
+        <v>20.69</v>
       </c>
       <c r="M15" s="14">
         <f>IF(AND(C15&gt;=K15,C15&lt;=L15),"Да | Yes","НЕ | NO")</f>
@@ -22951,10 +22951,10 @@
         <v>19</v>
       </c>
       <c r="U15" s="15" t="n">
-        <v>17.2</v>
+        <v>17.31</v>
       </c>
       <c r="V15" s="15" t="n">
-        <v>20.8</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="16">
@@ -23000,13 +23000,13 @@
         <v>23</v>
       </c>
       <c r="J16" s="13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L16" s="13" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="M16" s="12">
         <f>IF(AND(C16&gt;=K16,C16&lt;=L16),"Да | Yes","НЕ | NO")</f>
@@ -23041,10 +23041,10 @@
         <v>23</v>
       </c>
       <c r="U16" s="13" t="n">
-        <v>20.81</v>
+        <v>20.7</v>
       </c>
       <c r="V16" s="13" t="n">
-        <v>25.19</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="17">
@@ -23090,13 +23090,13 @@
         <v>16</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="L17" s="15" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="M17" s="14">
         <f>IF(AND(C17&gt;=K17,C17&lt;=L17),"Да | Yes","НЕ | NO")</f>
@@ -23180,13 +23180,13 @@
         <v>23</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L18" s="13" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="M18" s="12">
         <f>IF(AND(C18&gt;=K18,C18&lt;=L18),"Да | Yes","НЕ | NO")</f>
@@ -23221,10 +23221,10 @@
         <v>23</v>
       </c>
       <c r="U18" s="13" t="n">
-        <v>20.81</v>
+        <v>20.7</v>
       </c>
       <c r="V18" s="13" t="n">
-        <v>25.19</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="19">
@@ -23270,13 +23270,13 @@
         <v>19</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>17.21</v>
+        <v>17.31</v>
       </c>
       <c r="L19" s="15" t="n">
-        <v>20.79</v>
+        <v>20.69</v>
       </c>
       <c r="M19" s="14">
         <f>IF(AND(C19&gt;=K19,C19&lt;=L19),"Да | Yes","НЕ | NO")</f>
@@ -23311,10 +23311,10 @@
         <v>19</v>
       </c>
       <c r="U19" s="15" t="n">
-        <v>17.2</v>
+        <v>17.31</v>
       </c>
       <c r="V19" s="15" t="n">
-        <v>20.8</v>
+        <v>20.69</v>
       </c>
     </row>
     <row r="20">
@@ -23360,13 +23360,13 @@
         <v>23</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L20" s="13" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="M20" s="12">
         <f>IF(AND(C20&gt;=K20,C20&lt;=L20),"Да | Yes","НЕ | NO")</f>
@@ -23401,10 +23401,10 @@
         <v>23</v>
       </c>
       <c r="U20" s="13" t="n">
-        <v>20.81</v>
+        <v>20.7</v>
       </c>
       <c r="V20" s="13" t="n">
-        <v>25.19</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="21">
@@ -23450,13 +23450,13 @@
         <v>23</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K21" s="15" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L21" s="15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="M21" s="14">
         <f>IF(AND(C21&gt;=K21,C21&lt;=L21),"Да | Yes","НЕ | NO")</f>
@@ -23540,13 +23540,13 @@
         <v>19</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>17.21</v>
+        <v>17.31</v>
       </c>
       <c r="L22" s="13" t="n">
-        <v>20.79</v>
+        <v>20.69</v>
       </c>
       <c r="M22" s="12">
         <f>IF(AND(C22&gt;=K22,C22&lt;=L22),"Да | Yes","НЕ | NO")</f>
@@ -23630,13 +23630,13 @@
         <v>23</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K23" s="15" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L23" s="15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="M23" s="14">
         <f>IF(AND(C23&gt;=K23,C23&lt;=L23),"Да | Yes","НЕ | NO")</f>
@@ -23671,10 +23671,10 @@
         <v>23</v>
       </c>
       <c r="U23" s="15" t="n">
-        <v>20.81</v>
+        <v>20.7</v>
       </c>
       <c r="V23" s="15" t="n">
-        <v>25.19</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="24">
@@ -23720,13 +23720,13 @@
         <v>23</v>
       </c>
       <c r="J24" s="13" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L24" s="13" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="M24" s="12">
         <f>IF(AND(C24&gt;=K24,C24&lt;=L24),"Да | Yes","НЕ | NO")</f>
@@ -23761,10 +23761,10 @@
         <v>23</v>
       </c>
       <c r="U24" s="13" t="n">
-        <v>20.81</v>
+        <v>20.7</v>
       </c>
       <c r="V24" s="13" t="n">
-        <v>25.19</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="25">
@@ -23810,13 +23810,13 @@
         <v>17</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>15.36</v>
+        <v>15.3</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>18.64</v>
+        <v>18.7</v>
       </c>
       <c r="M25" s="14">
         <f>IF(AND(C25&gt;=K25,C25&lt;=L25),"Да | Yes","НЕ | NO")</f>
@@ -23851,10 +23851,10 @@
         <v>17</v>
       </c>
       <c r="U25" s="15" t="n">
-        <v>15.36</v>
+        <v>15.3</v>
       </c>
       <c r="V25" s="15" t="n">
-        <v>18.64</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="26">
@@ -23900,13 +23900,13 @@
         <v>14</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>12.65</v>
+        <v>12.71</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>15.35</v>
+        <v>15.29</v>
       </c>
       <c r="M26" s="12">
         <f>IF(AND(C26&gt;=K26,C26&lt;=L26),"Да | Yes","НЕ | NO")</f>
@@ -23938,10 +23938,10 @@
         <v>14</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>12.65</v>
+        <v>12.71</v>
       </c>
       <c r="V26" s="13" t="n">
-        <v>15.35</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="27">
@@ -24067,13 +24067,13 @@
         <v>18</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>16.36</v>
+        <v>16.51</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>19.64</v>
+        <v>19.49</v>
       </c>
       <c r="M28" s="12">
         <f>IF(AND(C28&gt;=K28,C28&lt;=L28),"Да | Yes","НЕ | NO")</f>
@@ -24157,13 +24157,13 @@
         <v>18</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>16.36</v>
+        <v>16.51</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>19.64</v>
+        <v>19.49</v>
       </c>
       <c r="M29" s="14">
         <f>IF(AND(C29&gt;=K29,C29&lt;=L29),"Да | Yes","НЕ | NO")</f>
@@ -24247,13 +24247,13 @@
         <v>15</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>13.65</v>
+        <v>13.5</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>16.35</v>
+        <v>16.5</v>
       </c>
       <c r="M30" s="12">
         <f>IF(AND(C30&gt;=K30,C30&lt;=L30),"Да | Yes","НЕ | NO")</f>
@@ -24288,10 +24288,10 @@
         <v>15</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>13.65</v>
+        <v>13.5</v>
       </c>
       <c r="V30" s="13" t="n">
-        <v>16.35</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="31">
@@ -24407,13 +24407,13 @@
         <v>21</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>19.65</v>
+        <v>19.5</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>22.35</v>
+        <v>22.5</v>
       </c>
       <c r="M32" s="12">
         <f>IF(AND(C32&gt;=K32,C32&lt;=L32),"Да | Yes","НЕ | NO")</f>
@@ -24448,10 +24448,10 @@
         <v>21</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>19.65</v>
+        <v>19.5</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>22.35</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="33">
@@ -24497,13 +24497,13 @@
         <v>18</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>1.64</v>
+        <v>1.49</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>16.36</v>
+        <v>16.51</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>19.64</v>
+        <v>19.49</v>
       </c>
       <c r="M33" s="14">
         <f>IF(AND(C33&gt;=K33,C33&lt;=L33),"Да | Yes","НЕ | NO")</f>
@@ -24538,10 +24538,10 @@
         <v>18</v>
       </c>
       <c r="U33" s="15" t="n">
-        <v>16.36</v>
+        <v>16.51</v>
       </c>
       <c r="V33" s="15" t="n">
-        <v>19.64</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="34">
@@ -24587,13 +24587,13 @@
         <v>17</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="M34" s="12">
         <f>IF(AND(C34&gt;=K34,C34&lt;=L34),"Да | Yes","НЕ | NO")</f>
@@ -24628,10 +24628,10 @@
         <v>17</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="V34" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="35">
@@ -24677,13 +24677,13 @@
         <v>17</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="M35" s="14">
         <f>IF(AND(C35&gt;=K35,C35&lt;=L35),"Да | Yes","НЕ | NO")</f>
@@ -24757,13 +24757,13 @@
         <v>17</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="M36" s="12">
         <f>IF(AND(C36&gt;=K36,C36&lt;=L36),"Да | Yes","НЕ | NO")</f>
@@ -24847,13 +24847,13 @@
         <v>17</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="M37" s="14">
         <f>IF(AND(C37&gt;=K37,C37&lt;=L37),"Да | Yes","НЕ | NO")</f>
@@ -24927,13 +24927,13 @@
         <v>17</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="M38" s="12">
         <f>IF(AND(C38&gt;=K38,C38&lt;=L38),"Да | Yes","НЕ | NO")</f>
@@ -24968,10 +24968,10 @@
         <v>17</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="39">
@@ -25090,13 +25090,13 @@
         <v>17</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="M40" s="12">
         <f>IF(AND(C40&gt;=K40,C40&lt;=L40),"Да | Yes","НЕ | NO")</f>
@@ -25131,10 +25131,10 @@
         <v>17</v>
       </c>
       <c r="U40" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="V40" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="41">
@@ -25180,13 +25180,13 @@
         <v>14</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>12.7</v>
+        <v>12.71</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>15.3</v>
+        <v>15.29</v>
       </c>
       <c r="M41" s="14">
         <f>IF(AND(C41&gt;=K41,C41&lt;=L41),"Да | Yes","НЕ | NO")</f>
@@ -25221,10 +25221,10 @@
         <v>14</v>
       </c>
       <c r="U41" s="15" t="n">
-        <v>12.7</v>
+        <v>12.71</v>
       </c>
       <c r="V41" s="15" t="n">
-        <v>15.3</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="42">
@@ -25270,13 +25270,13 @@
         <v>17</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>15.31</v>
+        <v>15.3</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>18.69</v>
+        <v>18.7</v>
       </c>
       <c r="M42" s="12">
         <f>IF(AND(C42&gt;=K42,C42&lt;=L42),"Да | Yes","НЕ | NO")</f>
@@ -25569,13 +25569,13 @@
         <v>24</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="M46" s="12">
         <f>IF(AND(C46&gt;=K46,C46&lt;=L46),"Да | Yes","НЕ | NO")</f>
@@ -25649,13 +25649,13 @@
         <v>20</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
       <c r="M47" s="14">
         <f>IF(AND(C47&gt;=K47,C47&lt;=L47),"Да | Yes","НЕ | NO")</f>
@@ -25690,10 +25690,10 @@
         <v>20</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="48">
@@ -25739,13 +25739,13 @@
         <v>17</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>15.65</v>
+        <v>15.6</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>18.35</v>
+        <v>18.4</v>
       </c>
       <c r="M48" s="12">
         <f>IF(AND(C48&gt;=K48,C48&lt;=L48),"Да | Yes","НЕ | NO")</f>
@@ -25780,10 +25780,10 @@
         <v>17</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>15.65</v>
+        <v>15.6</v>
       </c>
       <c r="V48" s="13" t="n">
-        <v>18.35</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="49">
@@ -25829,13 +25829,13 @@
         <v>24</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="M49" s="14">
         <f>IF(AND(C49&gt;=K49,C49&lt;=L49),"Да | Yes","НЕ | NO")</f>
@@ -25909,13 +25909,13 @@
         <v>24</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="M50" s="12">
         <f>IF(AND(C50&gt;=K50,C50&lt;=L50),"Да | Yes","НЕ | NO")</f>
@@ -26062,13 +26062,13 @@
         <v>20</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
       <c r="M52" s="12">
         <f>IF(AND(C52&gt;=K52,C52&lt;=L52),"Да | Yes","НЕ | NO")</f>
@@ -26103,10 +26103,10 @@
         <v>20</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="V52" s="13" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="53">
@@ -26152,13 +26152,13 @@
         <v>20</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
       <c r="M53" s="14">
         <f>IF(AND(C53&gt;=K53,C53&lt;=L53),"Да | Yes","НЕ | NO")</f>
@@ -26193,10 +26193,10 @@
         <v>20</v>
       </c>
       <c r="U53" s="15" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="V53" s="15" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="54">
@@ -26242,13 +26242,13 @@
         <v>20</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
       <c r="M54" s="12">
         <f>IF(AND(C54&gt;=K54,C54&lt;=L54),"Да | Yes","НЕ | NO")</f>
@@ -26283,10 +26283,10 @@
         <v>20</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="V54" s="13" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="55">
@@ -26332,13 +26332,13 @@
         <v>20</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
       <c r="M55" s="14">
         <f>IF(AND(C55&gt;=K55,C55&lt;=L55),"Да | Yes","НЕ | NO")</f>
@@ -26373,10 +26373,10 @@
         <v>20</v>
       </c>
       <c r="U55" s="15" t="n">
-        <v>18.36</v>
+        <v>18.41</v>
       </c>
       <c r="V55" s="15" t="n">
-        <v>21.64</v>
+        <v>21.59</v>
       </c>
     </row>
     <row r="56">
@@ -26422,13 +26422,13 @@
         <v>17</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>15.65</v>
+        <v>15.6</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>18.35</v>
+        <v>18.4</v>
       </c>
       <c r="M56" s="12">
         <f>IF(AND(C56&gt;=K56,C56&lt;=L56),"Да | Yes","НЕ | NO")</f>
@@ -26463,10 +26463,10 @@
         <v>17</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>15.65</v>
+        <v>15.6</v>
       </c>
       <c r="V56" s="13" t="n">
-        <v>18.35</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="57">
@@ -26512,13 +26512,13 @@
         <v>24</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="M57" s="14">
         <f>IF(AND(C57&gt;=K57,C57&lt;=L57),"Да | Yes","НЕ | NO")</f>
@@ -26592,13 +26592,13 @@
         <v>24</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="M58" s="12">
         <f>IF(AND(C58&gt;=K58,C58&lt;=L58),"Да | Yes","НЕ | NO")</f>
@@ -26672,13 +26672,13 @@
         <v>24</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
       <c r="M59" s="14">
         <f>IF(AND(C59&gt;=K59,C59&lt;=L59),"Да | Yes","НЕ | NO")</f>
@@ -26713,10 +26713,10 @@
         <v>24</v>
       </c>
       <c r="U59" s="15" t="n">
-        <v>21.65</v>
+        <v>21.6</v>
       </c>
       <c r="V59" s="15" t="n">
-        <v>26.35</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="60">
@@ -26852,13 +26852,13 @@
         <v>18</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>1.35</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>16.65</v>
+        <v>17.11</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>19.35</v>
+        <v>18.89</v>
       </c>
       <c r="M61" s="14">
         <f>IF(AND(C61&gt;=K61,C61&lt;=L61),"Да | Yes","НЕ | NO")</f>
@@ -26932,13 +26932,13 @@
         <v>21</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="M62" s="12">
         <f>IF(AND(C62&gt;=K62,C62&lt;=L62),"Да | Yes","НЕ | NO")</f>
@@ -27022,13 +27022,13 @@
         <v>21</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="M63" s="14">
         <f>IF(AND(C63&gt;=K63,C63&lt;=L63),"Да | Yes","НЕ | NO")</f>
@@ -27112,13 +27112,13 @@
         <v>18</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>1.35</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>16.65</v>
+        <v>17.11</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>19.35</v>
+        <v>18.89</v>
       </c>
       <c r="M64" s="12">
         <f>IF(AND(C64&gt;=K64,C64&lt;=L64),"Да | Yes","НЕ | NO")</f>
@@ -27192,13 +27192,13 @@
         <v>21</v>
       </c>
       <c r="J65" s="15" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="K65" s="15" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="L65" s="15" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="M65" s="14">
         <f>IF(AND(C65&gt;=K65,C65&lt;=L65),"Да | Yes","НЕ | NO")</f>
@@ -27282,13 +27282,13 @@
         <v>19</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>17.28</v>
+        <v>17.1</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>20.72</v>
+        <v>20.9</v>
       </c>
       <c r="M66" s="12">
         <f>IF(AND(C66&gt;=K66,C66&lt;=L66),"Да | Yes","НЕ | NO")</f>
@@ -27362,13 +27362,13 @@
         <v>19</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>17.28</v>
+        <v>17.1</v>
       </c>
       <c r="L67" s="15" t="n">
-        <v>20.72</v>
+        <v>20.9</v>
       </c>
       <c r="M67" s="14">
         <f>IF(AND(C67&gt;=K67,C67&lt;=L67),"Да | Yes","НЕ | NO")</f>
@@ -27442,13 +27442,13 @@
         <v>19</v>
       </c>
       <c r="J68" s="13" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>17.28</v>
+        <v>17.1</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>20.72</v>
+        <v>20.9</v>
       </c>
       <c r="M68" s="12">
         <f>IF(AND(C68&gt;=K68,C68&lt;=L68),"Да | Yes","НЕ | NO")</f>
@@ -27522,13 +27522,13 @@
         <v>19</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>17.28</v>
+        <v>17.1</v>
       </c>
       <c r="L69" s="15" t="n">
-        <v>20.72</v>
+        <v>20.9</v>
       </c>
       <c r="M69" s="14">
         <f>IF(AND(C69&gt;=K69,C69&lt;=L69),"Да | Yes","НЕ | NO")</f>
@@ -27602,13 +27602,13 @@
         <v>19</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>17.28</v>
+        <v>17.1</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>20.72</v>
+        <v>20.9</v>
       </c>
       <c r="M70" s="12">
         <f>IF(AND(C70&gt;=K70,C70&lt;=L70),"Да | Yes","НЕ | NO")</f>
@@ -27682,13 +27682,13 @@
         <v>16</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>1.27</v>
+        <v>1.09</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>14.73</v>
+        <v>14.91</v>
       </c>
       <c r="L71" s="15" t="n">
-        <v>17.27</v>
+        <v>17.09</v>
       </c>
       <c r="M71" s="14">
         <f>IF(AND(C71&gt;=K71,C71&lt;=L71),"Да | Yes","НЕ | NO")</f>
@@ -27835,13 +27835,13 @@
         <v>18</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>1.35</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>16.65</v>
+        <v>17.11</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>19.35</v>
+        <v>18.89</v>
       </c>
       <c r="M73" s="14">
         <f>IF(AND(C73&gt;=K73,C73&lt;=L73),"Да | Yes","НЕ | NO")</f>
@@ -27915,13 +27915,13 @@
         <v>21</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="M74" s="12">
         <f>IF(AND(C74&gt;=K74,C74&lt;=L74),"Да | Yes","НЕ | NO")</f>
@@ -27995,13 +27995,13 @@
         <v>18</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>1.35</v>
+        <v>0.8900000000000001</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>16.65</v>
+        <v>17.11</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>19.35</v>
+        <v>18.89</v>
       </c>
       <c r="M75" s="14">
         <f>IF(AND(C75&gt;=K75,C75&lt;=L75),"Да | Yes","НЕ | NO")</f>
@@ -28075,13 +28075,13 @@
         <v>21</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="M76" s="12">
         <f>IF(AND(C76&gt;=K76,C76&lt;=L76),"Да | Yes","НЕ | NO")</f>
@@ -28155,13 +28155,13 @@
         <v>21</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="M77" s="14">
         <f>IF(AND(C77&gt;=K77,C77&lt;=L77),"Да | Yes","НЕ | NO")</f>
@@ -28235,13 +28235,13 @@
         <v>21</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>19.36</v>
+        <v>18.9</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>22.64</v>
+        <v>23.1</v>
       </c>
       <c r="M78" s="12">
         <f>IF(AND(C78&gt;=K78,C78&lt;=L78),"Да | Yes","НЕ | NO")</f>
@@ -28575,13 +28575,13 @@
         <v>8</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>7.67</v>
+        <v>7.91</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
       <c r="M82" s="12">
         <f>IF(AND(C82&gt;=K82,C82&lt;=L82),"Да | Yes","НЕ | NO")</f>
@@ -28616,10 +28616,10 @@
         <v>8</v>
       </c>
       <c r="U82" s="13" t="n">
-        <v>7.67</v>
+        <v>7.91</v>
       </c>
       <c r="V82" s="13" t="n">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="83">
@@ -28665,13 +28665,13 @@
         <v>15</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0.9</v>
+        <v>0.9500000000000008</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>14.1</v>
+        <v>14.05</v>
       </c>
       <c r="L83" s="15" t="n">
-        <v>15.9</v>
+        <v>15.95</v>
       </c>
       <c r="M83" s="14">
         <f>IF(AND(C83&gt;=K83,C83&lt;=L83),"Да | Yes","НЕ | NO")</f>
@@ -28755,13 +28755,13 @@
         <v>15</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>0.9</v>
+        <v>0.9500000000000008</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>14.1</v>
+        <v>14.05</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>15.9</v>
+        <v>15.95</v>
       </c>
       <c r="M84" s="12">
         <f>IF(AND(C84&gt;=K84,C84&lt;=L84),"Да | Yes","НЕ | NO")</f>
@@ -28845,13 +28845,13 @@
         <v>20</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="K85" s="15" t="n">
-        <v>18.1</v>
+        <v>18.05</v>
       </c>
       <c r="L85" s="15" t="n">
-        <v>21.9</v>
+        <v>21.95</v>
       </c>
       <c r="M85" s="14">
         <f>IF(AND(C85&gt;=K85,C85&lt;=L85),"Да | Yes","НЕ | NO")</f>
@@ -28935,13 +28935,13 @@
         <v>17</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>15.91</v>
+        <v>15.96</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>18.09</v>
+        <v>18.04</v>
       </c>
       <c r="M86" s="12">
         <f>IF(AND(C86&gt;=K86,C86&lt;=L86),"Да | Yes","НЕ | NO")</f>
@@ -29025,13 +29025,13 @@
         <v>8</v>
       </c>
       <c r="J87" s="15" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="K87" s="15" t="n">
-        <v>7.67</v>
+        <v>7.91</v>
       </c>
       <c r="L87" s="15" t="n">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
       <c r="M87" s="14">
         <f>IF(AND(C87&gt;=K87,C87&lt;=L87),"Да | Yes","НЕ | NO")</f>
@@ -29115,13 +29115,13 @@
         <v>8</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>0.33</v>
+        <v>0.09</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>7.67</v>
+        <v>7.91</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
       <c r="M88" s="12">
         <f>IF(AND(C88&gt;=K88,C88&lt;=L88),"Да | Yes","НЕ | NO")</f>
@@ -29205,13 +29205,13 @@
         <v>9</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="K89" s="15" t="n">
-        <v>8.34</v>
+        <v>8.1</v>
       </c>
       <c r="L89" s="15" t="n">
-        <v>9.66</v>
+        <v>9.9</v>
       </c>
       <c r="M89" s="14">
         <f>IF(AND(C89&gt;=K89,C89&lt;=L89),"Да | Yes","НЕ | NO")</f>
@@ -29246,10 +29246,10 @@
         <v>9</v>
       </c>
       <c r="U89" s="15" t="n">
-        <v>8.34</v>
+        <v>8.1</v>
       </c>
       <c r="V89" s="15" t="n">
-        <v>9.66</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="90">
@@ -29295,13 +29295,13 @@
         <v>20</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>18.1</v>
+        <v>18.05</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>21.9</v>
+        <v>21.95</v>
       </c>
       <c r="M90" s="12">
         <f>IF(AND(C90&gt;=K90,C90&lt;=L90),"Да | Yes","НЕ | NO")</f>
@@ -29385,13 +29385,13 @@
         <v>17</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>15.91</v>
+        <v>15.96</v>
       </c>
       <c r="L91" s="15" t="n">
-        <v>18.09</v>
+        <v>18.04</v>
       </c>
       <c r="M91" s="14">
         <f>IF(AND(C91&gt;=K91,C91&lt;=L91),"Да | Yes","НЕ | NO")</f>
@@ -29475,13 +29475,13 @@
         <v>17</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>15.91</v>
+        <v>15.96</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>18.09</v>
+        <v>18.04</v>
       </c>
       <c r="M92" s="12">
         <f>IF(AND(C92&gt;=K92,C92&lt;=L92),"Да | Yes","НЕ | NO")</f>
@@ -29565,13 +29565,13 @@
         <v>13</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="L93" s="15" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
       <c r="M93" s="14">
         <f>IF(AND(C93&gt;=K93,C93&lt;=L93),"Да | Yes","НЕ | NO")</f>
@@ -29606,10 +29606,10 @@
         <v>13</v>
       </c>
       <c r="U93" s="15" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="V93" s="15" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
@@ -29655,13 +29655,13 @@
         <v>13</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
       <c r="M94" s="12">
         <f>IF(AND(C94&gt;=K94,C94&lt;=L94),"Да | Yes","НЕ | NO")</f>
@@ -29696,10 +29696,10 @@
         <v>13</v>
       </c>
       <c r="U94" s="13" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="V94" s="13" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
@@ -29745,13 +29745,13 @@
         <v>13</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="L95" s="15" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
       <c r="M95" s="14">
         <f>IF(AND(C95&gt;=K95,C95&lt;=L95),"Да | Yes","НЕ | NO")</f>
@@ -29786,10 +29786,10 @@
         <v>13</v>
       </c>
       <c r="U95" s="15" t="n">
-        <v>12.06</v>
+        <v>12</v>
       </c>
       <c r="V95" s="15" t="n">
-        <v>13.94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
@@ -29835,13 +29835,13 @@
         <v>11</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>1.05</v>
+        <v>0.9900000000000002</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>9.949999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>12.05</v>
+        <v>11.99</v>
       </c>
       <c r="M96" s="12">
         <f>IF(AND(C96&gt;=K96,C96&lt;=L96),"Да | Yes","НЕ | NO")</f>
@@ -29876,10 +29876,10 @@
         <v>11</v>
       </c>
       <c r="U96" s="13" t="n">
-        <v>9.949999999999999</v>
+        <v>10.01</v>
       </c>
       <c r="V96" s="13" t="n">
-        <v>12.05</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="97">
@@ -30175,13 +30175,13 @@
         <v>11</v>
       </c>
       <c r="J100" s="13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K100" s="13" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
       <c r="L100" s="13" t="n">
-        <v>12.09</v>
+        <v>12.1</v>
       </c>
       <c r="M100" s="12">
         <f>IF(AND(C100&gt;=K100,C100&lt;=L100),"Да | Yes","НЕ | NO")</f>
@@ -30255,13 +30255,13 @@
         <v>9</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="K101" s="15" t="n">
-        <v>8.1</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L101" s="15" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M101" s="14">
         <f>IF(AND(C101&gt;=K101,C101&lt;=L101),"Да | Yes","НЕ | NO")</f>
@@ -30345,13 +30345,13 @@
         <v>11</v>
       </c>
       <c r="J102" s="13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K102" s="13" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
       <c r="L102" s="13" t="n">
-        <v>12.09</v>
+        <v>12.1</v>
       </c>
       <c r="M102" s="12">
         <f>IF(AND(C102&gt;=K102,C102&lt;=L102),"Да | Yes","НЕ | NO")</f>

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -17725,7 +17725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17939,16 +17939,16 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>1.59</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>18.41</v>
+        <v>19.86</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>21.59</v>
+        <v>21.14</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>1</v>
@@ -17977,16 +17977,16 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>21.6</v>
+        <v>21.15</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>26.4</v>
+        <v>25.85</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>2</v>
@@ -18129,28 +18129,28 @@
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>0.6999999999999997</v>
+        <v>1.34</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>11.3</v>
+        <v>12.16</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>12.7</v>
+        <v>14.84</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>CC012603</t>
+          <t>CC012603, CC112501</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J14" s="12" t="inlineStr"/>
@@ -18167,23 +18167,23 @@
         </is>
       </c>
       <c r="C15" s="15" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="D15" s="15" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>12.71</v>
+        <v>14.85</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>15.29</v>
+        <v>18.15</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -18196,37 +18196,37 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Cash Cow</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>18.7</v>
+        <v>11</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J16" s="12" t="inlineStr"/>
@@ -18234,7 +18234,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Clemosa a bud</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -18243,28 +18243,28 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>CLE072501</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J17" s="14" t="inlineStr"/>
@@ -18272,7 +18272,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Clemosa a bud</t>
+          <t>Fat Bastard</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -18281,23 +18281,23 @@
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.8</v>
+        <v>1.54</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>7.2</v>
+        <v>14.46</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>8.800000000000001</v>
+        <v>17.54</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>CLE072501</t>
+          <t>FB012601/1, FB112501</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -18315,27 +18315,27 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>13.5</v>
+        <v>17.55</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>16.5</v>
+        <v>21.45</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>FB012601/1</t>
+          <t>FB012603V, FB012602, FB012603</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -18348,32 +18348,32 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1.49</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>16.51</v>
+        <v>13.05</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>19.49</v>
+        <v>15.95</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>FB112501, FB012603V, FB012602</t>
+          <t>GG1024, GG012601, GG1024_02</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -18386,32 +18386,32 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>19.5</v>
+        <v>15.96</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>22.5</v>
+        <v>19.04</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>GG012603, GG112501, GG1024_01</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -18424,7 +18424,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -18433,23 +18433,23 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>12.71</v>
+        <v>15.5</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>15.29</v>
+        <v>18.5</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -18462,7 +18462,7 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -18471,23 +18471,23 @@
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>15.3</v>
+        <v>18.51</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>18.7</v>
+        <v>22.49</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>GG012601, GG1024_02, GG012603, GG112501, GG1024_01</t>
+          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -18505,27 +18505,27 @@
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>15.6</v>
+        <v>22.5</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>18.4</v>
+        <v>27.5</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>GP082501/2</t>
+          <t>GP0824_02, GP062501, GP0824_03, GP092501</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -18538,70 +18538,74 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>1.59</v>
+        <v>0.7</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>18.41</v>
+        <v>6.3</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>21.59</v>
+        <v>7.7</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J25" s="14" t="inlineStr"/>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 7.70%–10.35% | NO GRADE 7.70%–10.35%</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Graps &amp; Creme</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>2.4</v>
+        <v>1.15</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>21.6</v>
+        <v>10.35</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>26.4</v>
+        <v>12.65</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>GP0824_02, GP062501, GP0824_03, GP092501</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -18614,7 +18618,7 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -18623,40 +18627,36 @@
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0.7</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>6.3</v>
+        <v>16.56</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>7.7</v>
+        <v>18.44</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>GRC102501/1</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>НЕМА КЛАСА 7.70%–10.80% | NO GRADE 7.70%–10.80%</t>
-        </is>
-      </c>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J27" s="14" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Graps &amp; Creme</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
@@ -18665,23 +18665,23 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>12</v>
+        <v>20.5</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.2</v>
+        <v>2.05</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>10.8</v>
+        <v>18.45</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>13.2</v>
+        <v>22.55</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -18694,7 +18694,7 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -18703,23 +18703,23 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0.8900000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>17.11</v>
+        <v>15.01</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>18.89</v>
+        <v>17.99</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>JD012603/02V, JD012603/01</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -18732,7 +18732,7 @@
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jelly Donutz</t>
         </is>
       </c>
       <c r="B30" s="12" t="inlineStr">
@@ -18741,23 +18741,23 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>18.9</v>
+        <v>18</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>23.1</v>
+        <v>22</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>HPA052501, HPA1024_01</t>
+          <t>JD012601, JD112501, JD012603/02</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -18770,7 +18770,7 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -18779,23 +18779,23 @@
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>1.09</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>14.91</v>
+        <v>16.56</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>17.09</v>
+        <v>18.44</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>JD012603/02V, JD012603/01</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -18808,7 +18808,7 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donutz</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -18817,23 +18817,23 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>17.1</v>
+        <v>18.45</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>20.9</v>
+        <v>22.55</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>JD012601, JD112501, JD012603/02</t>
+          <t>J31112501, J31122501</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -18846,7 +18846,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -18855,23 +18855,23 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>0.8900000000000001</v>
+        <v>1.7</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>17.11</v>
+        <v>15.3</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>18.89</v>
+        <v>18.7</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -18884,32 +18884,32 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>18.9</v>
+        <v>15.3</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>23.1</v>
+        <v>18.7</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>J31112501, J31122501</t>
+          <t>MB0824_05, MB0824_04</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -18922,7 +18922,7 @@
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -18931,23 +18931,23 @@
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>1.7</v>
+        <v>0.54</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>15.3</v>
+        <v>7.46</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>18.7</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>OPM122501, OPM112501</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -18960,32 +18960,32 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>17</v>
+        <v>9.5</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>1.7</v>
+        <v>0.95</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>15.3</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>18.7</v>
+        <v>10.45</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>MB0824_05, MB0824_04</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -18993,7 +18993,11 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
-      <c r="J36" s="12" t="inlineStr"/>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 10.45%–14.16% | NO GRADE 10.45%–14.16%</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -19003,27 +19007,27 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>0.09</v>
+        <v>1.34</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>7.91</v>
+        <v>14.16</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>8.09</v>
+        <v>16.84</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>OPM122501, OPM112501</t>
+          <t>OPM052501, OMP1024_01, OPM1024_03</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -19041,27 +19045,27 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>0.9</v>
+        <v>1.65</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>8.1</v>
+        <v>16.85</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>9.9</v>
+        <v>20.15</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>OPM1024_02, OPM1024</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -19069,41 +19073,37 @@
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
-      <c r="J38" s="12" t="inlineStr">
-        <is>
-          <t>НЕМА КЛАСА 9.90%–14.05% | NO GRADE 9.90%–14.05%</t>
-        </is>
-      </c>
+      <c r="J38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>0.9500000000000008</v>
+        <v>0.74</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>14.05</v>
+        <v>9.76</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>15.95</v>
+        <v>11.24</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>OPM052501, OMP1024_01</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -19116,32 +19116,32 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>15.96</v>
+        <v>11.25</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>18.04</v>
+        <v>13.75</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>OPM1024_03, OPM1024_02</t>
+          <t>PM092501, PM112501</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -19154,37 +19154,37 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-5</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>18.05</v>
+        <v>13.95</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>21.95</v>
+        <v>17.05</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr"/>
@@ -19192,7 +19192,7 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -19201,23 +19201,23 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>0.9900000000000002</v>
+        <v>1.79</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>10.01</v>
+        <v>16.21</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>11.99</v>
+        <v>19.79</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -19230,7 +19230,7 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -19239,23 +19239,23 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D43" s="15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G43" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E43" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="G43" s="14" t="n">
-        <v>2</v>
-      </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>PM092501, PM112501</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -19277,28 +19277,28 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1.6</v>
+        <v>0.89</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>14.4</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>17.6</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr"/>
@@ -19306,32 +19306,32 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>1.79</v>
+        <v>1.1</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>16.21</v>
+        <v>9.9</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>19.79</v>
+        <v>12.1</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -19344,12 +19344,12 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
@@ -19369,12 +19369,12 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Wedding Crasher</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -19391,23 +19391,23 @@
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.89</v>
+        <v>2.2</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>8.109999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>9.890000000000001</v>
+        <v>24.2</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>WC082501, WC072501</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -19416,120 +19416,6 @@
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>Sleepy Joy</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>Pot.-2</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="D48" s="13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E48" s="13" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G48" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="12" t="inlineStr">
-        <is>
-          <t>SJ092501, SJ102501</t>
-        </is>
-      </c>
-      <c r="I48" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J48" s="12" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="14" t="inlineStr">
-        <is>
-          <t>Wedding Cake</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>Pot.-1</t>
-        </is>
-      </c>
-      <c r="C49" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="D49" s="15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G49" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>WED102501</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
-        <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="J49" s="14" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Wedding Crasher</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>Pot.-1</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="D50" s="13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F50" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>WC082501, WC072501</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -19547,7 +19433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19899,7 +19785,7 @@
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>НЕМА КЛАСА 8.80%–13.50% | NO GRADE 8.80%–13.50%</t>
+          <t>НЕМА КЛАСА 8.80%–13.05% | NO GRADE 8.80%–13.05%</t>
         </is>
       </c>
     </row>
@@ -19915,16 +19801,16 @@
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>13.5</v>
+        <v>13.05</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>16.5</v>
+        <v>15.95</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>2</v>
@@ -20087,16 +19973,16 @@
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>13.5</v>
+        <v>14.46</v>
       </c>
       <c r="F16" s="13" t="n">
-        <v>16.5</v>
+        <v>17.54</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>1</v>
@@ -20130,23 +20016,23 @@
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="D17" s="15" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>16.51</v>
+        <v>17.55</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>19.49</v>
+        <v>21.45</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>FB012603V</t>
+          <t>FB012603V, FB012603</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -20164,32 +20050,32 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>Daywalker</t>
+          <t>Fat Sofa</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>19.5</v>
+        <v>15.75</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>22.5</v>
+        <v>19.25</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>FB012603</t>
+          <t>FB112501, FB012602</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -20207,7 +20093,7 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>Fat Sofa</t>
+          <t>Formula 1</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
@@ -20216,23 +20102,23 @@
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="D19" s="15" t="n">
-        <v>1.8</v>
+        <v>0.74</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>16.2</v>
+        <v>9.76</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>19.8</v>
+        <v>11.24</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>FB112501, FB012602</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -20242,7 +20128,7 @@
       </c>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>Fat Bastard</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr"/>
@@ -20255,27 +20141,27 @@
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.9900000000000002</v>
+        <v>1.25</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>10.01</v>
+        <v>11.25</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>11.99</v>
+        <v>13.75</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>PM092501, PM112501</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -20293,32 +20179,32 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Formula 1</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>12</v>
+        <v>13.95</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>14</v>
+        <v>17.05</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>2</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>PM092501, PM112501</t>
+          <t>GG012601, GG012603</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -20328,7 +20214,7 @@
       </c>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>GG4</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr"/>
@@ -20336,7 +20222,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Gorilla Gang</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -20345,23 +20231,23 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>14.4</v>
+        <v>12.71</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>17.6</v>
+        <v>15.29</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>GG012601, GG012603</t>
+          <t>GG1024</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -20371,7 +20257,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>GG4</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr"/>
@@ -20384,27 +20270,27 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>12.71</v>
+        <v>15.3</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>15.29</v>
+        <v>18.7</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>GG1024</t>
+          <t>GG1024_02, GG1024_01</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -20422,32 +20308,32 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Gorilla Gang</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>15.3</v>
+        <v>22.5</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>18.7</v>
+        <v>27.5</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>GG1024_02, GG1024_01</t>
+          <t>GP0824_02, GP0824_03, GP092501</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -20457,7 +20343,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>Gorilla Glue</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr"/>
@@ -20465,7 +20351,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Hazy Daze</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -20474,23 +20360,23 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>22.5</v>
+        <v>18.45</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>27.5</v>
+        <v>22.55</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>GP0824_02, GP0824_03, GP092501</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -20500,7 +20386,7 @@
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr"/>
@@ -20508,7 +20394,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Hazy Daze</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -20517,23 +20403,23 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>18.9</v>
+        <v>15.75</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>23.1</v>
+        <v>19.25</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>HPA052501, HPA1024_01</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -20551,7 +20437,7 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -20560,23 +20446,23 @@
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>15.3</v>
+        <v>14.46</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>18.7</v>
+        <v>17.54</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -20586,7 +20472,7 @@
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr"/>
@@ -20599,27 +20485,27 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.09</v>
+        <v>1.95</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>14.91</v>
+        <v>17.55</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>17.09</v>
+        <v>21.45</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>JD012603/02V</t>
+          <t>JD012601, JD112501, JD012603/02</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -20637,32 +20523,32 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.9</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>17.1</v>
+        <v>16.56</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>20.9</v>
+        <v>18.44</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>JD012601, JD112501, JD012603/02</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -20672,7 +20558,7 @@
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr"/>
@@ -20685,27 +20571,27 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>18</v>
+        <v>20.5</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>0.8900000000000001</v>
+        <v>2.05</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>17.11</v>
+        <v>18.45</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>18.89</v>
+        <v>22.55</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>J31112501, J31122501</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -20723,32 +20609,32 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>18.9</v>
+        <v>15.3</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>23.1</v>
+        <v>18.7</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>J31112501, J31122501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -20758,7 +20644,7 @@
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr"/>
@@ -20766,7 +20652,7 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Lifeguard</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -20775,33 +20661,33 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>15.3</v>
+        <v>13.95</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>18.7</v>
+        <v>17.05</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr"/>
@@ -20809,7 +20695,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>Lifeguard</t>
+          <t>NY Diesel</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -20818,33 +20704,33 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>17.6</v>
+        <v>18.7</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>MB0824_05, MB0824_04</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr"/>
@@ -20852,7 +20738,7 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>NY Diesel</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -20861,23 +20747,23 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>15.3</v>
+        <v>14.93</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>18.7</v>
+        <v>18.07</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>MB0824_05, MB0824_04</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -20887,7 +20773,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr"/>
@@ -20900,27 +20786,27 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>1.2</v>
+        <v>1.92</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>13.8</v>
+        <v>18.08</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>16.2</v>
+        <v>21.92</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>CJ062501/2, CJ062501/1</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -20938,32 +20824,32 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>OG Banana's</t>
+          <t>Orange Dream</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="D36" s="13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="E36" s="13" t="n">
-        <v>16.21</v>
-      </c>
       <c r="F36" s="13" t="n">
-        <v>19.79</v>
+        <v>22</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>CJ062501/2</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -20973,7 +20859,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr"/>
@@ -20981,32 +20867,32 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>OG Banana's</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>2.2</v>
+        <v>1.34</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>19.8</v>
+        <v>12.16</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>24.2</v>
+        <v>14.84</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>CJ062501/1</t>
+          <t>CC012603, CC112501</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -21016,7 +20902,7 @@
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>CashCow</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr"/>
@@ -21024,32 +20910,32 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Orange Dream</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>18</v>
+        <v>14.85</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>22</v>
+        <v>18.15</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -21059,7 +20945,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>CashCow</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr"/>
@@ -21067,7 +20953,7 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -21076,23 +20962,23 @@
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>0.6999999999999997</v>
+        <v>0.7</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>11.3</v>
+        <v>6.3</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>12.7</v>
+        <v>7.7</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>CC012603</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -21102,15 +20988,19 @@
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>CashCow</t>
-        </is>
-      </c>
-      <c r="K39" s="14" t="inlineStr"/>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 7.70%–10.35% | NO GRADE 7.70%–10.35%</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
@@ -21119,23 +21009,23 @@
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>12.71</v>
+        <v>10.35</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>15.29</v>
+        <v>12.65</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>CC112501</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -21145,7 +21035,7 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr"/>
@@ -21153,32 +21043,32 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>Rainbow Sherbet</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>15.3</v>
+        <v>19.8</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>18.7</v>
+        <v>24.2</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -21188,7 +21078,7 @@
       </c>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr"/>
@@ -21196,7 +21086,7 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Plum Tarte</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -21205,80 +21095,76 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>6.3</v>
+        <v>16.2</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>7.7</v>
+        <v>19.8</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/1</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>НЕМА КЛАСА 7.70%–10.80% | NO GRADE 7.70%–10.80%</t>
-        </is>
-      </c>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="K42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Plum Tarte</t>
+          <t>Shark Tank</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>13.2</v>
+        <v>11</v>
       </c>
       <c r="G43" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr"/>
@@ -21286,7 +21172,7 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Rainbow Sherbet</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -21295,23 +21181,23 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>19.8</v>
+        <v>9.9</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>24.2</v>
+        <v>12.1</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -21321,7 +21207,7 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr"/>
@@ -21329,7 +21215,7 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -21338,23 +21224,23 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>1.8</v>
+        <v>0.54</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>16.2</v>
+        <v>7.46</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>19.8</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -21364,7 +21250,7 @@
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr"/>
@@ -21372,42 +21258,42 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Shark Tank</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>11</v>
+        <v>10.45</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr"/>
@@ -21415,7 +21301,7 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Strawberry Cupcakes</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -21424,33 +21310,33 @@
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>1.1</v>
+        <v>1.65</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>9.9</v>
+        <v>14.85</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>12.1</v>
+        <v>18.15</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>SJ092501, SJ102501</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr"/>
@@ -21458,7 +21344,7 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Soft Citrus Bloom</t>
+          <t>Sunset Sherbet</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -21467,23 +21353,23 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>8</v>
+        <v>20.5</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>0.09</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>7.91</v>
+        <v>19.86</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>8.09</v>
+        <v>21.14</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
@@ -21493,7 +21379,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr"/>
@@ -21501,7 +21387,7 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Soft Citrus Bloom</t>
+          <t>Sunset Sherbet</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -21510,23 +21396,23 @@
         </is>
       </c>
       <c r="C49" s="15" t="n">
-        <v>9</v>
+        <v>23.5</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>0.9</v>
+        <v>2.35</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>8.1</v>
+        <v>21.15</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>9.9</v>
+        <v>25.85</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>BSS1024_01/1, BSS1024</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -21536,7 +21422,7 @@
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr"/>
@@ -21544,7 +21430,7 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Strawberry Cupcakes</t>
+          <t>Tangie Queen</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
@@ -21565,21 +21451,21 @@
         <v>18.7</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>OPM1024_03, OPM1024_02</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr"/>
@@ -21587,7 +21473,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Sunset Sherbet</t>
+          <t>Tropic Cake</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -21596,33 +21482,33 @@
         </is>
       </c>
       <c r="C51" s="15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>18.41</v>
+        <v>19.8</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>21.59</v>
+        <v>24.2</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>BSS052501</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="K51" s="14" t="inlineStr"/>
@@ -21630,32 +21516,32 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Sunset Sherbet</t>
+          <t>Vanilla Grapes</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>21.6</v>
+        <v>15.3</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>26.4</v>
+        <v>18.7</v>
       </c>
       <c r="G52" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>BSS1024_01/1, BSS1024</t>
+          <t>GP082501/2, GP052501</t>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr">
@@ -21665,7 +21551,7 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr"/>
@@ -21673,32 +21559,32 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Tangie Queen</t>
+          <t>Vanilla Grapes</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C53" s="15" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>15.3</v>
+        <v>18.71</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>18.7</v>
+        <v>22.29</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>OPM1024_03, OPM1024_02</t>
+          <t>GP072501/2, GP082501/1, GP072501/1</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
@@ -21708,7 +21594,7 @@
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="K53" s="14" t="inlineStr"/>
@@ -21716,42 +21602,42 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>Tropic Cake</t>
+          <t>Vanilla Grapes</t>
         </is>
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>22</v>
+        <v>24.5</v>
       </c>
       <c r="D54" s="13" t="n">
         <v>2.2</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>19.8</v>
+        <v>22.3</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>24.2</v>
+        <v>26.7</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>GP062501</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr"/>
@@ -21759,7 +21645,7 @@
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>Vanilla Grapes</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
@@ -21768,23 +21654,23 @@
         </is>
       </c>
       <c r="C55" s="15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>15.6</v>
+        <v>19.8</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>18.4</v>
+        <v>24.2</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>GP082501/2</t>
+          <t>WC082501, WC072501</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
@@ -21794,139 +21680,10 @@
       </c>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Wedding Crusher</t>
         </is>
       </c>
       <c r="K55" s="14" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>Vanilla Grapes</t>
-        </is>
-      </c>
-      <c r="B56" s="12" t="inlineStr">
-        <is>
-          <t>Pot.-2</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="D56" s="13" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="E56" s="13" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="F56" s="13" t="n">
-        <v>21.59</v>
-      </c>
-      <c r="G56" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H56" s="12" t="inlineStr">
-        <is>
-          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
-        </is>
-      </c>
-      <c r="I56" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J56" s="12" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-      <c r="K56" s="12" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>Vanilla Grapes</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Pot.-3</t>
-        </is>
-      </c>
-      <c r="C57" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="D57" s="15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F57" s="15" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G57" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>GP062501</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J57" s="14" t="inlineStr">
-        <is>
-          <t>Grape Pie</t>
-        </is>
-      </c>
-      <c r="K57" s="14" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>Wedding Crusher</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="inlineStr">
-        <is>
-          <t>Pot.-1</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="D58" s="13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E58" s="13" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F58" s="13" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="G58" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="H58" s="12" t="inlineStr">
-        <is>
-          <t>WC082501, WC072501</t>
-        </is>
-      </c>
-      <c r="I58" s="12" t="inlineStr">
-        <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
-        </is>
-      </c>
-      <c r="J58" s="12" t="inlineStr">
-        <is>
-          <t>Wedding Crusher</t>
-        </is>
-      </c>
-      <c r="K58" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -22384,16 +22141,16 @@
         </is>
       </c>
       <c r="I9" s="15" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>21.6</v>
+        <v>21.15</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>26.4</v>
+        <v>25.85</v>
       </c>
       <c r="M9" s="14">
         <f>IF(AND(C9&gt;=K9,C9&lt;=L9),"Да | Yes","НЕ | NO")</f>
@@ -22425,13 +22182,13 @@
         </is>
       </c>
       <c r="T9" s="15" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="U9" s="15" t="n">
-        <v>21.6</v>
+        <v>21.15</v>
       </c>
       <c r="V9" s="15" t="n">
-        <v>26.4</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="10">
@@ -22547,16 +22304,16 @@
         </is>
       </c>
       <c r="I11" s="15" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>21.6</v>
+        <v>21.15</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>26.4</v>
+        <v>25.85</v>
       </c>
       <c r="M11" s="14">
         <f>IF(AND(C11&gt;=K11,C11&lt;=L11),"Да | Yes","НЕ | NO")</f>
@@ -22588,13 +22345,13 @@
         </is>
       </c>
       <c r="T11" s="15" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="U11" s="15" t="n">
-        <v>21.6</v>
+        <v>21.15</v>
       </c>
       <c r="V11" s="15" t="n">
-        <v>26.4</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="12">
@@ -22637,16 +22394,16 @@
         </is>
       </c>
       <c r="I12" s="13" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>1.59</v>
+        <v>0.6400000000000001</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>18.41</v>
+        <v>19.86</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>21.59</v>
+        <v>21.14</v>
       </c>
       <c r="M12" s="12">
         <f>IF(AND(C12&gt;=K12,C12&lt;=L12),"Да | Yes","НЕ | NO")</f>
@@ -22678,13 +22435,13 @@
         </is>
       </c>
       <c r="T12" s="13" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>18.41</v>
+        <v>19.86</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>21.59</v>
+        <v>21.14</v>
       </c>
     </row>
     <row r="13">
@@ -22858,13 +22615,13 @@
         </is>
       </c>
       <c r="T14" s="13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>16.21</v>
+        <v>18.08</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>19.79</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="15">
@@ -23128,13 +22885,13 @@
         </is>
       </c>
       <c r="T17" s="15" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="U17" s="15" t="n">
-        <v>13.8</v>
+        <v>14.93</v>
       </c>
       <c r="V17" s="15" t="n">
-        <v>16.2</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="18">
@@ -23484,17 +23241,17 @@
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T21" s="15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U21" s="15" t="n">
-        <v>19.8</v>
+        <v>18.08</v>
       </c>
       <c r="V21" s="15" t="n">
-        <v>24.2</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="22">
@@ -23578,13 +23335,13 @@
         </is>
       </c>
       <c r="T22" s="13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>16.21</v>
+        <v>18.08</v>
       </c>
       <c r="V22" s="13" t="n">
-        <v>19.79</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="23">
@@ -23803,20 +23560,20 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I25" s="15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="K25" s="15" t="n">
-        <v>15.3</v>
+        <v>14.85</v>
       </c>
       <c r="L25" s="15" t="n">
-        <v>18.7</v>
+        <v>18.15</v>
       </c>
       <c r="M25" s="14">
         <f>IF(AND(C25&gt;=K25,C25&lt;=L25),"Да | Yes","НЕ | NO")</f>
@@ -23844,17 +23601,17 @@
       </c>
       <c r="S25" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T25" s="15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="U25" s="15" t="n">
-        <v>15.3</v>
+        <v>14.85</v>
       </c>
       <c r="V25" s="15" t="n">
-        <v>18.7</v>
+        <v>18.15</v>
       </c>
     </row>
     <row r="26">
@@ -23893,20 +23650,20 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I26" s="13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J26" s="13" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>12.71</v>
+        <v>12.16</v>
       </c>
       <c r="L26" s="13" t="n">
-        <v>15.29</v>
+        <v>14.84</v>
       </c>
       <c r="M26" s="12">
         <f>IF(AND(C26&gt;=K26,C26&lt;=L26),"Да | Yes","НЕ | NO")</f>
@@ -23931,17 +23688,17 @@
       </c>
       <c r="S26" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T26" s="13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="U26" s="13" t="n">
-        <v>12.71</v>
+        <v>12.16</v>
       </c>
       <c r="V26" s="13" t="n">
-        <v>15.29</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="27">
@@ -24064,16 +23821,16 @@
         </is>
       </c>
       <c r="I28" s="13" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="K28" s="13" t="n">
-        <v>16.51</v>
+        <v>17.55</v>
       </c>
       <c r="L28" s="13" t="n">
-        <v>19.49</v>
+        <v>21.45</v>
       </c>
       <c r="M28" s="12">
         <f>IF(AND(C28&gt;=K28,C28&lt;=L28),"Да | Yes","НЕ | NO")</f>
@@ -24105,13 +23862,13 @@
         </is>
       </c>
       <c r="T28" s="13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U28" s="13" t="n">
-        <v>16.2</v>
+        <v>15.75</v>
       </c>
       <c r="V28" s="13" t="n">
-        <v>19.8</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="29">
@@ -24150,20 +23907,20 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I29" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>16.51</v>
+        <v>14.46</v>
       </c>
       <c r="L29" s="15" t="n">
-        <v>19.49</v>
+        <v>17.54</v>
       </c>
       <c r="M29" s="14">
         <f>IF(AND(C29&gt;=K29,C29&lt;=L29),"Да | Yes","НЕ | NO")</f>
@@ -24195,13 +23952,13 @@
         </is>
       </c>
       <c r="T29" s="15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="U29" s="15" t="n">
-        <v>16.2</v>
+        <v>15.75</v>
       </c>
       <c r="V29" s="15" t="n">
-        <v>19.8</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="30">
@@ -24244,16 +24001,16 @@
         </is>
       </c>
       <c r="I30" s="13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J30" s="13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="K30" s="13" t="n">
-        <v>13.5</v>
+        <v>14.46</v>
       </c>
       <c r="L30" s="13" t="n">
-        <v>16.5</v>
+        <v>17.54</v>
       </c>
       <c r="M30" s="12">
         <f>IF(AND(C30&gt;=K30,C30&lt;=L30),"Да | Yes","НЕ | NO")</f>
@@ -24285,13 +24042,13 @@
         </is>
       </c>
       <c r="T30" s="13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U30" s="13" t="n">
-        <v>13.5</v>
+        <v>14.46</v>
       </c>
       <c r="V30" s="13" t="n">
-        <v>16.5</v>
+        <v>17.54</v>
       </c>
     </row>
     <row r="31">
@@ -24400,20 +24157,20 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I32" s="13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="J32" s="13" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="K32" s="13" t="n">
-        <v>19.5</v>
+        <v>17.55</v>
       </c>
       <c r="L32" s="13" t="n">
-        <v>22.5</v>
+        <v>21.45</v>
       </c>
       <c r="M32" s="12">
         <f>IF(AND(C32&gt;=K32,C32&lt;=L32),"Да | Yes","НЕ | NO")</f>
@@ -24441,17 +24198,17 @@
       </c>
       <c r="S32" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T32" s="13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="U32" s="13" t="n">
-        <v>19.5</v>
+        <v>17.55</v>
       </c>
       <c r="V32" s="13" t="n">
-        <v>22.5</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="33">
@@ -24494,16 +24251,16 @@
         </is>
       </c>
       <c r="I33" s="15" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>16.51</v>
+        <v>17.55</v>
       </c>
       <c r="L33" s="15" t="n">
-        <v>19.49</v>
+        <v>21.45</v>
       </c>
       <c r="M33" s="14">
         <f>IF(AND(C33&gt;=K33,C33&lt;=L33),"Да | Yes","НЕ | NO")</f>
@@ -24535,13 +24292,13 @@
         </is>
       </c>
       <c r="T33" s="15" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="U33" s="15" t="n">
-        <v>16.51</v>
+        <v>17.55</v>
       </c>
       <c r="V33" s="15" t="n">
-        <v>19.49</v>
+        <v>21.45</v>
       </c>
     </row>
     <row r="34">
@@ -24584,16 +24341,16 @@
         </is>
       </c>
       <c r="I34" s="13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>15.3</v>
+        <v>15.96</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>18.7</v>
+        <v>19.04</v>
       </c>
       <c r="M34" s="12">
         <f>IF(AND(C34&gt;=K34,C34&lt;=L34),"Да | Yes","НЕ | NO")</f>
@@ -24674,16 +24431,16 @@
         </is>
       </c>
       <c r="I35" s="15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>15.3</v>
+        <v>15.96</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>18.7</v>
+        <v>19.04</v>
       </c>
       <c r="M35" s="14">
         <f>IF(AND(C35&gt;=K35,C35&lt;=L35),"Да | Yes","НЕ | NO")</f>
@@ -24754,16 +24511,16 @@
         </is>
       </c>
       <c r="I36" s="13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>15.3</v>
+        <v>15.96</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>18.7</v>
+        <v>19.04</v>
       </c>
       <c r="M36" s="12">
         <f>IF(AND(C36&gt;=K36,C36&lt;=L36),"Да | Yes","НЕ | NO")</f>
@@ -24840,20 +24597,20 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I37" s="15" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>1.7</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>15.3</v>
+        <v>13.05</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>18.7</v>
+        <v>15.95</v>
       </c>
       <c r="M37" s="14">
         <f>IF(AND(C37&gt;=K37,C37&lt;=L37),"Да | Yes","НЕ | NO")</f>
@@ -24924,16 +24681,16 @@
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>15.3</v>
+        <v>15.96</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>18.7</v>
+        <v>19.04</v>
       </c>
       <c r="M38" s="12">
         <f>IF(AND(C38&gt;=K38,C38&lt;=L38),"Да | Yes","НЕ | NO")</f>
@@ -25083,20 +24840,20 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="I40" s="13" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>1.7</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>15.3</v>
+        <v>13.05</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>18.7</v>
+        <v>15.95</v>
       </c>
       <c r="M40" s="12">
         <f>IF(AND(C40&gt;=K40,C40&lt;=L40),"Да | Yes","НЕ | NO")</f>
@@ -25177,16 +24934,16 @@
         </is>
       </c>
       <c r="I41" s="15" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>1.29</v>
+        <v>1.449999999999999</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>12.71</v>
+        <v>13.05</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>15.29</v>
+        <v>15.95</v>
       </c>
       <c r="M41" s="14">
         <f>IF(AND(C41&gt;=K41,C41&lt;=L41),"Да | Yes","НЕ | NO")</f>
@@ -25267,16 +25024,16 @@
         </is>
       </c>
       <c r="I42" s="13" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>15.3</v>
+        <v>15.96</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>18.7</v>
+        <v>19.04</v>
       </c>
       <c r="M42" s="12">
         <f>IF(AND(C42&gt;=K42,C42&lt;=L42),"Да | Yes","НЕ | NO")</f>
@@ -25566,16 +25323,16 @@
         </is>
       </c>
       <c r="I46" s="13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="M46" s="12">
         <f>IF(AND(C46&gt;=K46,C46&lt;=L46),"Да | Yes","НЕ | NO")</f>
@@ -25646,16 +25403,16 @@
         </is>
       </c>
       <c r="I47" s="15" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>18.41</v>
+        <v>18.51</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>21.59</v>
+        <v>22.49</v>
       </c>
       <c r="M47" s="14">
         <f>IF(AND(C47&gt;=K47,C47&lt;=L47),"Да | Yes","НЕ | NO")</f>
@@ -25683,17 +25440,17 @@
       </c>
       <c r="S47" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T47" s="15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>18.41</v>
+        <v>15.3</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>21.59</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="48">
@@ -25739,13 +25496,13 @@
         <v>17</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="M48" s="12">
         <f>IF(AND(C48&gt;=K48,C48&lt;=L48),"Да | Yes","НЕ | NO")</f>
@@ -25780,10 +25537,10 @@
         <v>17</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="V48" s="13" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="49">
@@ -25826,16 +25583,16 @@
         </is>
       </c>
       <c r="I49" s="15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="M49" s="14">
         <f>IF(AND(C49&gt;=K49,C49&lt;=L49),"Да | Yes","НЕ | NO")</f>
@@ -25906,16 +25663,16 @@
         </is>
       </c>
       <c r="I50" s="13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="M50" s="12">
         <f>IF(AND(C50&gt;=K50,C50&lt;=L50),"Да | Yes","НЕ | NO")</f>
@@ -26059,16 +25816,16 @@
         </is>
       </c>
       <c r="I52" s="13" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>18.41</v>
+        <v>18.51</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>21.59</v>
+        <v>22.49</v>
       </c>
       <c r="M52" s="12">
         <f>IF(AND(C52&gt;=K52,C52&lt;=L52),"Да | Yes","НЕ | NO")</f>
@@ -26096,17 +25853,17 @@
       </c>
       <c r="S52" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="T52" s="13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>18.41</v>
+        <v>15.3</v>
       </c>
       <c r="V52" s="13" t="n">
-        <v>21.59</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="53">
@@ -26149,16 +25906,16 @@
         </is>
       </c>
       <c r="I53" s="15" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>18.41</v>
+        <v>18.51</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>21.59</v>
+        <v>22.49</v>
       </c>
       <c r="M53" s="14">
         <f>IF(AND(C53&gt;=K53,C53&lt;=L53),"Да | Yes","НЕ | NO")</f>
@@ -26190,13 +25947,13 @@
         </is>
       </c>
       <c r="T53" s="15" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="U53" s="15" t="n">
-        <v>18.41</v>
+        <v>18.71</v>
       </c>
       <c r="V53" s="15" t="n">
-        <v>21.59</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="54">
@@ -26239,16 +25996,16 @@
         </is>
       </c>
       <c r="I54" s="13" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>18.41</v>
+        <v>18.51</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>21.59</v>
+        <v>22.49</v>
       </c>
       <c r="M54" s="12">
         <f>IF(AND(C54&gt;=K54,C54&lt;=L54),"Да | Yes","НЕ | NO")</f>
@@ -26280,13 +26037,13 @@
         </is>
       </c>
       <c r="T54" s="13" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>18.41</v>
+        <v>18.71</v>
       </c>
       <c r="V54" s="13" t="n">
-        <v>21.59</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="55">
@@ -26329,16 +26086,16 @@
         </is>
       </c>
       <c r="I55" s="15" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>1.59</v>
+        <v>1.99</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>18.41</v>
+        <v>18.51</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>21.59</v>
+        <v>22.49</v>
       </c>
       <c r="M55" s="14">
         <f>IF(AND(C55&gt;=K55,C55&lt;=L55),"Да | Yes","НЕ | NO")</f>
@@ -26370,13 +26127,13 @@
         </is>
       </c>
       <c r="T55" s="15" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="U55" s="15" t="n">
-        <v>18.41</v>
+        <v>18.71</v>
       </c>
       <c r="V55" s="15" t="n">
-        <v>21.59</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="56">
@@ -26422,13 +26179,13 @@
         <v>17</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="M56" s="12">
         <f>IF(AND(C56&gt;=K56,C56&lt;=L56),"Да | Yes","НЕ | NO")</f>
@@ -26463,10 +26220,10 @@
         <v>17</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="V56" s="13" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="57">
@@ -26509,16 +26266,16 @@
         </is>
       </c>
       <c r="I57" s="15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="M57" s="14">
         <f>IF(AND(C57&gt;=K57,C57&lt;=L57),"Да | Yes","НЕ | NO")</f>
@@ -26589,16 +26346,16 @@
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="M58" s="12">
         <f>IF(AND(C58&gt;=K58,C58&lt;=L58),"Да | Yes","НЕ | NO")</f>
@@ -26669,16 +26426,16 @@
         </is>
       </c>
       <c r="I59" s="15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>26.4</v>
+        <v>27.5</v>
       </c>
       <c r="M59" s="14">
         <f>IF(AND(C59&gt;=K59,C59&lt;=L59),"Да | Yes","НЕ | NO")</f>
@@ -26710,13 +26467,13 @@
         </is>
       </c>
       <c r="T59" s="15" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="U59" s="15" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="V59" s="15" t="n">
-        <v>26.4</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="60">
@@ -26759,16 +26516,16 @@
         </is>
       </c>
       <c r="I60" s="13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J60" s="13" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="K60" s="13" t="n">
-        <v>10.8</v>
+        <v>10.35</v>
       </c>
       <c r="L60" s="13" t="n">
-        <v>13.2</v>
+        <v>12.65</v>
       </c>
       <c r="M60" s="12">
         <f>IF(AND(C60&gt;=K60,C60&lt;=L60),"Да | Yes","НЕ | NO")</f>
@@ -26800,13 +26557,13 @@
         </is>
       </c>
       <c r="T60" s="13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="U60" s="13" t="n">
-        <v>10.8</v>
+        <v>10.35</v>
       </c>
       <c r="V60" s="13" t="n">
-        <v>13.2</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="61">
@@ -26849,16 +26606,16 @@
         </is>
       </c>
       <c r="I61" s="15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>0.8900000000000001</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>17.11</v>
+        <v>16.56</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>18.89</v>
+        <v>18.44</v>
       </c>
       <c r="M61" s="14">
         <f>IF(AND(C61&gt;=K61,C61&lt;=L61),"Да | Yes","НЕ | NO")</f>
@@ -26929,16 +26686,16 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
       <c r="M62" s="12">
         <f>IF(AND(C62&gt;=K62,C62&lt;=L62),"Да | Yes","НЕ | NO")</f>
@@ -26970,13 +26727,13 @@
         </is>
       </c>
       <c r="T62" s="13" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="U62" s="13" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="V62" s="13" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="63">
@@ -27019,16 +26776,16 @@
         </is>
       </c>
       <c r="I63" s="15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
       <c r="M63" s="14">
         <f>IF(AND(C63&gt;=K63,C63&lt;=L63),"Да | Yes","НЕ | NO")</f>
@@ -27060,13 +26817,13 @@
         </is>
       </c>
       <c r="T63" s="15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="U63" s="15" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="V63" s="15" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="64">
@@ -27109,16 +26866,16 @@
         </is>
       </c>
       <c r="I64" s="13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>0.8900000000000001</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>17.11</v>
+        <v>16.56</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>18.89</v>
+        <v>18.44</v>
       </c>
       <c r="M64" s="12">
         <f>IF(AND(C64&gt;=K64,C64&lt;=L64),"Да | Yes","НЕ | NO")</f>
@@ -27189,16 +26946,16 @@
         </is>
       </c>
       <c r="I65" s="15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J65" s="15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="K65" s="15" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="L65" s="15" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
       <c r="M65" s="14">
         <f>IF(AND(C65&gt;=K65,C65&lt;=L65),"Да | Yes","НЕ | NO")</f>
@@ -27230,13 +26987,13 @@
         </is>
       </c>
       <c r="T65" s="15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="U65" s="15" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="V65" s="15" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
     </row>
     <row r="66">
@@ -27279,16 +27036,16 @@
         </is>
       </c>
       <c r="I66" s="13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J66" s="13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K66" s="13" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="L66" s="13" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="M66" s="12">
         <f>IF(AND(C66&gt;=K66,C66&lt;=L66),"Да | Yes","НЕ | NO")</f>
@@ -27359,16 +27116,16 @@
         </is>
       </c>
       <c r="I67" s="15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K67" s="15" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="L67" s="15" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="M67" s="14">
         <f>IF(AND(C67&gt;=K67,C67&lt;=L67),"Да | Yes","НЕ | NO")</f>
@@ -27439,16 +27196,16 @@
         </is>
       </c>
       <c r="I68" s="13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J68" s="13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K68" s="13" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="L68" s="13" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="M68" s="12">
         <f>IF(AND(C68&gt;=K68,C68&lt;=L68),"Да | Yes","НЕ | NO")</f>
@@ -27519,16 +27276,16 @@
         </is>
       </c>
       <c r="I69" s="15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K69" s="15" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="L69" s="15" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="M69" s="14">
         <f>IF(AND(C69&gt;=K69,C69&lt;=L69),"Да | Yes","НЕ | NO")</f>
@@ -27599,16 +27356,16 @@
         </is>
       </c>
       <c r="I70" s="13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J70" s="13" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K70" s="13" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="L70" s="13" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="M70" s="12">
         <f>IF(AND(C70&gt;=K70,C70&lt;=L70),"Да | Yes","НЕ | NO")</f>
@@ -27679,16 +27436,16 @@
         </is>
       </c>
       <c r="I71" s="15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>1.09</v>
+        <v>1.49</v>
       </c>
       <c r="K71" s="15" t="n">
-        <v>14.91</v>
+        <v>15.01</v>
       </c>
       <c r="L71" s="15" t="n">
-        <v>17.09</v>
+        <v>17.99</v>
       </c>
       <c r="M71" s="14">
         <f>IF(AND(C71&gt;=K71,C71&lt;=L71),"Да | Yes","НЕ | NO")</f>
@@ -27832,16 +27589,16 @@
         </is>
       </c>
       <c r="I73" s="15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0.8900000000000001</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>17.11</v>
+        <v>16.56</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>18.89</v>
+        <v>18.44</v>
       </c>
       <c r="M73" s="14">
         <f>IF(AND(C73&gt;=K73,C73&lt;=L73),"Да | Yes","НЕ | NO")</f>
@@ -27912,16 +27669,16 @@
         </is>
       </c>
       <c r="I74" s="13" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
       <c r="M74" s="12">
         <f>IF(AND(C74&gt;=K74,C74&lt;=L74),"Да | Yes","НЕ | NO")</f>
@@ -27992,16 +27749,16 @@
         </is>
       </c>
       <c r="I75" s="15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0.8900000000000001</v>
+        <v>0.9400000000000004</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>17.11</v>
+        <v>16.56</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>18.89</v>
+        <v>18.44</v>
       </c>
       <c r="M75" s="14">
         <f>IF(AND(C75&gt;=K75,C75&lt;=L75),"Да | Yes","НЕ | NO")</f>
@@ -28072,16 +27829,16 @@
         </is>
       </c>
       <c r="I76" s="13" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
       <c r="M76" s="12">
         <f>IF(AND(C76&gt;=K76,C76&lt;=L76),"Да | Yes","НЕ | NO")</f>
@@ -28152,16 +27909,16 @@
         </is>
       </c>
       <c r="I77" s="15" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
       <c r="M77" s="14">
         <f>IF(AND(C77&gt;=K77,C77&lt;=L77),"Да | Yes","НЕ | NO")</f>
@@ -28232,16 +27989,16 @@
         </is>
       </c>
       <c r="I78" s="13" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>18.9</v>
+        <v>18.45</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>23.1</v>
+        <v>22.55</v>
       </c>
       <c r="M78" s="12">
         <f>IF(AND(C78&gt;=K78,C78&lt;=L78),"Да | Yes","НЕ | NO")</f>
@@ -28575,13 +28332,13 @@
         <v>8</v>
       </c>
       <c r="J82" s="13" t="n">
-        <v>0.09</v>
+        <v>0.54</v>
       </c>
       <c r="K82" s="13" t="n">
-        <v>7.91</v>
+        <v>7.46</v>
       </c>
       <c r="L82" s="13" t="n">
-        <v>8.09</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M82" s="12">
         <f>IF(AND(C82&gt;=K82,C82&lt;=L82),"Да | Yes","НЕ | NO")</f>
@@ -28616,10 +28373,10 @@
         <v>8</v>
       </c>
       <c r="U82" s="13" t="n">
-        <v>7.91</v>
+        <v>7.46</v>
       </c>
       <c r="V82" s="13" t="n">
-        <v>8.09</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -28662,16 +28419,16 @@
         </is>
       </c>
       <c r="I83" s="15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>0.9500000000000008</v>
+        <v>1.34</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>14.05</v>
+        <v>14.16</v>
       </c>
       <c r="L83" s="15" t="n">
-        <v>15.95</v>
+        <v>16.84</v>
       </c>
       <c r="M83" s="14">
         <f>IF(AND(C83&gt;=K83,C83&lt;=L83),"Да | Yes","НЕ | NO")</f>
@@ -28703,13 +28460,13 @@
         </is>
       </c>
       <c r="T83" s="15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="U83" s="15" t="n">
-        <v>13.5</v>
+        <v>13.05</v>
       </c>
       <c r="V83" s="15" t="n">
-        <v>16.5</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="84">
@@ -28752,16 +28509,16 @@
         </is>
       </c>
       <c r="I84" s="13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>0.9500000000000008</v>
+        <v>1.34</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>14.05</v>
+        <v>14.16</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>15.95</v>
+        <v>16.84</v>
       </c>
       <c r="M84" s="12">
         <f>IF(AND(C84&gt;=K84,C84&lt;=L84),"Да | Yes","НЕ | NO")</f>
@@ -28793,13 +28550,13 @@
         </is>
       </c>
       <c r="T84" s="13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="U84" s="13" t="n">
-        <v>13.5</v>
+        <v>13.05</v>
       </c>
       <c r="V84" s="13" t="n">
-        <v>16.5</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="85">
@@ -28838,20 +28595,20 @@
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>Pot.-5</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I85" s="15" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="K85" s="15" t="n">
-        <v>18.05</v>
+        <v>16.85</v>
       </c>
       <c r="L85" s="15" t="n">
-        <v>21.95</v>
+        <v>20.15</v>
       </c>
       <c r="M85" s="14">
         <f>IF(AND(C85&gt;=K85,C85&lt;=L85),"Да | Yes","НЕ | NO")</f>
@@ -28932,16 +28689,16 @@
         </is>
       </c>
       <c r="I86" s="13" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>15.96</v>
+        <v>16.85</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>18.04</v>
+        <v>20.15</v>
       </c>
       <c r="M86" s="12">
         <f>IF(AND(C86&gt;=K86,C86&lt;=L86),"Да | Yes","НЕ | NO")</f>
@@ -29025,13 +28782,13 @@
         <v>8</v>
       </c>
       <c r="J87" s="15" t="n">
-        <v>0.09</v>
+        <v>0.54</v>
       </c>
       <c r="K87" s="15" t="n">
-        <v>7.91</v>
+        <v>7.46</v>
       </c>
       <c r="L87" s="15" t="n">
-        <v>8.09</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M87" s="14">
         <f>IF(AND(C87&gt;=K87,C87&lt;=L87),"Да | Yes","НЕ | NO")</f>
@@ -29115,13 +28872,13 @@
         <v>8</v>
       </c>
       <c r="J88" s="13" t="n">
-        <v>0.09</v>
+        <v>0.54</v>
       </c>
       <c r="K88" s="13" t="n">
-        <v>7.91</v>
+        <v>7.46</v>
       </c>
       <c r="L88" s="13" t="n">
-        <v>8.09</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M88" s="12">
         <f>IF(AND(C88&gt;=K88,C88&lt;=L88),"Да | Yes","НЕ | NO")</f>
@@ -29202,16 +28959,16 @@
         </is>
       </c>
       <c r="I89" s="15" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="K89" s="15" t="n">
-        <v>8.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L89" s="15" t="n">
-        <v>9.9</v>
+        <v>10.45</v>
       </c>
       <c r="M89" s="14">
         <f>IF(AND(C89&gt;=K89,C89&lt;=L89),"Да | Yes","НЕ | NO")</f>
@@ -29243,13 +29000,13 @@
         </is>
       </c>
       <c r="T89" s="15" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="U89" s="15" t="n">
-        <v>8.1</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="V89" s="15" t="n">
-        <v>9.9</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="90">
@@ -29288,20 +29045,20 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>Pot.-5</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I90" s="13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>18.05</v>
+        <v>16.85</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>21.95</v>
+        <v>20.15</v>
       </c>
       <c r="M90" s="12">
         <f>IF(AND(C90&gt;=K90,C90&lt;=L90),"Да | Yes","НЕ | NO")</f>
@@ -29382,16 +29139,16 @@
         </is>
       </c>
       <c r="I91" s="15" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>15.96</v>
+        <v>16.85</v>
       </c>
       <c r="L91" s="15" t="n">
-        <v>18.04</v>
+        <v>20.15</v>
       </c>
       <c r="M91" s="14">
         <f>IF(AND(C91&gt;=K91,C91&lt;=L91),"Да | Yes","НЕ | NO")</f>
@@ -29468,20 +29225,20 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>15.96</v>
+        <v>14.16</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>18.04</v>
+        <v>16.84</v>
       </c>
       <c r="M92" s="12">
         <f>IF(AND(C92&gt;=K92,C92&lt;=L92),"Да | Yes","НЕ | NO")</f>
@@ -29562,16 +29319,16 @@
         </is>
       </c>
       <c r="I93" s="15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K93" s="15" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="L93" s="15" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="M93" s="14">
         <f>IF(AND(C93&gt;=K93,C93&lt;=L93),"Да | Yes","НЕ | NO")</f>
@@ -29603,13 +29360,13 @@
         </is>
       </c>
       <c r="T93" s="15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="U93" s="15" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="V93" s="15" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="94">
@@ -29652,16 +29409,16 @@
         </is>
       </c>
       <c r="I94" s="13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J94" s="13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K94" s="13" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="L94" s="13" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="M94" s="12">
         <f>IF(AND(C94&gt;=K94,C94&lt;=L94),"Да | Yes","НЕ | NO")</f>
@@ -29693,13 +29450,13 @@
         </is>
       </c>
       <c r="T94" s="13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="U94" s="13" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="V94" s="13" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="95">
@@ -29742,16 +29499,16 @@
         </is>
       </c>
       <c r="I95" s="15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K95" s="15" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="L95" s="15" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="M95" s="14">
         <f>IF(AND(C95&gt;=K95,C95&lt;=L95),"Да | Yes","НЕ | NO")</f>
@@ -29783,13 +29540,13 @@
         </is>
       </c>
       <c r="T95" s="15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="U95" s="15" t="n">
-        <v>12</v>
+        <v>11.25</v>
       </c>
       <c r="V95" s="15" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="96">
@@ -29832,16 +29589,16 @@
         </is>
       </c>
       <c r="I96" s="13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J96" s="13" t="n">
-        <v>0.9900000000000002</v>
+        <v>0.74</v>
       </c>
       <c r="K96" s="13" t="n">
-        <v>10.01</v>
+        <v>9.76</v>
       </c>
       <c r="L96" s="13" t="n">
-        <v>11.99</v>
+        <v>11.24</v>
       </c>
       <c r="M96" s="12">
         <f>IF(AND(C96&gt;=K96,C96&lt;=L96),"Да | Yes","НЕ | NO")</f>
@@ -29873,13 +29630,13 @@
         </is>
       </c>
       <c r="T96" s="13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="U96" s="13" t="n">
-        <v>10.01</v>
+        <v>9.76</v>
       </c>
       <c r="V96" s="13" t="n">
-        <v>11.99</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="97">

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -17725,7 +17725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -17942,13 +17942,13 @@
         <v>20.5</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.6400000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>19.86</v>
+        <v>18.96</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>21.14</v>
+        <v>22.04</v>
       </c>
       <c r="G9" s="14" t="n">
         <v>1</v>
@@ -17977,16 +17977,16 @@
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>21.15</v>
+        <v>22.05</v>
       </c>
       <c r="F10" s="13" t="n">
-        <v>25.85</v>
+        <v>26.95</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>2</v>
@@ -18360,20 +18360,20 @@
         <v>14.5</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>1.449999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>13.05</v>
+        <v>13.26</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>15.95</v>
+        <v>15.74</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>GG1024, GG012601, GG1024_02</t>
+          <t>GG1024, GG012601</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -18398,20 +18398,20 @@
         <v>17.5</v>
       </c>
       <c r="D21" s="15" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>15.96</v>
+        <v>15.75</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>19.04</v>
+        <v>19.25</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>GG012603, GG112501, GG1024_01</t>
+          <t>GG1024_02, GG012603, GG112501, GG1024_01</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -18630,13 +18630,13 @@
         <v>17.5</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0.9400000000000004</v>
+        <v>1.39</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>16.56</v>
+        <v>16.11</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>1</v>
@@ -18665,16 +18665,16 @@
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
@@ -18782,13 +18782,13 @@
         <v>17.5</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>0.9400000000000004</v>
+        <v>1.39</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>16.56</v>
+        <v>16.11</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>1</v>
@@ -18817,16 +18817,16 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>2</v>
@@ -18995,7 +18995,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>НЕМА КЛАСА 10.45%–14.16% | NO GRADE 10.45%–14.16%</t>
+          <t>НЕМА КЛАСА 10.45%–13.45% | NO GRADE 10.45%–13.45%</t>
         </is>
       </c>
     </row>
@@ -19011,23 +19011,23 @@
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>14.16</v>
+        <v>13.45</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>16.84</v>
+        <v>15.55</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>OPM052501, OMP1024_01, OPM1024_03</t>
+          <t>OPM052501, OMP1024_01</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -19049,23 +19049,23 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>16.85</v>
+        <v>15.56</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>20.15</v>
+        <v>18.44</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>OPM1024_02, OPM1024</t>
+          <t>OPM1024_03, OPM1024_02</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -19078,32 +19078,32 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Permanent Marker</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>10.5</v>
+        <v>20.5</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>0.74</v>
+        <v>2.05</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>9.76</v>
+        <v>18.45</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>11.24</v>
+        <v>22.55</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>PM072501</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -19121,27 +19121,27 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.25</v>
+        <v>0.74</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>11.25</v>
+        <v>9.76</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>13.75</v>
+        <v>11.24</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>PM092501, PM112501</t>
+          <t>PM072501</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -19154,37 +19154,37 @@
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Permanent Marker</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>13.95</v>
+        <v>11.25</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>17.05</v>
+        <v>13.75</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>PM092501, PM112501</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr"/>
@@ -19192,7 +19192,7 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -19201,28 +19201,28 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>16.21</v>
+        <v>13.95</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>19.79</v>
+        <v>17.05</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J42" s="12" t="inlineStr"/>
@@ -19235,27 +19235,27 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>19.8</v>
+        <v>16.21</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>24.2</v>
+        <v>19.79</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -19268,32 +19268,32 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Sleepy Joy</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>0.89</v>
+        <v>2.2</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>8.109999999999999</v>
+        <v>19.8</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>9.890000000000001</v>
+        <v>24.2</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>SJ112501</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -19311,27 +19311,27 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>1.1</v>
+        <v>0.89</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>9.9</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>12.1</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>SJ092501, SJ102501</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -19344,37 +19344,37 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Sleepy Joy</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>19.8</v>
+        <v>9.9</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>24.2</v>
+        <v>12.1</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J46" s="12" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Wedding Crasher</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -19403,19 +19403,57 @@
         <v>24.2</v>
       </c>
       <c r="G47" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>WED102501</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
+        <is>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+        </is>
+      </c>
+      <c r="J47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D48" s="13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G48" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H48" s="12" t="inlineStr">
         <is>
           <t>WC082501, WC072501</t>
         </is>
       </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="I48" s="12" t="inlineStr">
         <is>
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
-      <c r="J47" s="14" t="inlineStr"/>
+      <c r="J48" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -19433,7 +19471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20535,13 +20573,13 @@
         <v>17.5</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0.9400000000000004</v>
+        <v>1.39</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>16.56</v>
+        <v>16.11</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>1</v>
@@ -20575,16 +20613,16 @@
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>2</v>
@@ -20747,16 +20785,16 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>14.93</v>
+        <v>13.8</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>18.07</v>
+        <v>16.2</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>1</v>
@@ -20790,23 +20828,23 @@
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>18.08</v>
+        <v>16.21</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>21.92</v>
+        <v>19.79</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>CJ062501/2, CJ062501/1</t>
+          <t>CJ062501/2</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -20824,32 +20862,32 @@
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Orange Dream</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>22</v>
+        <v>24.2</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -20859,7 +20897,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr"/>
@@ -20867,7 +20905,7 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>Orange Dream</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -20876,23 +20914,23 @@
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>12.16</v>
+        <v>18</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>14.84</v>
+        <v>22</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>CC012603, CC112501</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -20902,7 +20940,7 @@
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr"/>
@@ -20915,27 +20953,27 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>14.85</v>
+        <v>12.16</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>18.15</v>
+        <v>14.84</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>CC012603, CC112501</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -20953,49 +20991,45 @@
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Plum Tarte</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>0.7</v>
+        <v>1.65</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>6.3</v>
+        <v>14.85</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>7.7</v>
+        <v>18.15</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>GRC102501/1</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
-        </is>
-      </c>
-      <c r="K39" s="14" t="inlineStr">
-        <is>
-          <t>НЕМА КЛАСА 7.70%–10.35% | NO GRADE 7.70%–10.35%</t>
-        </is>
-      </c>
+          <t>CashCow</t>
+        </is>
+      </c>
+      <c r="K39" s="14" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
@@ -21005,32 +21039,32 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>1.15</v>
+        <v>0.7</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>10.35</v>
+        <v>6.3</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>12.65</v>
+        <v>7.7</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
@@ -21038,37 +21072,41 @@
           <t>Grapes and Cream</t>
         </is>
       </c>
-      <c r="K40" s="12" t="inlineStr"/>
+      <c r="K40" s="12" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 7.70%–10.35% | NO GRADE 7.70%–10.35%</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Rainbow Sherbet</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>19.8</v>
+        <v>10.35</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>24.2</v>
+        <v>12.65</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -21078,7 +21116,7 @@
       </c>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr"/>
@@ -21086,7 +21124,7 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Rainbow Sherbet</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
@@ -21095,23 +21133,23 @@
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>19.8</v>
+        <v>24.2</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -21129,7 +21167,7 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Shark Tank</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -21138,33 +21176,33 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>9</v>
+        <v>16.2</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>11</v>
+        <v>19.8</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr"/>
@@ -21172,7 +21210,7 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Shark Tank</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -21181,33 +21219,33 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="F44" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="D44" s="13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F44" s="13" t="n">
-        <v>12.1</v>
-      </c>
       <c r="G44" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>SJ092501, SJ102501</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr"/>
@@ -21215,7 +21253,7 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Soft Citrus Bloom</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -21224,23 +21262,23 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D45" s="15" t="n">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="E45" s="15" t="n">
-        <v>7.46</v>
+        <v>9.9</v>
       </c>
       <c r="F45" s="15" t="n">
-        <v>8.539999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -21250,7 +21288,7 @@
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr"/>
@@ -21263,27 +21301,27 @@
       </c>
       <c r="B46" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>8.550000000000001</v>
+        <v>7.46</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>10.45</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -21301,42 +21339,42 @@
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Strawberry Cupcakes</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>16.5</v>
+        <v>9.5</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>1.65</v>
+        <v>0.95</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>14.85</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>18.15</v>
+        <v>10.45</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr"/>
@@ -21344,7 +21382,7 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Sunset Sherbet</t>
+          <t>Strawberry Cupcakes</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
@@ -21353,33 +21391,33 @@
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>0.6400000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>19.86</v>
+        <v>14.85</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>21.14</v>
+        <v>18.15</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>BSS052501</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr"/>
@@ -21392,27 +21430,27 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C49" s="15" t="n">
-        <v>23.5</v>
+        <v>20.5</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>2.35</v>
+        <v>1.54</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>21.15</v>
+        <v>18.96</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>25.85</v>
+        <v>22.04</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>BSS1024_01/1, BSS1024</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -21430,32 +21468,32 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>Tangie Queen</t>
+          <t>Sunset Sherbet</t>
         </is>
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>15.3</v>
+        <v>22.05</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>18.7</v>
+        <v>26.95</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>OPM1024_03, OPM1024_02</t>
+          <t>BSS1024_01/1, BSS1024</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
@@ -21465,7 +21503,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr"/>
@@ -21473,7 +21511,7 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Tropic Cake</t>
+          <t>Tangie Queen</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -21482,33 +21520,33 @@
         </is>
       </c>
       <c r="C51" s="15" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>19.8</v>
+        <v>15.3</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>24.2</v>
+        <v>18.7</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>OPM1024_03, OPM1024_02</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K51" s="14" t="inlineStr"/>
@@ -21516,7 +21554,7 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Vanilla Grapes</t>
+          <t>Tropic Cake</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
@@ -21525,33 +21563,33 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>15.3</v>
+        <v>19.8</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>18.7</v>
+        <v>24.2</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>GP082501/2, GP052501</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr"/>
@@ -21564,27 +21602,27 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C53" s="15" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>18.71</v>
+        <v>15.5</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>22.29</v>
+        <v>18.5</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>GP072501/2, GP082501/1, GP072501/1</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
@@ -21607,27 +21645,27 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>24.5</v>
+        <v>20.5</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>22.3</v>
+        <v>18.51</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>26.7</v>
+        <v>22.49</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
@@ -21645,45 +21683,88 @@
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="C55" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="D55" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G55" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="K55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
           <t>Wedding Crusher</t>
         </is>
       </c>
-      <c r="B55" s="14" t="inlineStr">
+      <c r="B56" s="12" t="inlineStr">
         <is>
           <t>Pot.-1</t>
         </is>
       </c>
-      <c r="C55" s="15" t="n">
+      <c r="C56" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="D55" s="15" t="n">
+      <c r="D56" s="13" t="n">
         <v>2.2</v>
       </c>
-      <c r="E55" s="15" t="n">
+      <c r="E56" s="13" t="n">
         <v>19.8</v>
       </c>
-      <c r="F55" s="15" t="n">
+      <c r="F56" s="13" t="n">
         <v>24.2</v>
       </c>
-      <c r="G55" s="14" t="n">
+      <c r="G56" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="H56" s="12" t="inlineStr">
         <is>
           <t>WC082501, WC072501</t>
         </is>
       </c>
-      <c r="I55" s="14" t="inlineStr">
+      <c r="I56" s="12" t="inlineStr">
         <is>
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
-      <c r="J55" s="14" t="inlineStr">
+      <c r="J56" s="12" t="inlineStr">
         <is>
           <t>Wedding Crusher</t>
         </is>
       </c>
-      <c r="K55" s="14" t="inlineStr"/>
+      <c r="K56" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -22141,16 +22222,16 @@
         </is>
       </c>
       <c r="I9" s="15" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>21.15</v>
+        <v>22.05</v>
       </c>
       <c r="L9" s="15" t="n">
-        <v>25.85</v>
+        <v>26.95</v>
       </c>
       <c r="M9" s="14">
         <f>IF(AND(C9&gt;=K9,C9&lt;=L9),"Да | Yes","НЕ | NO")</f>
@@ -22182,13 +22263,13 @@
         </is>
       </c>
       <c r="T9" s="15" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="U9" s="15" t="n">
-        <v>21.15</v>
+        <v>22.05</v>
       </c>
       <c r="V9" s="15" t="n">
-        <v>25.85</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="10">
@@ -22304,16 +22385,16 @@
         </is>
       </c>
       <c r="I11" s="15" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>21.15</v>
+        <v>22.05</v>
       </c>
       <c r="L11" s="15" t="n">
-        <v>25.85</v>
+        <v>26.95</v>
       </c>
       <c r="M11" s="14">
         <f>IF(AND(C11&gt;=K11,C11&lt;=L11),"Да | Yes","НЕ | NO")</f>
@@ -22345,13 +22426,13 @@
         </is>
       </c>
       <c r="T11" s="15" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="U11" s="15" t="n">
-        <v>21.15</v>
+        <v>22.05</v>
       </c>
       <c r="V11" s="15" t="n">
-        <v>25.85</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="12">
@@ -22397,13 +22478,13 @@
         <v>20.5</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>0.6400000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>19.86</v>
+        <v>18.96</v>
       </c>
       <c r="L12" s="13" t="n">
-        <v>21.14</v>
+        <v>22.04</v>
       </c>
       <c r="M12" s="12">
         <f>IF(AND(C12&gt;=K12,C12&lt;=L12),"Да | Yes","НЕ | NO")</f>
@@ -22438,10 +22519,10 @@
         <v>20.5</v>
       </c>
       <c r="U12" s="13" t="n">
-        <v>19.86</v>
+        <v>18.96</v>
       </c>
       <c r="V12" s="13" t="n">
-        <v>21.14</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="13">
@@ -22615,13 +22696,13 @@
         </is>
       </c>
       <c r="T14" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U14" s="13" t="n">
-        <v>18.08</v>
+        <v>16.21</v>
       </c>
       <c r="V14" s="13" t="n">
-        <v>21.92</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="15">
@@ -22885,13 +22966,13 @@
         </is>
       </c>
       <c r="T17" s="15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="U17" s="15" t="n">
-        <v>14.93</v>
+        <v>13.8</v>
       </c>
       <c r="V17" s="15" t="n">
-        <v>18.07</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="18">
@@ -23241,17 +23322,17 @@
       </c>
       <c r="S21" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T21" s="15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="U21" s="15" t="n">
-        <v>18.08</v>
+        <v>19.8</v>
       </c>
       <c r="V21" s="15" t="n">
-        <v>21.92</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="22">
@@ -23335,13 +23416,13 @@
         </is>
       </c>
       <c r="T22" s="13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="U22" s="13" t="n">
-        <v>18.08</v>
+        <v>16.21</v>
       </c>
       <c r="V22" s="13" t="n">
-        <v>21.92</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="23">
@@ -24344,13 +24425,13 @@
         <v>17.5</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="K34" s="13" t="n">
-        <v>15.96</v>
+        <v>15.75</v>
       </c>
       <c r="L34" s="13" t="n">
-        <v>19.04</v>
+        <v>19.25</v>
       </c>
       <c r="M34" s="12">
         <f>IF(AND(C34&gt;=K34,C34&lt;=L34),"Да | Yes","НЕ | NO")</f>
@@ -24434,13 +24515,13 @@
         <v>17.5</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>15.96</v>
+        <v>15.75</v>
       </c>
       <c r="L35" s="15" t="n">
-        <v>19.04</v>
+        <v>19.25</v>
       </c>
       <c r="M35" s="14">
         <f>IF(AND(C35&gt;=K35,C35&lt;=L35),"Да | Yes","НЕ | NO")</f>
@@ -24514,13 +24595,13 @@
         <v>17.5</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="K36" s="13" t="n">
-        <v>15.96</v>
+        <v>15.75</v>
       </c>
       <c r="L36" s="13" t="n">
-        <v>19.04</v>
+        <v>19.25</v>
       </c>
       <c r="M36" s="12">
         <f>IF(AND(C36&gt;=K36,C36&lt;=L36),"Да | Yes","НЕ | NO")</f>
@@ -24604,13 +24685,13 @@
         <v>14.5</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>1.449999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>13.05</v>
+        <v>13.26</v>
       </c>
       <c r="L37" s="15" t="n">
-        <v>15.95</v>
+        <v>15.74</v>
       </c>
       <c r="M37" s="14">
         <f>IF(AND(C37&gt;=K37,C37&lt;=L37),"Да | Yes","НЕ | NO")</f>
@@ -24684,13 +24765,13 @@
         <v>17.5</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="K38" s="13" t="n">
-        <v>15.96</v>
+        <v>15.75</v>
       </c>
       <c r="L38" s="13" t="n">
-        <v>19.04</v>
+        <v>19.25</v>
       </c>
       <c r="M38" s="12">
         <f>IF(AND(C38&gt;=K38,C38&lt;=L38),"Да | Yes","НЕ | NO")</f>
@@ -24840,20 +24921,20 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="I40" s="13" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>1.449999999999999</v>
+        <v>1.75</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>13.05</v>
+        <v>15.75</v>
       </c>
       <c r="L40" s="13" t="n">
-        <v>15.95</v>
+        <v>19.25</v>
       </c>
       <c r="M40" s="12">
         <f>IF(AND(C40&gt;=K40,C40&lt;=L40),"Да | Yes","НЕ | NO")</f>
@@ -24937,13 +25018,13 @@
         <v>14.5</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>1.449999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>13.05</v>
+        <v>13.26</v>
       </c>
       <c r="L41" s="15" t="n">
-        <v>15.95</v>
+        <v>15.74</v>
       </c>
       <c r="M41" s="14">
         <f>IF(AND(C41&gt;=K41,C41&lt;=L41),"Да | Yes","НЕ | NO")</f>
@@ -25027,13 +25108,13 @@
         <v>17.5</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>15.96</v>
+        <v>15.75</v>
       </c>
       <c r="L42" s="13" t="n">
-        <v>19.04</v>
+        <v>19.25</v>
       </c>
       <c r="M42" s="12">
         <f>IF(AND(C42&gt;=K42,C42&lt;=L42),"Да | Yes","НЕ | NO")</f>
@@ -25440,17 +25521,17 @@
       </c>
       <c r="S47" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T47" s="15" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="U47" s="15" t="n">
-        <v>15.3</v>
+        <v>18.51</v>
       </c>
       <c r="V47" s="15" t="n">
-        <v>18.7</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="48">
@@ -25537,10 +25618,10 @@
         <v>17</v>
       </c>
       <c r="U48" s="13" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="V48" s="13" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="49">
@@ -25853,17 +25934,17 @@
       </c>
       <c r="S52" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="T52" s="13" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="U52" s="13" t="n">
-        <v>15.3</v>
+        <v>18.51</v>
       </c>
       <c r="V52" s="13" t="n">
-        <v>18.7</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="53">
@@ -25950,10 +26031,10 @@
         <v>20.5</v>
       </c>
       <c r="U53" s="15" t="n">
-        <v>18.71</v>
+        <v>18.51</v>
       </c>
       <c r="V53" s="15" t="n">
-        <v>22.29</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="54">
@@ -26040,10 +26121,10 @@
         <v>20.5</v>
       </c>
       <c r="U54" s="13" t="n">
-        <v>18.71</v>
+        <v>18.51</v>
       </c>
       <c r="V54" s="13" t="n">
-        <v>22.29</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="55">
@@ -26130,10 +26211,10 @@
         <v>20.5</v>
       </c>
       <c r="U55" s="15" t="n">
-        <v>18.71</v>
+        <v>18.51</v>
       </c>
       <c r="V55" s="15" t="n">
-        <v>22.29</v>
+        <v>22.49</v>
       </c>
     </row>
     <row r="56">
@@ -26220,10 +26301,10 @@
         <v>17</v>
       </c>
       <c r="U56" s="13" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="V56" s="13" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="57">
@@ -26467,13 +26548,13 @@
         </is>
       </c>
       <c r="T59" s="15" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="U59" s="15" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="V59" s="15" t="n">
-        <v>26.7</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="60">
@@ -26609,13 +26690,13 @@
         <v>17.5</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>0.9400000000000004</v>
+        <v>1.39</v>
       </c>
       <c r="K61" s="15" t="n">
-        <v>16.56</v>
+        <v>16.11</v>
       </c>
       <c r="L61" s="15" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
       <c r="M61" s="14">
         <f>IF(AND(C61&gt;=K61,C61&lt;=L61),"Да | Yes","НЕ | NO")</f>
@@ -26686,16 +26767,16 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="M62" s="12">
         <f>IF(AND(C62&gt;=K62,C62&lt;=L62),"Да | Yes","НЕ | NO")</f>
@@ -26776,16 +26857,16 @@
         </is>
       </c>
       <c r="I63" s="15" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="J63" s="15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="K63" s="15" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="L63" s="15" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="M63" s="14">
         <f>IF(AND(C63&gt;=K63,C63&lt;=L63),"Да | Yes","НЕ | NO")</f>
@@ -26869,13 +26950,13 @@
         <v>17.5</v>
       </c>
       <c r="J64" s="13" t="n">
-        <v>0.9400000000000004</v>
+        <v>1.39</v>
       </c>
       <c r="K64" s="13" t="n">
-        <v>16.56</v>
+        <v>16.11</v>
       </c>
       <c r="L64" s="13" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
       <c r="M64" s="12">
         <f>IF(AND(C64&gt;=K64,C64&lt;=L64),"Да | Yes","НЕ | NO")</f>
@@ -26946,16 +27027,16 @@
         </is>
       </c>
       <c r="I65" s="15" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="J65" s="15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="K65" s="15" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="L65" s="15" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="M65" s="14">
         <f>IF(AND(C65&gt;=K65,C65&lt;=L65),"Да | Yes","НЕ | NO")</f>
@@ -27592,13 +27673,13 @@
         <v>17.5</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>0.9400000000000004</v>
+        <v>1.39</v>
       </c>
       <c r="K73" s="15" t="n">
-        <v>16.56</v>
+        <v>16.11</v>
       </c>
       <c r="L73" s="15" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
       <c r="M73" s="14">
         <f>IF(AND(C73&gt;=K73,C73&lt;=L73),"Да | Yes","НЕ | NO")</f>
@@ -27669,16 +27750,16 @@
         </is>
       </c>
       <c r="I74" s="13" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="J74" s="13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="K74" s="13" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="L74" s="13" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="M74" s="12">
         <f>IF(AND(C74&gt;=K74,C74&lt;=L74),"Да | Yes","НЕ | NO")</f>
@@ -27752,13 +27833,13 @@
         <v>17.5</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>0.9400000000000004</v>
+        <v>1.39</v>
       </c>
       <c r="K75" s="15" t="n">
-        <v>16.56</v>
+        <v>16.11</v>
       </c>
       <c r="L75" s="15" t="n">
-        <v>18.44</v>
+        <v>18.89</v>
       </c>
       <c r="M75" s="14">
         <f>IF(AND(C75&gt;=K75,C75&lt;=L75),"Да | Yes","НЕ | NO")</f>
@@ -27829,16 +27910,16 @@
         </is>
       </c>
       <c r="I76" s="13" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="J76" s="13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="K76" s="13" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="L76" s="13" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="M76" s="12">
         <f>IF(AND(C76&gt;=K76,C76&lt;=L76),"Да | Yes","НЕ | NO")</f>
@@ -27909,16 +27990,16 @@
         </is>
       </c>
       <c r="I77" s="15" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="K77" s="15" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="L77" s="15" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="M77" s="14">
         <f>IF(AND(C77&gt;=K77,C77&lt;=L77),"Да | Yes","НЕ | NO")</f>
@@ -27989,16 +28070,16 @@
         </is>
       </c>
       <c r="I78" s="13" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="J78" s="13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="K78" s="13" t="n">
-        <v>18.45</v>
+        <v>18.9</v>
       </c>
       <c r="L78" s="13" t="n">
-        <v>22.55</v>
+        <v>23.1</v>
       </c>
       <c r="M78" s="12">
         <f>IF(AND(C78&gt;=K78,C78&lt;=L78),"Да | Yes","НЕ | NO")</f>
@@ -28419,16 +28500,16 @@
         </is>
       </c>
       <c r="I83" s="15" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="K83" s="15" t="n">
-        <v>14.16</v>
+        <v>13.45</v>
       </c>
       <c r="L83" s="15" t="n">
-        <v>16.84</v>
+        <v>15.55</v>
       </c>
       <c r="M83" s="14">
         <f>IF(AND(C83&gt;=K83,C83&lt;=L83),"Да | Yes","НЕ | NO")</f>
@@ -28509,16 +28590,16 @@
         </is>
       </c>
       <c r="I84" s="13" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="J84" s="13" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="K84" s="13" t="n">
-        <v>14.16</v>
+        <v>13.45</v>
       </c>
       <c r="L84" s="13" t="n">
-        <v>16.84</v>
+        <v>15.55</v>
       </c>
       <c r="M84" s="12">
         <f>IF(AND(C84&gt;=K84,C84&lt;=L84),"Да | Yes","НЕ | NO")</f>
@@ -28595,20 +28676,20 @@
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="I85" s="15" t="n">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="K85" s="15" t="n">
-        <v>16.85</v>
+        <v>18.45</v>
       </c>
       <c r="L85" s="15" t="n">
-        <v>20.15</v>
+        <v>22.55</v>
       </c>
       <c r="M85" s="14">
         <f>IF(AND(C85&gt;=K85,C85&lt;=L85),"Да | Yes","НЕ | NO")</f>
@@ -28689,16 +28770,16 @@
         </is>
       </c>
       <c r="I86" s="13" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="J86" s="13" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="K86" s="13" t="n">
-        <v>16.85</v>
+        <v>15.56</v>
       </c>
       <c r="L86" s="13" t="n">
-        <v>20.15</v>
+        <v>18.44</v>
       </c>
       <c r="M86" s="12">
         <f>IF(AND(C86&gt;=K86,C86&lt;=L86),"Да | Yes","НЕ | NO")</f>
@@ -29045,20 +29126,20 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>Pot.-4</t>
+          <t>Pot.-5</t>
         </is>
       </c>
       <c r="I90" s="13" t="n">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="J90" s="13" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="K90" s="13" t="n">
-        <v>16.85</v>
+        <v>18.45</v>
       </c>
       <c r="L90" s="13" t="n">
-        <v>20.15</v>
+        <v>22.55</v>
       </c>
       <c r="M90" s="12">
         <f>IF(AND(C90&gt;=K90,C90&lt;=L90),"Да | Yes","НЕ | NO")</f>
@@ -29139,16 +29220,16 @@
         </is>
       </c>
       <c r="I91" s="15" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="K91" s="15" t="n">
-        <v>16.85</v>
+        <v>15.56</v>
       </c>
       <c r="L91" s="15" t="n">
-        <v>20.15</v>
+        <v>18.44</v>
       </c>
       <c r="M91" s="14">
         <f>IF(AND(C91&gt;=K91,C91&lt;=L91),"Да | Yes","НЕ | NO")</f>
@@ -29225,20 +29306,20 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-4</t>
         </is>
       </c>
       <c r="I92" s="13" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="J92" s="13" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="K92" s="13" t="n">
-        <v>14.16</v>
+        <v>15.56</v>
       </c>
       <c r="L92" s="13" t="n">
-        <v>16.84</v>
+        <v>18.44</v>
       </c>
       <c r="M92" s="12">
         <f>IF(AND(C92&gt;=K92,C92&lt;=L92),"Да | Yes","НЕ | NO")</f>

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -18436,13 +18436,13 @@
         <v>17</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>1</v>
@@ -18471,16 +18471,16 @@
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>18.51</v>
+        <v>18.41</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>22.49</v>
+        <v>21.59</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>4</v>
@@ -18509,16 +18509,16 @@
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>4</v>
@@ -18893,16 +18893,16 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>2</v>
@@ -19471,7 +19471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20269,16 +20269,16 @@
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>1.29</v>
+        <v>0.8</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>12.71</v>
+        <v>12.2</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>15.29</v>
+        <v>13.8</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>1</v>
@@ -20312,23 +20312,23 @@
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D23" s="15" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>15.3</v>
+        <v>13.81</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>18.7</v>
+        <v>16.19</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>GG1024_02, GG1024_01</t>
+          <t>GG1024_02</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -20346,32 +20346,32 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Gang</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E24" s="13" t="n">
-        <v>22.5</v>
+        <v>16.2</v>
       </c>
       <c r="F24" s="13" t="n">
-        <v>27.5</v>
+        <v>19.8</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>GP0824_02, GP0824_03, GP092501</t>
+          <t>GG1024_01</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Gorilla Glue</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr"/>
@@ -20389,7 +20389,7 @@
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
-          <t>Hazy Daze</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
@@ -20398,23 +20398,23 @@
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>20.5</v>
+        <v>24</v>
       </c>
       <c r="D25" s="15" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>18.45</v>
+        <v>21.6</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>22.55</v>
+        <v>26.4</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>HPA052501, HPA1024_01</t>
+          <t>GP0824_02, GP0824_03, GP092501</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Grape Pie</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr"/>
@@ -20432,7 +20432,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>High Pro Amnesia</t>
+          <t>Hazy Daze</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
@@ -20441,23 +20441,23 @@
         </is>
       </c>
       <c r="C26" s="13" t="n">
-        <v>17.5</v>
+        <v>20.5</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>15.75</v>
+        <v>18.45</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>19.25</v>
+        <v>22.55</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>HPA1024</t>
+          <t>HPA052501, HPA1024_01</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -20475,7 +20475,7 @@
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -20484,23 +20484,23 @@
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="D27" s="15" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>14.46</v>
+        <v>15.75</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>17.54</v>
+        <v>19.25</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>JD012603/02V</t>
+          <t>HPA1024</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -20510,7 +20510,7 @@
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>High Pro Amnesia</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr"/>
@@ -20523,27 +20523,27 @@
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C28" s="13" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="E28" s="13" t="n">
-        <v>17.55</v>
+        <v>14.46</v>
       </c>
       <c r="F28" s="13" t="n">
-        <v>21.45</v>
+        <v>17.54</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>JD012601, JD112501, JD012603/02</t>
+          <t>JD012603/02V</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -20561,32 +20561,32 @@
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="D29" s="15" t="n">
-        <v>1.39</v>
+        <v>1.95</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>16.11</v>
+        <v>17.55</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>18.89</v>
+        <v>21.45</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>J31102501</t>
+          <t>JD012601, JD112501, JD012603/02</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>Jokerz 31</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr"/>
@@ -20609,27 +20609,27 @@
       </c>
       <c r="B30" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>2.1</v>
+        <v>1.39</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>18.9</v>
+        <v>16.11</v>
       </c>
       <c r="F30" s="13" t="n">
-        <v>23.1</v>
+        <v>18.89</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>J31112501, J31122501</t>
+          <t>J31102501</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -20647,32 +20647,32 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D31" s="15" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>15.3</v>
+        <v>18.9</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>18.7</v>
+        <v>23.1</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>KC102501</t>
+          <t>J31112501, J31122501</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -20682,7 +20682,7 @@
       </c>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>Kush Crasher</t>
+          <t>Jokerz 31</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr"/>
@@ -20690,7 +20690,7 @@
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Lifeguard</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="B32" s="12" t="inlineStr">
@@ -20699,33 +20699,33 @@
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="D32" s="13" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>13.95</v>
+        <v>15.3</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>17.05</v>
+        <v>18.7</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>PUM102501</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>Pure Michigen</t>
+          <t>Kush Crasher</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr"/>
@@ -20733,7 +20733,7 @@
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
-          <t>NY Diesel</t>
+          <t>Lifeguard</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -20742,33 +20742,33 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="D33" s="15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>15.3</v>
+        <v>13.95</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>18.7</v>
+        <v>17.05</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>MB0824_05, MB0824_04</t>
+          <t>PUM102501</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>Motor Breath</t>
+          <t>Pure Michigen</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr"/>
@@ -20776,7 +20776,7 @@
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>OG Banana's</t>
+          <t>NY Diesel</t>
         </is>
       </c>
       <c r="B34" s="12" t="inlineStr">
@@ -20785,23 +20785,23 @@
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>13.8</v>
+        <v>16.2</v>
       </c>
       <c r="F34" s="13" t="n">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>CJ052501/02</t>
+          <t>MB0824_05, MB0824_04</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>Cap Junkie</t>
+          <t>Motor Breath</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr"/>
@@ -20824,27 +20824,27 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D35" s="15" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>16.21</v>
+        <v>13.8</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>19.79</v>
+        <v>16.2</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>CJ062501/2</t>
+          <t>CJ052501/02</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -20867,27 +20867,27 @@
       </c>
       <c r="B36" s="12" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D36" s="13" t="n">
-        <v>2.2</v>
+        <v>1.79</v>
       </c>
       <c r="E36" s="13" t="n">
-        <v>19.8</v>
+        <v>16.21</v>
       </c>
       <c r="F36" s="13" t="n">
-        <v>24.2</v>
+        <v>19.79</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>CJ062501/1</t>
+          <t>CJ062501/2</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -20905,32 +20905,32 @@
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Orange Dream</t>
+          <t>OG Banana's</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="C37" s="15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D37" s="15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>18</v>
+        <v>19.8</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>22</v>
+        <v>24.2</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>OPM1024</t>
+          <t>CJ062501/1</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Cap Junkie</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr"/>
@@ -20948,7 +20948,7 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>Payday</t>
+          <t>Orange Dream</t>
         </is>
       </c>
       <c r="B38" s="12" t="inlineStr">
@@ -20957,23 +20957,23 @@
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>12.16</v>
+        <v>18</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>14.84</v>
+        <v>22</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>CC012603, CC112501</t>
+          <t>OPM1024</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>CashCow</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr"/>
@@ -20996,27 +20996,27 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="D39" s="15" t="n">
-        <v>1.65</v>
+        <v>1.34</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>14.85</v>
+        <v>12.16</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>18.15</v>
+        <v>14.84</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>CC012601/1</t>
+          <t>CC012603, CC112501</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -21034,49 +21034,45 @@
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Plum Tarte</t>
+          <t>Payday</t>
         </is>
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="D40" s="13" t="n">
-        <v>0.7</v>
+        <v>1.65</v>
       </c>
       <c r="E40" s="13" t="n">
-        <v>6.3</v>
+        <v>14.85</v>
       </c>
       <c r="F40" s="13" t="n">
-        <v>7.7</v>
+        <v>18.15</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>GRC102501/1</t>
+          <t>CC012601/1</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>Grapes and Cream</t>
-        </is>
-      </c>
-      <c r="K40" s="12" t="inlineStr">
-        <is>
-          <t>НЕМА КЛАСА 7.70%–10.35% | NO GRADE 7.70%–10.35%</t>
-        </is>
-      </c>
+          <t>CashCow</t>
+        </is>
+      </c>
+      <c r="K40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -21086,32 +21082,32 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C41" s="15" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="D41" s="15" t="n">
-        <v>1.15</v>
+        <v>0.7</v>
       </c>
       <c r="E41" s="15" t="n">
-        <v>10.35</v>
+        <v>6.3</v>
       </c>
       <c r="F41" s="15" t="n">
-        <v>12.65</v>
+        <v>7.7</v>
       </c>
       <c r="G41" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>GRC102501/2</t>
+          <t>GRC102501/1</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
@@ -21119,37 +21115,41 @@
           <t>Grapes and Cream</t>
         </is>
       </c>
-      <c r="K41" s="14" t="inlineStr"/>
+      <c r="K41" s="14" t="inlineStr">
+        <is>
+          <t>НЕМА КЛАСА 7.70%–10.35% | NO GRADE 7.70%–10.35%</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Rainbow Sherbet</t>
+          <t>Plum Tarte</t>
         </is>
       </c>
       <c r="B42" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>2.2</v>
+        <v>1.15</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>19.8</v>
+        <v>10.35</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>24.2</v>
+        <v>12.65</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>SCR022601</t>
+          <t>GRC102501/2</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Grapes and Cream</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr"/>
@@ -21167,7 +21167,7 @@
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
-          <t>Scrambler</t>
+          <t>Rainbow Sherbet</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -21176,23 +21176,23 @@
         </is>
       </c>
       <c r="C43" s="15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D43" s="15" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
       <c r="F43" s="15" t="n">
-        <v>19.8</v>
+        <v>24.2</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>SCR112501, SCR012603, SCR012601</t>
+          <t>SCR022601</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -21210,7 +21210,7 @@
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>Shark Tank</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="B44" s="12" t="inlineStr">
@@ -21219,33 +21219,33 @@
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D44" s="13" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E44" s="13" t="n">
-        <v>9</v>
+        <v>16.2</v>
       </c>
       <c r="F44" s="13" t="n">
-        <v>11</v>
+        <v>19.8</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>CF102501</t>
+          <t>SCR112501, SCR012603, SCR012601</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>Chem Flyer</t>
+          <t>Scrambler</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr"/>
@@ -21253,7 +21253,7 @@
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Shark Tank</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -21262,33 +21262,33 @@
         </is>
       </c>
       <c r="C45" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F45" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="D45" s="15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>12.1</v>
-      </c>
       <c r="G45" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>SJ092501, SJ102501</t>
+          <t>CF102501</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Sleepy Joe</t>
+          <t>Chem Flyer</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr"/>
@@ -21296,7 +21296,7 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Soft Citrus Bloom</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="B46" s="12" t="inlineStr">
@@ -21305,23 +21305,23 @@
         </is>
       </c>
       <c r="C46" s="13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>0.54</v>
+        <v>1.1</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>7.46</v>
+        <v>9.9</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>8.539999999999999</v>
+        <v>12.1</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>OPM112501</t>
+          <t>SJ092501, SJ102501</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Sleepy Joe</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr"/>
@@ -21344,27 +21344,27 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C47" s="15" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="D47" s="15" t="n">
-        <v>0.95</v>
+        <v>0.54</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>8.550000000000001</v>
+        <v>7.46</v>
       </c>
       <c r="F47" s="15" t="n">
-        <v>10.45</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="G47" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>OPM092501</t>
+          <t>OPM112501</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -21382,42 +21382,42 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>Strawberry Cupcakes</t>
+          <t>Soft Citrus Bloom</t>
         </is>
       </c>
       <c r="B48" s="12" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>16.5</v>
+        <v>9.5</v>
       </c>
       <c r="D48" s="13" t="n">
-        <v>1.65</v>
+        <v>0.95</v>
       </c>
       <c r="E48" s="13" t="n">
-        <v>14.85</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="F48" s="13" t="n">
-        <v>18.15</v>
+        <v>10.45</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>JD012603/01</t>
+          <t>OPM092501</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>Jelly Donuts</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr"/>
@@ -21425,7 +21425,7 @@
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Sunset Sherbet</t>
+          <t>Strawberry Cupcakes</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -21434,33 +21434,33 @@
         </is>
       </c>
       <c r="C49" s="15" t="n">
-        <v>20.5</v>
+        <v>16.5</v>
       </c>
       <c r="D49" s="15" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>18.96</v>
+        <v>14.85</v>
       </c>
       <c r="F49" s="15" t="n">
-        <v>22.04</v>
+        <v>18.15</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>BSS052501</t>
+          <t>JD012603/01</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>Blue Sunset Sherbet</t>
+          <t>Jelly Donuts</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr"/>
@@ -21473,27 +21473,27 @@
       </c>
       <c r="B50" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>24.5</v>
+        <v>20.5</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>2.45</v>
+        <v>1.54</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>22.05</v>
+        <v>18.96</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>26.95</v>
+        <v>22.04</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>BSS1024_01/1, BSS1024</t>
+          <t>BSS052501</t>
         </is>
       </c>
       <c r="I50" s="12" t="inlineStr">
@@ -21511,32 +21511,32 @@
     <row r="51">
       <c r="A51" s="14" t="inlineStr">
         <is>
-          <t>Tangie Queen</t>
+          <t>Sunset Sherbet</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Pot.-1</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C51" s="15" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="D51" s="15" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="E51" s="15" t="n">
-        <v>15.3</v>
+        <v>22.05</v>
       </c>
       <c r="F51" s="15" t="n">
-        <v>18.7</v>
+        <v>26.95</v>
       </c>
       <c r="G51" s="14" t="n">
         <v>2</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>OPM1024_03, OPM1024_02</t>
+          <t>BSS1024_01/1, BSS1024</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Orange Punch Mimosa</t>
+          <t>Blue Sunset Sherbet</t>
         </is>
       </c>
       <c r="K51" s="14" t="inlineStr"/>
@@ -21554,7 +21554,7 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>Tropic Cake</t>
+          <t>Tangie Queen</t>
         </is>
       </c>
       <c r="B52" s="12" t="inlineStr">
@@ -21563,33 +21563,33 @@
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D52" s="13" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="E52" s="13" t="n">
-        <v>19.8</v>
+        <v>15.3</v>
       </c>
       <c r="F52" s="13" t="n">
-        <v>24.2</v>
+        <v>18.7</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>WED102501</t>
+          <t>OPM1024_03, OPM1024_02</t>
         </is>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>ПРОВИЗОРНО | PROVISIONAL</t>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>Wedding Cake</t>
+          <t>Orange Punch Mimosa</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr"/>
@@ -21597,7 +21597,7 @@
     <row r="53">
       <c r="A53" s="14" t="inlineStr">
         <is>
-          <t>Vanilla Grapes</t>
+          <t>Tropic Cake</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -21606,33 +21606,33 @@
         </is>
       </c>
       <c r="C53" s="15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D53" s="15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>15.5</v>
+        <v>19.8</v>
       </c>
       <c r="F53" s="15" t="n">
-        <v>18.5</v>
+        <v>24.2</v>
       </c>
       <c r="G53" s="14" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>GP082501/2</t>
+          <t>WED102501</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+          <t>ПРОВИЗОРНО | PROVISIONAL</t>
         </is>
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>Grape Pie</t>
+          <t>Wedding Cake</t>
         </is>
       </c>
       <c r="K53" s="14" t="inlineStr"/>
@@ -21645,27 +21645,27 @@
       </c>
       <c r="B54" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-1</t>
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>18.51</v>
+        <v>15.5</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>22.49</v>
+        <v>18.5</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
+          <t>GP082501/2</t>
         </is>
       </c>
       <c r="I54" s="12" t="inlineStr">
@@ -21688,27 +21688,27 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Pot.-3</t>
+          <t>Pot.-2</t>
         </is>
       </c>
       <c r="C55" s="15" t="n">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="D55" s="15" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>22.5</v>
+        <v>18.51</v>
       </c>
       <c r="F55" s="15" t="n">
-        <v>27.5</v>
+        <v>22.49</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>GP062501</t>
+          <t>GP052501, GP072501/2, GP082501/1, GP072501/1</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
@@ -21726,45 +21726,88 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="inlineStr">
+        <is>
+          <t>ДЕФИНИТИВНО | DEFINITIVE</t>
+        </is>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
           <t>Wedding Crusher</t>
         </is>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>Pot.-1</t>
         </is>
       </c>
-      <c r="C56" s="13" t="n">
+      <c r="C57" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D57" s="15" t="n">
         <v>2.2</v>
       </c>
-      <c r="E56" s="13" t="n">
+      <c r="E57" s="15" t="n">
         <v>19.8</v>
       </c>
-      <c r="F56" s="13" t="n">
+      <c r="F57" s="15" t="n">
         <v>24.2</v>
       </c>
-      <c r="G56" s="12" t="n">
+      <c r="G57" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="H57" s="14" t="inlineStr">
         <is>
           <t>WC082501, WC072501</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>ДЕФИНИТИВНО | DEFINITIVE</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="J57" s="14" t="inlineStr">
         <is>
           <t>Wedding Crusher</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr"/>
+      <c r="K57" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -24459,17 +24502,17 @@
       </c>
       <c r="S34" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T34" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U34" s="13" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="V34" s="13" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="35">
@@ -24799,17 +24842,17 @@
       </c>
       <c r="S38" s="12" t="inlineStr">
         <is>
-          <t>Pot.-2</t>
+          <t>Pot.-3</t>
         </is>
       </c>
       <c r="T38" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U38" s="13" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="V38" s="13" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="39">
@@ -24966,13 +25009,13 @@
         </is>
       </c>
       <c r="T40" s="13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U40" s="13" t="n">
-        <v>15.3</v>
+        <v>13.81</v>
       </c>
       <c r="V40" s="13" t="n">
-        <v>18.7</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="41">
@@ -25056,13 +25099,13 @@
         </is>
       </c>
       <c r="T41" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U41" s="15" t="n">
-        <v>12.71</v>
+        <v>12.2</v>
       </c>
       <c r="V41" s="15" t="n">
-        <v>15.29</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="42">
@@ -25404,16 +25447,16 @@
         </is>
       </c>
       <c r="I46" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K46" s="13" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="L46" s="13" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="M46" s="12">
         <f>IF(AND(C46&gt;=K46,C46&lt;=L46),"Да | Yes","НЕ | NO")</f>
@@ -25484,16 +25527,16 @@
         </is>
       </c>
       <c r="I47" s="15" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="K47" s="15" t="n">
-        <v>18.51</v>
+        <v>18.41</v>
       </c>
       <c r="L47" s="15" t="n">
-        <v>22.49</v>
+        <v>21.59</v>
       </c>
       <c r="M47" s="14">
         <f>IF(AND(C47&gt;=K47,C47&lt;=L47),"Да | Yes","НЕ | NO")</f>
@@ -25577,13 +25620,13 @@
         <v>17</v>
       </c>
       <c r="J48" s="13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K48" s="13" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="L48" s="13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="M48" s="12">
         <f>IF(AND(C48&gt;=K48,C48&lt;=L48),"Да | Yes","НЕ | NO")</f>
@@ -25664,16 +25707,16 @@
         </is>
       </c>
       <c r="I49" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K49" s="15" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="L49" s="15" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="M49" s="14">
         <f>IF(AND(C49&gt;=K49,C49&lt;=L49),"Да | Yes","НЕ | NO")</f>
@@ -25744,16 +25787,16 @@
         </is>
       </c>
       <c r="I50" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J50" s="13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K50" s="13" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="L50" s="13" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="M50" s="12">
         <f>IF(AND(C50&gt;=K50,C50&lt;=L50),"Да | Yes","НЕ | NO")</f>
@@ -25897,16 +25940,16 @@
         </is>
       </c>
       <c r="I52" s="13" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="J52" s="13" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="K52" s="13" t="n">
-        <v>18.51</v>
+        <v>18.41</v>
       </c>
       <c r="L52" s="13" t="n">
-        <v>22.49</v>
+        <v>21.59</v>
       </c>
       <c r="M52" s="12">
         <f>IF(AND(C52&gt;=K52,C52&lt;=L52),"Да | Yes","НЕ | NO")</f>
@@ -25987,16 +26030,16 @@
         </is>
       </c>
       <c r="I53" s="15" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="K53" s="15" t="n">
-        <v>18.51</v>
+        <v>18.41</v>
       </c>
       <c r="L53" s="15" t="n">
-        <v>22.49</v>
+        <v>21.59</v>
       </c>
       <c r="M53" s="14">
         <f>IF(AND(C53&gt;=K53,C53&lt;=L53),"Да | Yes","НЕ | NO")</f>
@@ -26077,16 +26120,16 @@
         </is>
       </c>
       <c r="I54" s="13" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="J54" s="13" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="K54" s="13" t="n">
-        <v>18.51</v>
+        <v>18.41</v>
       </c>
       <c r="L54" s="13" t="n">
-        <v>22.49</v>
+        <v>21.59</v>
       </c>
       <c r="M54" s="12">
         <f>IF(AND(C54&gt;=K54,C54&lt;=L54),"Да | Yes","НЕ | NO")</f>
@@ -26167,16 +26210,16 @@
         </is>
       </c>
       <c r="I55" s="15" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>1.99</v>
+        <v>1.59</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>18.51</v>
+        <v>18.41</v>
       </c>
       <c r="L55" s="15" t="n">
-        <v>22.49</v>
+        <v>21.59</v>
       </c>
       <c r="M55" s="14">
         <f>IF(AND(C55&gt;=K55,C55&lt;=L55),"Да | Yes","НЕ | NO")</f>
@@ -26260,13 +26303,13 @@
         <v>17</v>
       </c>
       <c r="J56" s="13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K56" s="13" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="L56" s="13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="M56" s="12">
         <f>IF(AND(C56&gt;=K56,C56&lt;=L56),"Да | Yes","НЕ | NO")</f>
@@ -26347,16 +26390,16 @@
         </is>
       </c>
       <c r="I57" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K57" s="15" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="L57" s="15" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="M57" s="14">
         <f>IF(AND(C57&gt;=K57,C57&lt;=L57),"Да | Yes","НЕ | NO")</f>
@@ -26427,16 +26470,16 @@
         </is>
       </c>
       <c r="I58" s="13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J58" s="13" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K58" s="13" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="L58" s="13" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="M58" s="12">
         <f>IF(AND(C58&gt;=K58,C58&lt;=L58),"Да | Yes","НЕ | NO")</f>
@@ -26507,16 +26550,16 @@
         </is>
       </c>
       <c r="I59" s="15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="K59" s="15" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="L59" s="15" t="n">
-        <v>27.5</v>
+        <v>26.4</v>
       </c>
       <c r="M59" s="14">
         <f>IF(AND(C59&gt;=K59,C59&lt;=L59),"Да | Yes","НЕ | NO")</f>
@@ -28230,16 +28273,16 @@
         </is>
       </c>
       <c r="I80" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J80" s="13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K80" s="13" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="L80" s="13" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
       <c r="M80" s="12">
         <f>IF(AND(C80&gt;=K80,C80&lt;=L80),"Да | Yes","НЕ | NO")</f>
@@ -28271,13 +28314,13 @@
         </is>
       </c>
       <c r="T80" s="13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U80" s="13" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="V80" s="13" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="81">
@@ -28320,16 +28363,16 @@
         </is>
       </c>
       <c r="I81" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K81" s="15" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="L81" s="15" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
       <c r="M81" s="14">
         <f>IF(AND(C81&gt;=K81,C81&lt;=L81),"Да | Yes","НЕ | NO")</f>
@@ -28361,13 +28404,13 @@
         </is>
       </c>
       <c r="T81" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U81" s="15" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="V81" s="15" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="82">

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -10,10 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Original Strain Specs" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Renamed Strain Specs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Master — Renames" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atlas Grades — Original" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atlas Grades — Renamed" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potency Test Results" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specs × Batches — Original" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specs × Batches — Renamed" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio Master — Renames" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atlas Grades — Original" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atlas Grades — Renamed" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potency Test Results" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -85,7 +87,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -100,6 +102,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4F7FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECEA"/>
       </patternFill>
     </fill>
   </fills>
@@ -129,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -162,6 +169,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -14195,6 +14203,8070 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Спецификации и серии во лимитите — оригинални имиња</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Specifications &amp; Batches Within Limits — Original Names</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>За секоја сорта: сите издадени QCSP 001 спецификации (номинала, толеранција, опсег) и сериите чие сидро (најнов верификуван резултат; декларирана вредност каде нема сертификат — означено) паѓа во лимитите на таа спецификација.  |  Per strain: every issued QCSP 001 specification (nominal, tolerance, range) and the batches whose anchor (most recent verified result; declared value where no certificate — flagged) falls within that specification's limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Сорта | Strain</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Класа | Grade</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Код на документ | Doc Code</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Номинала (печатена) | Nominal (as printed)</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Номинала THC | Nominal THC</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Толеранција | Tolerance</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>THC-опсег | THC Range</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Серии во лимитите (сидро) | Batches within limits (anchor)</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>Бр. | #</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_ACC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_ACC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_ACC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_ACC-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>ACC102501 (12.91% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Apple and Banana</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_AB-I_v.01</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Apple and Banana</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_AB-II_v.01</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Apple and Banana</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_AB-III_v.01</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>AB092501 (16.93%)</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Blue Gelato</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_BG-I_v.01</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.38%</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>25.25% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>BG1024 (26.14%)</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Blue Gelato</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_BG-II_v.01</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.22%</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>20.80% – 25.25%</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_BSS-I_v.01</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>24.75% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>BSS1024 (25.01%)</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_BSS-II_v.01</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.68%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>19.39% – 24.75%</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>BSS052501 (20.39%), BSS1024_01/1 (23.42% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CJ-I_v.01</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.38%</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>25.25% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CJ-II_v.01</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>19.75% – 25.25%</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>CJ052501/01 (24.05%), CJ062501/1 (21.51%), CJ082501/1 (24.96%), CJ092501 (22.30%), CJ072501 (23.70%), CJ1024 (23.00%)</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CJ-III_v.01</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>17.00% ± 2.91%</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>13.93% – 19.75%</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>CJ062501/2 (18.91%), CJ082501/2 (18.29%), CJ052501/02 (14.93%)</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.25%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>25.50% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>20.50% – 25.50%</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>18.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>15.50% – 20.50%</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>CC012601/1 (17.67%)</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Cash Cow</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>надвор од сите класи | outside all grades</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>CC012603 (12.32% декл. | decl.), CC112501 (13.35%)</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CF-I_v.01</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CF-II_v.01</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CF-III_v.01</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CF-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>CF102501 (9.83% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CLE-I_v.01</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CLE-II_v.01</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CLE-III_v.01</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CLE-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>12.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>10.00% – 15.00%</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Clemosa a bud</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Grade V</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CLE-V_v.01</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>7.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>5.00% – 10.00%</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>CLE072501 (8.02%)</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_FB-I_v.01</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>24.75% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_FB-II_v.01</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>19.25% – 24.75%</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>FB012603 (20.83%)</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_FB-III_v.01</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>16.50% ± 2.79%</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>13.68% – 19.25%</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>FB012602 (18.86%), FB012601/1 (14.68%), FB012603V (18.29%), FB112501 (16.69%)</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GG-I_v.01</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>27.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>24.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GG-II_v.01</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>21.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>18.00% – 24.00%</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>GG1024_01 (18.67%)</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GG-III_v.01</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>15.00% ± 2.83%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>12.34% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>GG012603 (16.70%), GG1024 (13.34%), GG012601 (15.35%), GG112501 (17.94%), GG1024_02 (15.95%)</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GP-I_v.01</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>26.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GP-II_v.01</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>22.00% – 26.00%</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>GP0824_02 (22.61%), GP0824_03 (25.45%), GP092501 (25.73%), GP062501 (24.89%)</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GP-III_v.01</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>20.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>18.00% – 22.00%</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>GP052501 (18.52%), GP072501/2 (19.81%), GP082501/1 (21.29%), GP072501/1 (21.36%)</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GP-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>16.00% ± 2.08%</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>13.83% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>GP082501/2 (15.70%)</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GRC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GRC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GRC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GRC-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>12.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>10.00% – 15.00%</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>GRC102501/2 (11.53%)</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Graps &amp; Creme</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>надвор од сите класи | outside all grades</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>GRC102501/1 (7.05% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I47" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_HPA-I_v.01</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>24.75% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_HPA-II_v.01</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.68%</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>19.39% – 24.75%</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>HPA1024_01 (21.61%), HPA052501 (20.39%)</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_HPA-III_v.01</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>16.00% ± 2.95%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>13.50% – 19.39%</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>HPA1024 (17.31%)</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_JD-I_v.01</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>26.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_JD-II_v.01</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>22.00% – 26.00%</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_JD-III_v.01</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>20.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>18.00% – 22.00%</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>JD112501 (20.32%), JD012603/02 (20.54%), JD012601 (18.16%)</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Jelly Donutz</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_JD-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>15.00% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>12.50% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>JD012603/01 (16.71% декл. | decl.), JD012603/02V (15.16%)</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_J31-I_v.01</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>27.00% ± 3.25%</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>23.50% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_J31-II_v.01</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>20.00% ± 3.50%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>16.50% – 23.50%</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>J31102501 (17.32%), J31112501 (20.21%), J31122501 (21.84%)</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_KC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_KC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_KC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F59" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>KC102501 (17.04%)</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_MB-I_v.01</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_MB-II_v.01</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_MB-III_v.01</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="inlineStr">
+        <is>
+          <t>MB0824_05 (16.82%), MB0824_04 (18.67%)</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_OPM-I_v.01</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_OPM-II_v.01</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>22.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>19.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>OPM1024 (20.03%)</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_OPM-III_v.01</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>16.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F65" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>13.00% – 19.00%</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>OPM1024_02 (18.04%), OMP1024_01 (15.38%), OPM1024_03 (16.55%), OPM052501 (14.16%)</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_OPM-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>10.00% ± 2.96%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>7.09% – 13.00%</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>OPM122501 (7.91%), OPM092501 (9.43%), OPM112501 (8.00%)</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_PM-I_v.01</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>26.50% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F67" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>24.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PM-II_v.01</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>21.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>19.00% – 24.00%</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_PM-III_v.01</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="inlineStr">
+        <is>
+          <t>16.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F69" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>14.00% – 19.00%</t>
+        </is>
+      </c>
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PM-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>11.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>9.01% – 14.00%</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>PM092501 (12.25%), PM112501 (13.33%), PM072501 (10.01%)</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_PUM-I_v.01</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F71" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PUM-II_v.01</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_PUM-III_v.01</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F73" s="15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PUM-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F74" s="13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H74" s="12" t="inlineStr">
+        <is>
+          <t>PUM102501 (15.63% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_SCR-I_v.01</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.38%</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F75" s="15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>25.25% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_SCR-II_v.01</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.25%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>20.75% – 25.25%</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>SCR022601 (21.92%)</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_SCR-III_v.01</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>18.50% ± 2.31%</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F77" s="15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>16.13% – 20.75%</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>SCR012603 (17.84%), SCR112501 (17.13%), SCR012601 (18.07% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_SJ-I_v.01</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>27.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>24.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_SJ-II_v.01</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>21.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>18.00% – 24.00%</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_SJ-III_v.01</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>15.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>13.00% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Sleepy Joy</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_SJ-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>10.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>7.75% – 13.00%</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>SJ092501 (10.96%), SJ102501 (11.20%), SJ112501 (9.20%)</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="12" t="n"/>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>WED102501 (22.05% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_WC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F83" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_WC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>WC082501 (21.67%), WC072501 (22.11%)</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>Wedding Crasher</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_WC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Спецификации и серии во лимитите — нови имиња</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Specifications &amp; Batches Within Limits — New Names</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>За секоја сорта: сите издадени QCSP 001 спецификации (номинала, толеранција, опсег) и сериите чие сидро (најнов верификуван резултат; декларирана вредност каде нема сертификат — означено) паѓа во лимитите на таа спецификација.  |  Per strain: every issued QCSP 001 specification (nominal, tolerance, range) and the batches whose anchor (most recent verified result; declared value where no certificate — flagged) falls within that specification's limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Сорта | Strain</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Класа | Grade</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Код на документ | Doc Code</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Номинала (печатена) | Nominal (as printed)</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Номинала THC | Nominal THC</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Толеранција | Tolerance</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>THC-опсег | THC Range</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Серии во лимитите (сидро) | Batches within limits (anchor)</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>Бр. | #</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>Оригинално(и) име(иња) | Original name(s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Amnesia Core</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_AC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Amnesia Core</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_AC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Amnesia Core</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_AC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Amnesia Core</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_AC-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>ACC102501 (12.91% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Appels &amp; Bananas</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>AB092501 (16.93%)</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="12" t="inlineStr">
+        <is>
+          <t>Appels &amp; Bananas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Blue Gelato</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>BG1024 (26.14%)</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="14" t="inlineStr">
+        <is>
+          <t>Blue Gelato</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Calmino</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CAL-I_v.01</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>27.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>24.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Calmino</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CAL-II_v.01</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>21.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>18.00% – 24.00%</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Calmino</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CAL-III_v.01</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>15.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>13.00% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Calmino</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CAL-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>10.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>7.75% – 13.00%</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>SJ112501 (9.20%)</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="14" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Cherry Chocolate</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CHC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>27.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>27</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>24.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H16" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Cherry Chocolate</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CHC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>21.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>18.00% – 24.00%</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="14" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Cherry Chocolate</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CHC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>15.00% ± 2.83%</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>12.34% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>GG112501 (17.94%)</t>
+        </is>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CB-I_v.01</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CB-II_v.01</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>22.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>19.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CB-III_v.01</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>16.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>13.00% – 19.00%</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>OMP1024_01 (15.38%), OPM052501 (14.16%)</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CB-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>10.00% ± 2.96%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>7.09% – 13.00%</t>
+        </is>
+      </c>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>OPM122501 (7.91%)</t>
+        </is>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Clemosa</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>CLE072501 (8.02%)</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="14" t="inlineStr">
+        <is>
+          <t>Clemosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CK-I_v.01</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.38%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>25.25% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H24" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_CK-II_v.01</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>19.75% – 25.25%</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>CJ052501/01 (24.05%), CJ082501/1 (24.96%), CJ092501 (22.30%), CJ072501 (23.70%), CJ1024 (23.00%)</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" s="14" t="inlineStr">
+        <is>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_CK-III_v.01</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>17.00% ± 2.91%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>13.93% – 19.75%</t>
+        </is>
+      </c>
+      <c r="H26" s="12" t="inlineStr">
+        <is>
+          <t>CJ082501/2 (18.29%)</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="12" t="inlineStr">
+        <is>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Daywalker</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_DW-I_v.01</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>24.75% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Daywalker</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_DW-II_v.01</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>19.25% – 24.75%</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>FB012603 (20.83%)</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Daywalker</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_DW-III_v.01</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="inlineStr">
+        <is>
+          <t>16.50% ± 2.79%</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>13.68% – 19.25%</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>FB012601/1 (14.68%), FB012603V (18.29%)</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Fat Sofa</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_FS-I_v.01</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>24.75% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Fat Sofa</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_FS-II_v.01</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>19.25% – 24.75%</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>Fat Sofa</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_FS-III_v.01</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>16.50% ± 2.79%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>13.68% – 19.25%</t>
+        </is>
+      </c>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>FB012602 (18.86%), FB112501 (16.69%)</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Formula 1</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_F1-I_v.01</t>
+        </is>
+      </c>
+      <c r="D33" s="14" t="inlineStr">
+        <is>
+          <t>26.50% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>24.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="14" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Formula 1</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_F1-II_v.01</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>21.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>19.00% – 24.00%</t>
+        </is>
+      </c>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Formula 1</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_F1-III_v.01</t>
+        </is>
+      </c>
+      <c r="D35" s="14" t="inlineStr">
+        <is>
+          <t>16.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>14.00% – 19.00%</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="14" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Formula 1</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_F1-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>11.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>9.01% – 14.00%</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>PM092501 (12.25%), PM112501 (13.33%), PM072501 (10.01%)</t>
+        </is>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="12" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GG4-I_v.01</t>
+        </is>
+      </c>
+      <c r="D37" s="14" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="14" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GG4-II_v.01</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GG4-III_v.01</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>GG012603 (16.70%)</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GG4-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H40" s="12" t="inlineStr">
+        <is>
+          <t>GG012601 (15.35%)</t>
+        </is>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Gorilla Gang</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GNG-I_v.01</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>27.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>24.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t>Gorilla Gang</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_GNG-II_v.01</t>
+        </is>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>21.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>21</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>18.00% – 24.00%</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>GG1024_01 (18.67%)</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Gorilla Gang</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_GNG-III_v.01</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="inlineStr">
+        <is>
+          <t>15.00% ± 2.83%</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>12.34% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>GG1024 (13.34%), GG1024_02 (15.95%)</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J43" s="14" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>GP0824_02 (22.61%), GP0824_03 (25.45%), GP092501 (25.73%)</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Hazy Daze</t>
+        </is>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_HD-I_v.01</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>24.75% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>Hazy Daze</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_HD-II_v.01</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.68%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>19.39% – 24.75%</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>HPA1024_01 (21.61%), HPA052501 (20.39%)</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Hazy Daze</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_HD-III_v.01</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="inlineStr">
+        <is>
+          <t>16.00% ± 2.95%</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>13.50% – 19.39%</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="12" t="n"/>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="12" t="inlineStr">
+        <is>
+          <t>HPA1024 (17.31%)</t>
+        </is>
+      </c>
+      <c r="I48" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="12" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="14" t="n"/>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>JD112501 (20.32%), JD012603/02 (20.54%), JD012603/02V (15.16%), JD012601 (18.16%)</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J49" s="14" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="12" t="inlineStr">
+        <is>
+          <t>J31102501 (17.32%), J31112501 (20.21%), J31122501 (21.84%)</t>
+        </is>
+      </c>
+      <c r="I50" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" s="12" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="14" t="n"/>
+      <c r="F51" s="14" t="n"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>KC102501 (17.04%)</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="12" t="inlineStr">
+        <is>
+          <t>Lifeguard</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_LG-I_v.01</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F52" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H52" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="12" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Lifeguard</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_LG-II_v.01</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="14" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>Lifeguard</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_LG-III_v.01</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H54" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I54" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="12" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Lifeguard</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_LG-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F55" s="15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>PUM102501 (15.63% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="14" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="12" t="inlineStr">
+        <is>
+          <t>NY Diesel</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_NYD-I_v.01</t>
+        </is>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H56" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="12" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>NY Diesel</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_NYD-II_v.01</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="14" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>NY Diesel</t>
+        </is>
+      </c>
+      <c r="B58" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C58" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_NYD-III_v.01</t>
+        </is>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H58" s="12" t="inlineStr">
+        <is>
+          <t>MB0824_05 (16.82%), MB0824_04 (18.67%)</t>
+        </is>
+      </c>
+      <c r="I58" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" s="12" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>OG Banana's</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_OGB-I_v.01</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.38%</t>
+        </is>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="F59" s="15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>25.25% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="14" t="inlineStr">
+        <is>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>OG Banana's</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_OGB-II_v.01</t>
+        </is>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>19.75% – 25.25%</t>
+        </is>
+      </c>
+      <c r="H60" s="12" t="inlineStr">
+        <is>
+          <t>CJ062501/1 (21.51%)</t>
+        </is>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>OG Banana's</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_OGB-III_v.01</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="inlineStr">
+        <is>
+          <t>17.00% ± 2.91%</t>
+        </is>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>13.93% – 19.75%</t>
+        </is>
+      </c>
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>CJ062501/2 (18.91%), CJ052501/02 (14.93%)</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" s="14" t="inlineStr">
+        <is>
+          <t>Cap Junkie</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Orange Dream</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_OD-I_v.01</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H62" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Orange Dream</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_OD-II_v.01</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>22.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F63" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>19.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>OPM1024 (20.03%)</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Orange Dream</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_OD-III_v.01</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>16.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>13.00% – 19.00%</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Orange Dream</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_OD-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="inlineStr">
+        <is>
+          <t>10.00% ± 2.96%</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F65" s="15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>7.09% – 13.00%</t>
+        </is>
+      </c>
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Payday</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PDY-I_v.01</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.25%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>25.50% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H66" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>CashCow</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Payday</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_PDY-II_v.01</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="F67" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>20.50% – 25.50%</t>
+        </is>
+      </c>
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14" t="inlineStr">
+        <is>
+          <t>CashCow</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Payday</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PDY-III_v.01</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>18.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>15.50% – 20.50%</t>
+        </is>
+      </c>
+      <c r="H68" s="12" t="inlineStr">
+        <is>
+          <t>CC012601/1 (17.67%)</t>
+        </is>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>CashCow</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="inlineStr">
+        <is>
+          <t>Payday</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>надвор од сите класи | outside all grades</t>
+        </is>
+      </c>
+      <c r="D69" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="16" t="n"/>
+      <c r="F69" s="16" t="n"/>
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="16" t="inlineStr">
+        <is>
+          <t>CC012603 (12.32% декл. | decl.), CC112501 (13.35%)</t>
+        </is>
+      </c>
+      <c r="I69" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>CashCow</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>Plum Tarte</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PT-I_v.01</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H70" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Plum Tarte</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_PT-II_v.01</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="inlineStr">
+        <is>
+          <t>22.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F71" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>20.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>Plum Tarte</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_PT-III_v.01</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>17.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>15.00% – 20.00%</t>
+        </is>
+      </c>
+      <c r="H72" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Plum Tarte</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_PT-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="inlineStr">
+        <is>
+          <t>12.50% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F73" s="15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>10.00% – 15.00%</t>
+        </is>
+      </c>
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>GRC102501/2 (11.53%)</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="14" t="inlineStr">
+        <is>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>Plum Tarte</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>надвор од сите класи | outside all grades</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="n"/>
+      <c r="F74" s="16" t="n"/>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="16" t="inlineStr">
+        <is>
+          <t>GRC102501/1 (7.05% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I74" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Rainbow Sherbet</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_RSB-I_v.01</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.38%</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F75" s="15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>25.25% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="14" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Rainbow Sherbet</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_RSB-II_v.01</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.25%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="n">
+        <v>23</v>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>20.75% – 25.25%</t>
+        </is>
+      </c>
+      <c r="H76" s="12" t="inlineStr">
+        <is>
+          <t>SCR022601 (21.92%)</t>
+        </is>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="12" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Rainbow Sherbet</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_RSB-III_v.01</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="inlineStr">
+        <is>
+          <t>18.50% ± 2.31%</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F77" s="15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>16.13% – 20.75%</t>
+        </is>
+      </c>
+      <c r="H77" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I77" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="12" t="n"/>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="12" t="inlineStr">
+        <is>
+          <t>SCR012603 (17.84%), SCR112501 (17.13%), SCR012601 (18.07% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I78" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Shark Tank</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_ST-I_v.01</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G79" s="14" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="14" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Shark Tank</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_ST-II_v.01</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Shark Tank</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_ST-III_v.01</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F81" s="15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G81" s="14" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H81" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="14" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>Shark Tank</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_ST-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F82" s="13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H82" s="12" t="inlineStr">
+        <is>
+          <t>CF102501 (9.83% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="n"/>
+      <c r="F83" s="14" t="n"/>
+      <c r="G83" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H83" s="14" t="inlineStr">
+        <is>
+          <t>SJ092501 (10.96%), SJ102501 (11.20%)</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>Soft Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_SCB-I_v.01</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F84" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H84" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>Soft Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B85" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_SCB-II_v.01</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="inlineStr">
+        <is>
+          <t>22.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F85" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="14" t="inlineStr">
+        <is>
+          <t>19.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H85" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>Soft Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_SCB-III_v.01</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>16.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F86" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>13.00% – 19.00%</t>
+        </is>
+      </c>
+      <c r="H86" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Soft Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_SCB-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>10.00% ± 2.96%</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F87" s="15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>7.09% – 13.00%</t>
+        </is>
+      </c>
+      <c r="H87" s="14" t="inlineStr">
+        <is>
+          <t>OPM092501 (9.43%), OPM112501 (8.00%)</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J87" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>Strawberry Cupcakes</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_STC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F88" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>26.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H88" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>Strawberry Cupcakes</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_STC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
+        <is>
+          <t>22.00% – 26.00%</t>
+        </is>
+      </c>
+      <c r="H89" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I89" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="14" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>Strawberry Cupcakes</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_STC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>20.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F90" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>18.00% – 22.00%</t>
+        </is>
+      </c>
+      <c r="H90" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>Strawberry Cupcakes</t>
+        </is>
+      </c>
+      <c r="B91" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_STC-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="inlineStr">
+        <is>
+          <t>15.00% ± 2.75%</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F91" s="15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G91" s="14" t="inlineStr">
+        <is>
+          <t>12.50% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H91" s="14" t="inlineStr">
+        <is>
+          <t>JD012603/01 (16.71% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I91" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="14" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_SUN-I_v.01</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>27.50% ± 2.63%</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F92" s="13" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>24.75% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H92" s="12" t="inlineStr">
+        <is>
+          <t>BSS1024 (25.01%)</t>
+        </is>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_SUN-II_v.01</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.68%</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F93" s="15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G93" s="14" t="inlineStr">
+        <is>
+          <t>19.39% – 24.75%</t>
+        </is>
+      </c>
+      <c r="H93" s="14" t="inlineStr">
+        <is>
+          <t>BSS052501 (20.39%), BSS1024_01/1 (23.42% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I93" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" s="14" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Tangie Queen</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_TQ-I_v.01</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.50%</t>
+        </is>
+      </c>
+      <c r="E94" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F94" s="13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>25.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H94" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>Tangie Queen</t>
+        </is>
+      </c>
+      <c r="B95" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_TQ-II_v.01</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="inlineStr">
+        <is>
+          <t>22.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="F95" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G95" s="14" t="inlineStr">
+        <is>
+          <t>19.00% – 25.00%</t>
+        </is>
+      </c>
+      <c r="H95" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I95" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>Tangie Queen</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_TQ-III_v.01</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>16.00% ± 3.00%</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="n">
+        <v>16</v>
+      </c>
+      <c r="F96" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>13.00% – 19.00%</t>
+        </is>
+      </c>
+      <c r="H96" s="12" t="inlineStr">
+        <is>
+          <t>OPM1024_02 (18.04%), OPM1024_03 (16.55%)</t>
+        </is>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>Tangie Queen</t>
+        </is>
+      </c>
+      <c r="B97" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C97" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_TQ-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="inlineStr">
+        <is>
+          <t>10.00% ± 2.96%</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F97" s="15" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="G97" s="14" t="inlineStr">
+        <is>
+          <t>7.09% – 13.00%</t>
+        </is>
+      </c>
+      <c r="H97" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I97" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>Tropic Cake</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_TC-I_v.01</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>28.50% ± 1.50%</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F98" s="13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>27.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H98" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>Tropic Cake</t>
+        </is>
+      </c>
+      <c r="B99" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C99" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_TC-II_v.01</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="inlineStr">
+        <is>
+          <t>24.95% ± 1.95%</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F99" s="15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G99" s="14" t="inlineStr">
+        <is>
+          <t>23.00% – 26.90%</t>
+        </is>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="14" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>Tropic Cake</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_TC-III_v.01</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>19.45% ± 3.45%</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="F100" s="13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>16.00% – 22.90%</t>
+        </is>
+      </c>
+      <c r="H100" s="12" t="inlineStr">
+        <is>
+          <t>WED102501 (22.05% декл. | decl.)</t>
+        </is>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>Tropic Cake</t>
+        </is>
+      </c>
+      <c r="B101" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C101" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_TC-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="inlineStr">
+        <is>
+          <t>10.45% ± 5.45%</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="F101" s="15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="G101" s="14" t="inlineStr">
+        <is>
+          <t>5.00% – 15.90%</t>
+        </is>
+      </c>
+      <c r="H101" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I101" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="14" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_VG-I_v.01</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>28.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="n">
+        <v>28</v>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>26.00% – 30.00%</t>
+        </is>
+      </c>
+      <c r="H102" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="C103" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_VG-II_v.01</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F103" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>22.00% – 26.00%</t>
+        </is>
+      </c>
+      <c r="H103" s="14" t="inlineStr">
+        <is>
+          <t>GP062501 (24.89%)</t>
+        </is>
+      </c>
+      <c r="I103" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="14" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>QCSP 001_VG-III_v.01</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>20.00% ± 2.00%</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F104" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>18.00% – 22.00%</t>
+        </is>
+      </c>
+      <c r="H104" s="12" t="inlineStr">
+        <is>
+          <t>GP052501 (18.52%), GP072501/2 (19.81%), GP082501/1 (21.29%), GP072501/1 (21.36%)</t>
+        </is>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="B105" s="14" t="inlineStr">
+        <is>
+          <t>Grade IV</t>
+        </is>
+      </c>
+      <c r="C105" s="14" t="inlineStr">
+        <is>
+          <t>QCSP 001_VG-IV_v.01</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="inlineStr">
+        <is>
+          <t>16.00% ± 2.08%</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="F105" s="15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>13.83% – 18.00%</t>
+        </is>
+      </c>
+      <c r="H105" s="14" t="inlineStr">
+        <is>
+          <t>GP082501/2 (15.70%)</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="14" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>нема издадена спецификација | no issued specification</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="n"/>
+      <c r="F106" s="12" t="n"/>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H106" s="12" t="inlineStr">
+        <is>
+          <t>WC082501 (21.67%), WC072501 (22.11%)</t>
+        </is>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14312,7 +22384,7 @@
           <t>STEADY BG XY/1</t>
         </is>
       </c>
-      <c r="H6" s="16" t="n">
+      <c r="H6" s="17" t="n">
         <v>0.218</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
@@ -14356,7 +22428,7 @@
           <t>STEADY SUN XY/1</t>
         </is>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <v>0.21</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
@@ -14400,7 +22472,7 @@
           <t>STEADY PDY XY/1</t>
         </is>
       </c>
-      <c r="H8" s="16" t="n">
+      <c r="H8" s="17" t="n">
         <v>0.1563</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
@@ -14444,7 +22516,7 @@
           <t>CAYN CK XY/1</t>
         </is>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <v>0.2029</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -14488,7 +22560,7 @@
           <t>STEADY OGB XY/1</t>
         </is>
       </c>
-      <c r="H10" s="16" t="n">
+      <c r="H10" s="17" t="n">
         <v>0.1656</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
@@ -14532,7 +22604,7 @@
           <t>CAYN CK XY/1</t>
         </is>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <v>0.2084</v>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -14576,7 +22648,7 @@
           <t>CAYN FS XY/1</t>
         </is>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="17" t="n">
         <v>0.1977</v>
       </c>
       <c r="I12" s="12" t="inlineStr">
@@ -14620,7 +22692,7 @@
           <t>STEADY GG4 XY/1</t>
         </is>
       </c>
-      <c r="H13" s="17" t="n">
+      <c r="H13" s="18" t="n">
         <v>0.1559</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -14664,7 +22736,7 @@
           <t>STEADY GG XY/1</t>
         </is>
       </c>
-      <c r="H14" s="16" t="n">
+      <c r="H14" s="17" t="n">
         <v>0.17</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
@@ -14708,7 +22780,7 @@
           <t>CAYN VG XY/1</t>
         </is>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="18" t="n">
         <v>0.1898</v>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -14752,7 +22824,7 @@
           <t>STEADY GP XY/1</t>
         </is>
       </c>
-      <c r="H16" s="16" t="n">
+      <c r="H16" s="17" t="n">
         <v>0.2379</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
@@ -14796,7 +22868,7 @@
           <t>CAYN VG XY/1</t>
         </is>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H17" s="18" t="n">
         <v>0.1483</v>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -14840,7 +22912,7 @@
           <t>STEADY HPA XY/1</t>
         </is>
       </c>
-      <c r="H18" s="16" t="n">
+      <c r="H18" s="17" t="n">
         <v>0.1497</v>
       </c>
       <c r="I18" s="12" t="inlineStr">
@@ -14884,7 +22956,7 @@
           <t>CAYN HD XY/1</t>
         </is>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="18" t="n">
         <v>0.2243</v>
       </c>
       <c r="I19" s="14" t="inlineStr">
@@ -14928,7 +23000,7 @@
           <t>CAYN JOZ XY/1</t>
         </is>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="17" t="n">
         <v>0.1914</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -14972,7 +23044,7 @@
           <t>CAYN JD XY/1</t>
         </is>
       </c>
-      <c r="H21" s="17" t="n">
+      <c r="H21" s="18" t="n">
         <v>0.1964</v>
       </c>
       <c r="I21" s="14" t="inlineStr">
@@ -15016,7 +23088,7 @@
           <t>CAYN OD XY/1</t>
         </is>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H22" s="17" t="n">
         <v>0.1996</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
@@ -15060,7 +23132,7 @@
           <t>CAYN TQ XY/1</t>
         </is>
       </c>
-      <c r="H23" s="17" t="n">
+      <c r="H23" s="18" t="n">
         <v>0.1827</v>
       </c>
       <c r="I23" s="14" t="inlineStr">
@@ -15104,7 +23176,7 @@
           <t>STEADY CB XY/1</t>
         </is>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="17" t="n">
         <v>0.11</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
@@ -15148,7 +23220,7 @@
           <t>STEADY F1 XY/1</t>
         </is>
       </c>
-      <c r="H25" s="17" t="n">
+      <c r="H25" s="18" t="n">
         <v>0.1406</v>
       </c>
       <c r="I25" s="14" t="inlineStr">
@@ -15192,7 +23264,7 @@
           <t>CAYN SCR XY/1</t>
         </is>
       </c>
-      <c r="H26" s="16" t="n">
+      <c r="H26" s="17" t="n">
         <v>0.17</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
@@ -15236,7 +23308,7 @@
           <t>STEADY Amnesia Core XY/1</t>
         </is>
       </c>
-      <c r="H27" s="17" t="n">
+      <c r="H27" s="18" t="n">
         <v>0.1291</v>
       </c>
       <c r="I27" s="14" t="inlineStr">
@@ -15280,7 +23352,7 @@
           <t>STEADY SUN XY/1</t>
         </is>
       </c>
-      <c r="H28" s="16" t="n">
+      <c r="H28" s="17" t="n">
         <v>0.2047</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
@@ -15324,7 +23396,7 @@
           <t>STEADY PDY XY/1</t>
         </is>
       </c>
-      <c r="H29" s="17" t="n">
+      <c r="H29" s="18" t="n">
         <v>0.1232</v>
       </c>
       <c r="I29" s="14" t="inlineStr">
@@ -15368,7 +23440,7 @@
           <t>STEADY ST XY/1</t>
         </is>
       </c>
-      <c r="H30" s="16" t="n">
+      <c r="H30" s="17" t="n">
         <v>0.0983</v>
       </c>
       <c r="I30" s="12" t="inlineStr">
@@ -15412,7 +23484,7 @@
           <t>STEADY OGB XY/1</t>
         </is>
       </c>
-      <c r="H31" s="17" t="n">
+      <c r="H31" s="18" t="n">
         <v>0.2151</v>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -15456,7 +23528,7 @@
           <t>CAYN CK XY/1</t>
         </is>
       </c>
-      <c r="H32" s="16" t="n">
+      <c r="H32" s="17" t="n">
         <v>0.2496</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
@@ -15500,7 +23572,7 @@
           <t>CAYN CK XY/1</t>
         </is>
       </c>
-      <c r="H33" s="17" t="n">
+      <c r="H33" s="18" t="n">
         <v>0.223</v>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -15544,7 +23616,7 @@
           <t>STEADY CL XY/1</t>
         </is>
       </c>
-      <c r="H34" s="16" t="n">
+      <c r="H34" s="17" t="n">
         <v>0.08019999999999999</v>
       </c>
       <c r="I34" s="12" t="inlineStr">
@@ -15588,7 +23660,7 @@
           <t>CAYN DW XY/1</t>
         </is>
       </c>
-      <c r="H35" s="17" t="n">
+      <c r="H35" s="18" t="n">
         <v>0.1468</v>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -15632,7 +23704,7 @@
           <t>STEADY GG XY/1</t>
         </is>
       </c>
-      <c r="H36" s="16" t="n">
+      <c r="H36" s="17" t="n">
         <v>0.1334</v>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -15676,7 +23748,7 @@
           <t>CAYN VG XY/1</t>
         </is>
       </c>
-      <c r="H37" s="17" t="n">
+      <c r="H37" s="18" t="n">
         <v>0.1981</v>
       </c>
       <c r="I37" s="14" t="inlineStr">
@@ -15720,7 +23792,7 @@
           <t>STEADY GP XY/1</t>
         </is>
       </c>
-      <c r="H38" s="16" t="n">
+      <c r="H38" s="17" t="n">
         <v>0.2545</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
@@ -15764,7 +23836,7 @@
           <t>CAYN VG XY/1</t>
         </is>
       </c>
-      <c r="H39" s="17" t="n">
+      <c r="H39" s="18" t="n">
         <v>0.2129</v>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -15808,7 +23880,7 @@
           <t>STEADY GP XY/1</t>
         </is>
       </c>
-      <c r="H40" s="16" t="n">
+      <c r="H40" s="17" t="n">
         <v>0.2573</v>
       </c>
       <c r="I40" s="12" t="inlineStr">
@@ -15852,7 +23924,7 @@
           <t>STEADY PT XY/1</t>
         </is>
       </c>
-      <c r="H41" s="17" t="n">
+      <c r="H41" s="18" t="n">
         <v>0.1153</v>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -15896,7 +23968,7 @@
           <t>CAYN HD XY/1</t>
         </is>
       </c>
-      <c r="H42" s="16" t="n">
+      <c r="H42" s="17" t="n">
         <v>0.2039</v>
       </c>
       <c r="I42" s="12" t="inlineStr">
@@ -15940,7 +24012,7 @@
           <t>STEADY SC XY/1</t>
         </is>
       </c>
-      <c r="H43" s="17" t="n">
+      <c r="H43" s="18" t="n">
         <v>0.1671</v>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -15984,7 +24056,7 @@
           <t>CAYN JD XY/1</t>
         </is>
       </c>
-      <c r="H44" s="16" t="n">
+      <c r="H44" s="17" t="n">
         <v>0.133</v>
       </c>
       <c r="I44" s="12" t="inlineStr">
@@ -16028,7 +24100,7 @@
           <t>CAYN JD XY/1</t>
         </is>
       </c>
-      <c r="H45" s="17" t="n">
+      <c r="H45" s="18" t="n">
         <v>0.1497</v>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -16072,7 +24144,7 @@
           <t>CAYN KC XY/1</t>
         </is>
       </c>
-      <c r="H46" s="16" t="n">
+      <c r="H46" s="17" t="n">
         <v>0.174</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
@@ -16116,7 +24188,7 @@
           <t>CAYN NYD XY/1</t>
         </is>
       </c>
-      <c r="H47" s="17" t="n">
+      <c r="H47" s="18" t="n">
         <v>0.1682</v>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -16160,7 +24232,7 @@
           <t>STEADY CB XY/1</t>
         </is>
       </c>
-      <c r="H48" s="16" t="n">
+      <c r="H48" s="17" t="n">
         <v>0.1538</v>
       </c>
       <c r="I48" s="12" t="inlineStr">
@@ -16204,7 +24276,7 @@
           <t>STEADY SCB XY/1</t>
         </is>
       </c>
-      <c r="H49" s="17" t="n">
+      <c r="H49" s="18" t="n">
         <v>0.09429999999999999</v>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -16248,7 +24320,7 @@
           <t>CAYN TQ XY/1</t>
         </is>
       </c>
-      <c r="H50" s="16" t="n">
+      <c r="H50" s="17" t="n">
         <v>0.1655</v>
       </c>
       <c r="I50" s="12" t="inlineStr">
@@ -16292,7 +24364,7 @@
           <t>STEADY F1 XY/1</t>
         </is>
       </c>
-      <c r="H51" s="17" t="n">
+      <c r="H51" s="18" t="n">
         <v>0.13</v>
       </c>
       <c r="I51" s="14" t="inlineStr">
@@ -16336,7 +24408,7 @@
           <t>STEADY LG XY/1</t>
         </is>
       </c>
-      <c r="H52" s="16" t="n">
+      <c r="H52" s="17" t="n">
         <v>0.1563</v>
       </c>
       <c r="I52" s="12" t="inlineStr">
@@ -16380,7 +24452,7 @@
           <t>CAYN SCR XY/1</t>
         </is>
       </c>
-      <c r="H53" s="17" t="n">
+      <c r="H53" s="18" t="n">
         <v>0.1713</v>
       </c>
       <c r="I53" s="14" t="inlineStr">
@@ -16424,7 +24496,7 @@
           <t>STEADY SJ XY/1</t>
         </is>
       </c>
-      <c r="H54" s="16" t="n">
+      <c r="H54" s="17" t="n">
         <v>0.1096</v>
       </c>
       <c r="I54" s="12" t="inlineStr">
@@ -16468,7 +24540,7 @@
           <t>CAYN WC XY/1</t>
         </is>
       </c>
-      <c r="H55" s="17" t="n">
+      <c r="H55" s="18" t="n">
         <v>0.2167</v>
       </c>
       <c r="I55" s="14" t="inlineStr">
@@ -16512,7 +24584,7 @@
           <t>CAYN AB XY/1</t>
         </is>
       </c>
-      <c r="H56" s="16" t="n">
+      <c r="H56" s="17" t="n">
         <v>0.1693</v>
       </c>
       <c r="I56" s="12" t="inlineStr">
@@ -16556,7 +24628,7 @@
           <t>STEADY SUN XY/1</t>
         </is>
       </c>
-      <c r="H57" s="17" t="n">
+      <c r="H57" s="18" t="n">
         <v>0.2342</v>
       </c>
       <c r="I57" s="14" t="inlineStr">
@@ -16600,7 +24672,7 @@
           <t>STEADY PDY XY/1</t>
         </is>
       </c>
-      <c r="H58" s="16" t="n">
+      <c r="H58" s="17" t="n">
         <v>0.1335</v>
       </c>
       <c r="I58" s="12" t="inlineStr">
@@ -16644,7 +24716,7 @@
           <t>STEADY OGB XY/1</t>
         </is>
       </c>
-      <c r="H59" s="17" t="n">
+      <c r="H59" s="18" t="n">
         <v>0.1449</v>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -16688,7 +24760,7 @@
           <t>CAYN CK XY/1</t>
         </is>
       </c>
-      <c r="H60" s="16" t="n">
+      <c r="H60" s="17" t="n">
         <v>0.237</v>
       </c>
       <c r="I60" s="12" t="inlineStr">
@@ -16732,7 +24804,7 @@
           <t>CAYN CK XY/1</t>
         </is>
       </c>
-      <c r="H61" s="17" t="n">
+      <c r="H61" s="18" t="n">
         <v>0.23</v>
       </c>
       <c r="I61" s="14" t="inlineStr">
@@ -16776,7 +24848,7 @@
           <t>CAYN DW XY/1</t>
         </is>
       </c>
-      <c r="H62" s="16" t="n">
+      <c r="H62" s="17" t="n">
         <v>0.1465</v>
       </c>
       <c r="I62" s="12" t="inlineStr">
@@ -16820,7 +24892,7 @@
           <t>CAYN DW XY/1</t>
         </is>
       </c>
-      <c r="H63" s="17" t="n">
+      <c r="H63" s="18" t="n">
         <v>0.156</v>
       </c>
       <c r="I63" s="14" t="inlineStr">
@@ -16864,7 +24936,7 @@
           <t>CAYN FS XY/1</t>
         </is>
       </c>
-      <c r="H64" s="16" t="n">
+      <c r="H64" s="17" t="n">
         <v>0.1669</v>
       </c>
       <c r="I64" s="12" t="inlineStr">
@@ -16908,7 +24980,7 @@
           <t>STEADY GG4 XY/1</t>
         </is>
       </c>
-      <c r="H65" s="17" t="n">
+      <c r="H65" s="18" t="n">
         <v>0.1535</v>
       </c>
       <c r="I65" s="14" t="inlineStr">
@@ -16952,7 +25024,7 @@
           <t>STEADY GG XY/1</t>
         </is>
       </c>
-      <c r="H66" s="16" t="n">
+      <c r="H66" s="17" t="n">
         <v>0.1595</v>
       </c>
       <c r="I66" s="12" t="inlineStr">
@@ -16996,7 +25068,7 @@
           <t>CAYN CC XY/1</t>
         </is>
       </c>
-      <c r="H67" s="17" t="n">
+      <c r="H67" s="18" t="n">
         <v>0.1794</v>
       </c>
       <c r="I67" s="14" t="inlineStr">
@@ -17040,7 +25112,7 @@
           <t>CAYN VG XY/1</t>
         </is>
       </c>
-      <c r="H68" s="16" t="n">
+      <c r="H68" s="17" t="n">
         <v>0.2289</v>
       </c>
       <c r="I68" s="12" t="inlineStr">
@@ -17084,7 +25156,7 @@
           <t>CAYN VG XY/1</t>
         </is>
       </c>
-      <c r="H69" s="17" t="n">
+      <c r="H69" s="18" t="n">
         <v>0.2136</v>
       </c>
       <c r="I69" s="14" t="inlineStr">
@@ -17128,7 +25200,7 @@
           <t>STEADY PT XY/1</t>
         </is>
       </c>
-      <c r="H70" s="16" t="n">
+      <c r="H70" s="17" t="n">
         <v>0.07049999999999999</v>
       </c>
       <c r="I70" s="12" t="inlineStr">
@@ -17172,7 +25244,7 @@
           <t>STEADY Jokerz 31 25/1</t>
         </is>
       </c>
-      <c r="H71" s="17" t="n">
+      <c r="H71" s="18" t="n">
         <v>0.25</v>
       </c>
       <c r="I71" s="14" t="inlineStr">
@@ -17216,7 +25288,7 @@
           <t>CAYN JOZ XY/1</t>
         </is>
       </c>
-      <c r="H72" s="16" t="n">
+      <c r="H72" s="17" t="n">
         <v>0.2177</v>
       </c>
       <c r="I72" s="12" t="inlineStr">
@@ -17260,7 +25332,7 @@
           <t>CAYN JD XY/1</t>
         </is>
       </c>
-      <c r="H73" s="17" t="n">
+      <c r="H73" s="18" t="n">
         <v>0.1816</v>
       </c>
       <c r="I73" s="14" t="inlineStr">
@@ -17304,7 +25376,7 @@
           <t>CAYN NYD XY/1</t>
         </is>
       </c>
-      <c r="H74" s="16" t="n">
+      <c r="H74" s="17" t="n">
         <v>0.1867</v>
       </c>
       <c r="I74" s="12" t="inlineStr">
@@ -17348,7 +25420,7 @@
           <t>STEADY CB XY/1</t>
         </is>
       </c>
-      <c r="H75" s="17" t="n">
+      <c r="H75" s="18" t="n">
         <v>0.1416</v>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -17392,7 +25464,7 @@
           <t>STEADY SCB XY/1</t>
         </is>
       </c>
-      <c r="H76" s="16" t="n">
+      <c r="H76" s="17" t="n">
         <v>0.08</v>
       </c>
       <c r="I76" s="12" t="inlineStr">
@@ -17436,7 +25508,7 @@
           <t>STEADY F1 XY/1</t>
         </is>
       </c>
-      <c r="H77" s="17" t="n">
+      <c r="H77" s="18" t="n">
         <v>0.1001</v>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -17480,7 +25552,7 @@
           <t>CAYN SCR XY/1</t>
         </is>
       </c>
-      <c r="H78" s="16" t="n">
+      <c r="H78" s="17" t="n">
         <v>0.1807</v>
       </c>
       <c r="I78" s="12" t="inlineStr">
@@ -17524,7 +25596,7 @@
           <t>STEADY RS XY/1</t>
         </is>
       </c>
-      <c r="H79" s="17" t="n">
+      <c r="H79" s="18" t="n">
         <v>0.16</v>
       </c>
       <c r="I79" s="14" t="inlineStr">
@@ -17568,7 +25640,7 @@
           <t>STEADY SJ XY/1</t>
         </is>
       </c>
-      <c r="H80" s="16" t="n">
+      <c r="H80" s="17" t="n">
         <v>0.112</v>
       </c>
       <c r="I80" s="12" t="inlineStr">
@@ -17612,7 +25684,7 @@
           <t>CAYN CAL XY/1</t>
         </is>
       </c>
-      <c r="H81" s="17" t="n">
+      <c r="H81" s="18" t="n">
         <v>0.09</v>
       </c>
       <c r="I81" s="14" t="inlineStr">
@@ -17656,7 +25728,7 @@
           <t>CAYN Wedding Crusher 22/1</t>
         </is>
       </c>
-      <c r="H82" s="16" t="n">
+      <c r="H82" s="17" t="n">
         <v>0.2211</v>
       </c>
       <c r="I82" s="12" t="inlineStr">
@@ -17700,7 +25772,7 @@
           <t>STEADY Tropic Cake XY/1</t>
         </is>
       </c>
-      <c r="H83" s="17" t="n">
+      <c r="H83" s="18" t="n">
         <v>0.2205</v>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -17719,7 +25791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19465,7 +27537,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21819,7 +29891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -9,9 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Potency by Strain" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock without register result" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Classes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Class Totals" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Potency by Strain'!$A$5:$R$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Export Classes'!$A$5:$Q$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="25">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -164,6 +167,68 @@
       <color rgb="008A6D14"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="001B3A5C"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B3A5C"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0014532B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008A6D14"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008A6D14"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="004A5B6C"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="008A2E2E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008A2E2E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B3A5C"/>
+      <sz val="12.5"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B3A5C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001B3A5C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -239,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -369,6 +434,69 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9445,4 +9573,7673 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4.5" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Purely Plant GmbH — Распределба по извозни класи: транши и серии наспроти нашите резултати и декларирани опсези | Export-class distribution: tranches and batches against our results and declared ranges</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Извори: извозната листа „THC level,qty by batch.xlsx“ (класи, THC на листата, количини) + PP_Batch_Release_QC_Register_CORRECTED.xlsx (нашиот резултат) + Атласот на потенција (декларирана класа: номинала ± толеранција). | Sources: the export list “THC level,qty by batch.xlsx” (classes, list THC, quantities) + the corrected release register (our result) + the Potency Atlas (declared grade: nominal ± tolerance).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="74" customHeight="1">
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>ПРАВИЛО ЗА ИЗВОЗНАТА КЛАСА | THE EXPORT-CLASS RULE — Прозорците на класите се преклопуваат (18 → 16,20–19,80; 20 → 18,00–22,00; 22 → 19,80–24,20), па само границите не ја определуваат класата. Правилото е реконструирано од самите количински табели на листата: серијата оди во НАЈВИСОКАТА класа чиј прозорец ±10% ја содржи вредноста. Под тоа правило сите 33 количини по транша и класа се репродуцираат точно, со еден исклучок (P060142, 7,05% — под подот од 7,20% на класата 8, а сепак е броена таму). | The class windows overlap, so the limits alone do not fix the class. The rule was recovered from the list's own quantity tables: a batch goes to the HIGHEST class whose ±10% window contains its value. Under it all 33 per-tranche class quantities reproduce exactly, with one exception (P060142, 7.05% — below class 8's 7.20% floor, yet counted there).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Транша | Tranche</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Сорта (листа) | Strain (list)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Ново име (листа) | New name (list)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Серија на листата | List batch no.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Наша серија | Our batch</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>THC на листата | List THC</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Наш резултат | Our result</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Δ (пп | pp)</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Наша класа | Our tier</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Наш опсег | Our range</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Извозна класа | Export class</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Долна −10% | Lower</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Горна +10% | Upper</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>Класа по наш резултат | Class on our result</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>Количина (kg) | Quantity</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>Забелешка | Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>ТРАНША 1 | TRANCHE 1 — 19 серии | batches · 1496.070 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>Blue Gelato</t>
+        </is>
+      </c>
+      <c r="D7" s="46" t="inlineStr">
+        <is>
+          <t>Blue Gelato</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>BG1024</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>BG1024</t>
+        </is>
+      </c>
+      <c r="G7" s="30" t="inlineStr">
+        <is>
+          <t>26.14%</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>26.14%</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K7" s="47" t="inlineStr">
+        <is>
+          <t>26.00% ± 2.60% (23.40%–28.60%)</t>
+        </is>
+      </c>
+      <c r="L7" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="M7" s="49" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="N7" s="49" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="O7" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="P7" s="30" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="Q7" s="50" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>BSS1024</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>BSS1024</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>25.01%</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>25.01%</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K8" s="47" t="inlineStr">
+        <is>
+          <t>24.50% ± 2.45% (22.05%–26.95%)</t>
+        </is>
+      </c>
+      <c r="L8" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="M8" s="49" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="N8" s="49" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="O8" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="P8" s="28" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="Q8" s="52" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>P050162</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>CJ052501/01</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>24.05%</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>24.05%</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K9" s="47" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.30% (20.70%–25.30%)</t>
+        </is>
+      </c>
+      <c r="L9" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="M9" s="49" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="N9" s="49" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="O9" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="P9" s="30" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="Q9" s="50" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>P060032</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>CJ082501/2</t>
+        </is>
+      </c>
+      <c r="G10" s="28" t="inlineStr">
+        <is>
+          <t>18.29%</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>18.29%</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K10" s="47" t="inlineStr">
+        <is>
+          <t>19.00% ± 1.69% (17.31%–20.69%)</t>
+        </is>
+      </c>
+      <c r="L10" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N10" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O10" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" s="28" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="Q10" s="52" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>Fat Sofa</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>P060352</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>FB012602</t>
+        </is>
+      </c>
+      <c r="G11" s="30" t="inlineStr">
+        <is>
+          <t>18.86%</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>18.86%</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K11" s="47" t="inlineStr">
+        <is>
+          <t>19.50% ± 1.95% (17.55%–21.45%)</t>
+        </is>
+      </c>
+      <c r="L11" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M11" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N11" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O11" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="P11" s="30" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="Q11" s="50" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>P060402</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>GG012603</t>
+        </is>
+      </c>
+      <c r="G12" s="28" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>16.70%</t>
+        </is>
+      </c>
+      <c r="I12" s="53" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K12" s="47" t="inlineStr">
+        <is>
+          <t>17.50% ± 1.75% (15.75%–19.25%)</t>
+        </is>
+      </c>
+      <c r="L12" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M12" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N12" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O12" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="P12" s="28" t="n">
+        <v>37.67</v>
+      </c>
+      <c r="Q12" s="52" t="inlineStr">
+        <is>
+          <t>листата: 17.59% ≠ наш: 16.70% | list vs ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>Gorilla Gang</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>P050092</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>GG1024_01</t>
+        </is>
+      </c>
+      <c r="G13" s="30" t="inlineStr">
+        <is>
+          <t>18.67%</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>18.67%</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K13" s="47" t="inlineStr">
+        <is>
+          <t>17.50% ± 1.75% (15.75%–19.25%)</t>
+        </is>
+      </c>
+      <c r="L13" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N13" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O13" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="P13" s="30" t="n">
+        <v>223.73</v>
+      </c>
+      <c r="Q13" s="50" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C14" s="42" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>P050152</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>GP052501</t>
+        </is>
+      </c>
+      <c r="G14" s="28" t="inlineStr">
+        <is>
+          <t>18.52%</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>18.52%</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K14" s="47" t="inlineStr">
+        <is>
+          <t>20.00% ± 1.59% (18.41%–21.59%)</t>
+        </is>
+      </c>
+      <c r="L14" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N14" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O14" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P14" s="28" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="Q14" s="52" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C15" s="40" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D15" s="46" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>P050022</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>GP0824_02</t>
+        </is>
+      </c>
+      <c r="G15" s="30" t="inlineStr">
+        <is>
+          <t>22.61%</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>22.61%</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K15" s="47" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.40% (21.60%–26.40%)</t>
+        </is>
+      </c>
+      <c r="L15" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M15" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N15" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O15" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="P15" s="30" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q15" s="50" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C16" s="42" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>P050322</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>GP082501/2</t>
+        </is>
+      </c>
+      <c r="G16" s="28" t="inlineStr">
+        <is>
+          <t>15.70%</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>15.70%</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K16" s="47" t="inlineStr">
+        <is>
+          <t>17.00% ± 1.40% (15.60%–18.40%)</t>
+        </is>
+      </c>
+      <c r="L16" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M16" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N16" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O16" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="P16" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="52" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C17" s="40" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="D17" s="46" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>HPA1024</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>HPA1024</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>17.31%</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>17.31%</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K17" s="47" t="inlineStr">
+        <is>
+          <t>17.50% ± 1.39% (16.11%–18.89%)</t>
+        </is>
+      </c>
+      <c r="L17" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M17" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N17" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O17" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="P17" s="30" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="Q17" s="50" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>Hazy Daze</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>P050052</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>HPA1024_01</t>
+        </is>
+      </c>
+      <c r="G18" s="28" t="inlineStr">
+        <is>
+          <t>21.61%</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>21.61%</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K18" s="47" t="inlineStr">
+        <is>
+          <t>21.00% ± 2.10% (18.90%–23.10%)</t>
+        </is>
+      </c>
+      <c r="L18" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M18" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N18" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O18" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="P18" s="28" t="n">
+        <v>130.3</v>
+      </c>
+      <c r="Q18" s="52" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C19" s="40" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="D19" s="46" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>P060212</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>JD112501</t>
+        </is>
+      </c>
+      <c r="G19" s="30" t="inlineStr">
+        <is>
+          <t>20.32%</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>20.32%</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K19" s="47" t="inlineStr">
+        <is>
+          <t>20.00% ± 2.00% (18.00%–22.00%)</t>
+        </is>
+      </c>
+      <c r="L19" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M19" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N19" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O19" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="P19" s="30" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="Q19" s="50" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>P060152</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>J31102501</t>
+        </is>
+      </c>
+      <c r="G20" s="28" t="inlineStr">
+        <is>
+          <t>17.32%</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>17.32%</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K20" s="47" t="inlineStr">
+        <is>
+          <t>17.50% ± 1.39% (16.11%–18.89%)</t>
+        </is>
+      </c>
+      <c r="L20" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N20" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O20" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="P20" s="28" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="Q20" s="52" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C21" s="40" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>Orange Dream</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>OPM1024</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>OPM1024</t>
+        </is>
+      </c>
+      <c r="G21" s="30" t="inlineStr">
+        <is>
+          <t>20.03%</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>20.03%</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-5</t>
+        </is>
+      </c>
+      <c r="K21" s="47" t="inlineStr">
+        <is>
+          <t>20.50% ± 2.05% (18.45%–22.55%)</t>
+        </is>
+      </c>
+      <c r="L21" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M21" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N21" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O21" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="P21" s="30" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="Q21" s="50" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="inlineStr">
+        <is>
+          <t>Tangie Queen</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>P050062</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>OPM1024_02</t>
+        </is>
+      </c>
+      <c r="G22" s="28" t="inlineStr">
+        <is>
+          <t>18.04%</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>18.04%</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-4</t>
+        </is>
+      </c>
+      <c r="K22" s="47" t="inlineStr">
+        <is>
+          <t>17.00% ± 1.44% (15.56%–18.44%)</t>
+        </is>
+      </c>
+      <c r="L22" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M22" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N22" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O22" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P22" s="28" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="Q22" s="52" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C23" s="40" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="inlineStr">
+        <is>
+          <t>Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>P060242</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>OPM122501</t>
+        </is>
+      </c>
+      <c r="G23" s="30" t="inlineStr">
+        <is>
+          <t>7.91%</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>7.91%</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K23" s="47" t="inlineStr">
+        <is>
+          <t>8.00% ± 0.54% (7.46%–8.54%)</t>
+        </is>
+      </c>
+      <c r="L23" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" s="49" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="N23" s="49" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="O23" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P23" s="30" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q23" s="50" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>Formula 1</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>P060062</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>PM092501</t>
+        </is>
+      </c>
+      <c r="G24" s="28" t="inlineStr">
+        <is>
+          <t>12.25%</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>12.25%</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K24" s="47" t="inlineStr">
+        <is>
+          <t>12.50% ± 1.25% (11.25%–13.75%)</t>
+        </is>
+      </c>
+      <c r="L24" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="M24" s="49" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="N24" s="49" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="O24" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="P24" s="28" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="Q24" s="52" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Т1</t>
+        </is>
+      </c>
+      <c r="C25" s="40" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="D25" s="46" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>P060382</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>SCR012603</t>
+        </is>
+      </c>
+      <c r="G25" s="30" t="inlineStr">
+        <is>
+          <t>17.84%</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>17.84%</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K25" s="47" t="inlineStr">
+        <is>
+          <t>18.00% ± 1.79% (16.21%–19.79%)</t>
+        </is>
+      </c>
+      <c r="L25" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M25" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N25" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O25" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="P25" s="30" t="n">
+        <v>78.84</v>
+      </c>
+      <c r="Q25" s="50" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="45" t="inlineStr">
+        <is>
+          <t>ТРАНША 2 | TRANCHE 2 — 29 серии | batches · 2668.440 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C27" s="42" t="inlineStr">
+        <is>
+          <t>Amnesia Core Cut</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="inlineStr">
+        <is>
+          <t>Amnesia Core</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>P060122</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>ACC102501</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="inlineStr">
+        <is>
+          <t>12.91%</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>12.91%</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K27" s="47" t="inlineStr">
+        <is>
+          <t>13.00% ± 1.30% (11.70%–14.30%)</t>
+        </is>
+      </c>
+      <c r="L27" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="M27" s="49" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="N27" s="49" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="O27" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="P27" s="28" t="n">
+        <v>37.85</v>
+      </c>
+      <c r="Q27" s="52" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C28" s="40" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="inlineStr">
+        <is>
+          <t>Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>P050192</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>BSS052501</t>
+        </is>
+      </c>
+      <c r="G28" s="30" t="inlineStr">
+        <is>
+          <t>20.47%</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>20.39%</t>
+        </is>
+      </c>
+      <c r="I28" s="55" t="inlineStr">
+        <is>
+          <t>-0.08</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K28" s="47" t="inlineStr">
+        <is>
+          <t>20.50% ± 1.54% (18.96%–22.04%)</t>
+        </is>
+      </c>
+      <c r="L28" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M28" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N28" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O28" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="P28" s="30" t="n">
+        <v>342.54</v>
+      </c>
+      <c r="Q28" s="50" t="inlineStr">
+        <is>
+          <t>листата: 20.47% ≠ наш: 20.39% | list vs ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C29" s="42" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="inlineStr">
+        <is>
+          <t>OG Banana's</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>P050222</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="inlineStr">
+        <is>
+          <t>CJ062501/1</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="inlineStr">
+        <is>
+          <t>21.51%</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>21.51%</t>
+        </is>
+      </c>
+      <c r="I29" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K29" s="47" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.30% (20.70%–25.30%)</t>
+        </is>
+      </c>
+      <c r="L29" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M29" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N29" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O29" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P29" s="28" t="n">
+        <v>76.56999999999999</v>
+      </c>
+      <c r="Q29" s="52" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C30" s="40" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>P060022</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>CJ082501/1</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>24.96%</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>24.96%</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K30" s="47" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.30% (20.70%–25.30%)</t>
+        </is>
+      </c>
+      <c r="L30" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="M30" s="49" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="N30" s="49" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="O30" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="P30" s="30" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="Q30" s="50" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="20" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>P060072</t>
+        </is>
+      </c>
+      <c r="F31" s="20" t="inlineStr">
+        <is>
+          <t>CJ092501</t>
+        </is>
+      </c>
+      <c r="G31" s="28" t="inlineStr">
+        <is>
+          <t>22.30%</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>22.30%</t>
+        </is>
+      </c>
+      <c r="I31" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K31" s="47" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.30% (20.70%–25.30%)</t>
+        </is>
+      </c>
+      <c r="L31" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M31" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N31" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O31" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="P31" s="28" t="n">
+        <v>27.13</v>
+      </c>
+      <c r="Q31" s="52" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C32" s="40" t="inlineStr">
+        <is>
+          <t>CashCow</t>
+        </is>
+      </c>
+      <c r="D32" s="51" t="inlineStr">
+        <is>
+          <t>Payday</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>P060372</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>CC012603</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>12.32%</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>12.32%</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K32" s="47" t="inlineStr">
+        <is>
+          <t>13.50% ± 1.34% (12.16%–14.84%)</t>
+        </is>
+      </c>
+      <c r="L32" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" s="49" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="N32" s="49" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="O32" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="P32" s="30" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="Q32" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>Chem Flyer</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="inlineStr">
+        <is>
+          <t>Shark Tank</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>P060132</t>
+        </is>
+      </c>
+      <c r="F33" s="20" t="inlineStr">
+        <is>
+          <t>CF102501</t>
+        </is>
+      </c>
+      <c r="G33" s="28" t="inlineStr">
+        <is>
+          <t>9.83%</t>
+        </is>
+      </c>
+      <c r="H33" s="22" t="inlineStr">
+        <is>
+          <t>9.83%</t>
+        </is>
+      </c>
+      <c r="I33" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K33" s="47" t="inlineStr">
+        <is>
+          <t>10.00% ± 1.00% (9.00%–11.00%)</t>
+        </is>
+      </c>
+      <c r="L33" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" s="49" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="N33" s="49" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="O33" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P33" s="28" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="Q33" s="52" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C34" s="40" t="inlineStr">
+        <is>
+          <t>Clemosa A Bud</t>
+        </is>
+      </c>
+      <c r="D34" s="51" t="inlineStr">
+        <is>
+          <t>Clemosa</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>P050282</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>CLE072501</t>
+        </is>
+      </c>
+      <c r="G34" s="30" t="inlineStr">
+        <is>
+          <t>8.02%</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>8.02%</t>
+        </is>
+      </c>
+      <c r="I34" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K34" s="47" t="inlineStr">
+        <is>
+          <t>8.00% ± 0.80% (7.20%–8.80%)</t>
+        </is>
+      </c>
+      <c r="L34" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" s="49" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="N34" s="49" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="O34" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P34" s="30" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="Q34" s="50" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="D35" s="51" t="inlineStr">
+        <is>
+          <t>Daywalker</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>P060322</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>FB012601/1</t>
+        </is>
+      </c>
+      <c r="G35" s="28" t="inlineStr">
+        <is>
+          <t>14.68%</t>
+        </is>
+      </c>
+      <c r="H35" s="22" t="inlineStr">
+        <is>
+          <t>14.68%</t>
+        </is>
+      </c>
+      <c r="I35" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K35" s="47" t="inlineStr">
+        <is>
+          <t>16.00% ± 1.54% (14.46%–17.54%)</t>
+        </is>
+      </c>
+      <c r="L35" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M35" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N35" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O35" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="P35" s="28" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="Q35" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C36" s="40" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="D36" s="51" t="inlineStr">
+        <is>
+          <t>Gorilla Gang</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>GG1024</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>GG1024</t>
+        </is>
+      </c>
+      <c r="G36" s="30" t="inlineStr">
+        <is>
+          <t>13.34%</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>13.34%</t>
+        </is>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K36" s="47" t="inlineStr">
+        <is>
+          <t>14.50% ± 1.24% (13.26%–15.74%)</t>
+        </is>
+      </c>
+      <c r="L36" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="M36" s="49" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="N36" s="49" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="O36" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="P36" s="30" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="Q36" s="50" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C37" s="42" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>P050302</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>GP072501/2</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="inlineStr">
+        <is>
+          <t>19.81%</t>
+        </is>
+      </c>
+      <c r="H37" s="22" t="inlineStr">
+        <is>
+          <t>19.81%</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K37" s="47" t="inlineStr">
+        <is>
+          <t>20.00% ± 1.59% (18.41%–21.59%)</t>
+        </is>
+      </c>
+      <c r="L37" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M37" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N37" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O37" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P37" s="28" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="Q37" s="52" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C38" s="40" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D38" s="46" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>P050072</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>GP0824_03</t>
+        </is>
+      </c>
+      <c r="G38" s="30" t="inlineStr">
+        <is>
+          <t>25.45%</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>25.45%</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K38" s="47" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.40% (21.60%–26.40%)</t>
+        </is>
+      </c>
+      <c r="L38" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="M38" s="49" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="N38" s="49" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="O38" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="P38" s="30" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="Q38" s="50" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D39" s="51" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>P050312</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>GP082501/1</t>
+        </is>
+      </c>
+      <c r="G39" s="28" t="inlineStr">
+        <is>
+          <t>21.29%</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>21.29%</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K39" s="47" t="inlineStr">
+        <is>
+          <t>20.00% ± 1.59% (18.41%–21.59%)</t>
+        </is>
+      </c>
+      <c r="L39" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M39" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N39" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O39" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P39" s="28" t="n">
+        <v>197.03</v>
+      </c>
+      <c r="Q39" s="52" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C40" s="40" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D40" s="46" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>P060092</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>GP092501</t>
+        </is>
+      </c>
+      <c r="G40" s="30" t="inlineStr">
+        <is>
+          <t>25.73%</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>25.73%</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K40" s="47" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.40% (21.60%–26.40%)</t>
+        </is>
+      </c>
+      <c r="L40" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="M40" s="49" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="N40" s="49" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="O40" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="P40" s="30" t="n">
+        <v>167.72</v>
+      </c>
+      <c r="Q40" s="50" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+      <c r="D41" s="51" t="inlineStr">
+        <is>
+          <t>Plum Tarte</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>P060182</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>GRC102501/2</t>
+        </is>
+      </c>
+      <c r="G41" s="28" t="inlineStr">
+        <is>
+          <t>11.53%</t>
+        </is>
+      </c>
+      <c r="H41" s="22" t="inlineStr">
+        <is>
+          <t>11.53%</t>
+        </is>
+      </c>
+      <c r="I41" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K41" s="47" t="inlineStr">
+        <is>
+          <t>11.50% ± 1.15% (10.35%–12.65%)</t>
+        </is>
+      </c>
+      <c r="L41" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="M41" s="49" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="N41" s="49" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="O41" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="P41" s="28" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="Q41" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C42" s="40" t="inlineStr">
+        <is>
+          <t>High Pro Amnesia</t>
+        </is>
+      </c>
+      <c r="D42" s="51" t="inlineStr">
+        <is>
+          <t>Hazy Daze</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>P050182</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>HPA052501</t>
+        </is>
+      </c>
+      <c r="G42" s="30" t="inlineStr">
+        <is>
+          <t>20.39%</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>20.39%</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K42" s="47" t="inlineStr">
+        <is>
+          <t>21.00% ± 2.10% (18.90%–23.10%)</t>
+        </is>
+      </c>
+      <c r="L42" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M42" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N42" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O42" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="P42" s="30" t="n">
+        <v>247.2</v>
+      </c>
+      <c r="Q42" s="50" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="D43" s="51" t="inlineStr">
+        <is>
+          <t>Strawberry Cupcakes</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>P060362</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>JD012603/01</t>
+        </is>
+      </c>
+      <c r="G43" s="28" t="inlineStr">
+        <is>
+          <t>16.71%</t>
+        </is>
+      </c>
+      <c r="H43" s="22" t="inlineStr">
+        <is>
+          <t>16.71%</t>
+        </is>
+      </c>
+      <c r="I43" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K43" s="47" t="inlineStr">
+        <is>
+          <t>16.50% ± 1.49% (15.01%–17.99%)</t>
+        </is>
+      </c>
+      <c r="L43" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M43" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N43" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O43" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="P43" s="28" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="Q43" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C44" s="40" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>P060412</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>JD012603/02</t>
+        </is>
+      </c>
+      <c r="G44" s="30" t="inlineStr">
+        <is>
+          <t>20.54%</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>20.54%</t>
+        </is>
+      </c>
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K44" s="47" t="inlineStr">
+        <is>
+          <t>20.00% ± 2.00% (18.00%–22.00%)</t>
+        </is>
+      </c>
+      <c r="L44" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M44" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N44" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O44" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="P44" s="30" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="Q44" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="D45" s="54" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="inlineStr">
+        <is>
+          <t>P060422</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>JD012603/02V</t>
+        </is>
+      </c>
+      <c r="G45" s="28" t="inlineStr">
+        <is>
+          <t>15.16%</t>
+        </is>
+      </c>
+      <c r="H45" s="22" t="inlineStr">
+        <is>
+          <t>15.16%</t>
+        </is>
+      </c>
+      <c r="I45" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K45" s="47" t="inlineStr">
+        <is>
+          <t>16.50% ± 1.49% (15.01%–17.99%)</t>
+        </is>
+      </c>
+      <c r="L45" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M45" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N45" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O45" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="P45" s="28" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="Q45" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C46" s="40" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="D46" s="46" t="inlineStr">
+        <is>
+          <t>Kush Crasher</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>P060172</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="30" t="inlineStr">
+        <is>
+          <t>17.40%</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="32" t="inlineStr">
+        <is>
+          <t>нема декларирана класа | no declared grade</t>
+        </is>
+      </c>
+      <c r="L46" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M46" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N46" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O46" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P46" s="30" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q46" s="50" t="inlineStr">
+        <is>
+          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C47" s="42" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="D47" s="51" t="inlineStr">
+        <is>
+          <t>NY Diesel</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="inlineStr">
+        <is>
+          <t>P050112</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>MB0824_05</t>
+        </is>
+      </c>
+      <c r="G47" s="28" t="inlineStr">
+        <is>
+          <t>16.82%</t>
+        </is>
+      </c>
+      <c r="H47" s="22" t="inlineStr">
+        <is>
+          <t>16.82%</t>
+        </is>
+      </c>
+      <c r="I47" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K47" s="47" t="inlineStr">
+        <is>
+          <t>18.00% ± 1.80% (16.20%–19.80%)</t>
+        </is>
+      </c>
+      <c r="L47" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M47" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N47" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O47" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="P47" s="28" t="n">
+        <v>239.68</v>
+      </c>
+      <c r="Q47" s="52" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C48" s="40" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D48" s="51" t="inlineStr">
+        <is>
+          <t>Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>P050042</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>OMP1024_01</t>
+        </is>
+      </c>
+      <c r="G48" s="30" t="inlineStr">
+        <is>
+          <t>15.38%</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>15.38%</t>
+        </is>
+      </c>
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K48" s="47" t="inlineStr">
+        <is>
+          <t>14.50% ± 1.05% (13.45%–15.55%)</t>
+        </is>
+      </c>
+      <c r="L48" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M48" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N48" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O48" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="P48" s="30" t="n">
+        <v>209.95</v>
+      </c>
+      <c r="Q48" s="50" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C49" s="42" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D49" s="51" t="inlineStr">
+        <is>
+          <t>Soft Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>P060042</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>OPM092501</t>
+        </is>
+      </c>
+      <c r="G49" s="28" t="inlineStr">
+        <is>
+          <t>9.43%</t>
+        </is>
+      </c>
+      <c r="H49" s="22" t="inlineStr">
+        <is>
+          <t>9.43%</t>
+        </is>
+      </c>
+      <c r="I49" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K49" s="47" t="inlineStr">
+        <is>
+          <t>9.50% ± 0.95% (8.55%–10.45%)</t>
+        </is>
+      </c>
+      <c r="L49" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="M49" s="49" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="N49" s="49" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="O49" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P49" s="28" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="Q49" s="52" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C50" s="40" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D50" s="51" t="inlineStr">
+        <is>
+          <t>Tangie Queen</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>P050082</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>OPM1024_03</t>
+        </is>
+      </c>
+      <c r="G50" s="30" t="inlineStr">
+        <is>
+          <t>16.55%</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>16.55%</t>
+        </is>
+      </c>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-4</t>
+        </is>
+      </c>
+      <c r="K50" s="47" t="inlineStr">
+        <is>
+          <t>17.00% ± 1.44% (15.56%–18.44%)</t>
+        </is>
+      </c>
+      <c r="L50" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M50" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N50" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O50" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="P50" s="30" t="n">
+        <v>254.54</v>
+      </c>
+      <c r="Q50" s="50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="D51" s="51" t="inlineStr">
+        <is>
+          <t>Formula 1</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>P060232</t>
+        </is>
+      </c>
+      <c r="F51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="28" t="inlineStr">
+        <is>
+          <t>13.00%</t>
+        </is>
+      </c>
+      <c r="H51" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I51" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K51" s="32" t="inlineStr">
+        <is>
+          <t>нема декларирана класа | no declared grade</t>
+        </is>
+      </c>
+      <c r="L51" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="M51" s="49" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="N51" s="49" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="O51" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P51" s="28" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q51" s="52" t="inlineStr">
+        <is>
+          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C52" s="40" t="inlineStr">
+        <is>
+          <t>Pure Michigen</t>
+        </is>
+      </c>
+      <c r="D52" s="51" t="inlineStr">
+        <is>
+          <t>Lifeguard</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>P060112</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>PUM102501</t>
+        </is>
+      </c>
+      <c r="G52" s="30" t="inlineStr">
+        <is>
+          <t>15.63%</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>15.63%</t>
+        </is>
+      </c>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J52" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K52" s="47" t="inlineStr">
+        <is>
+          <t>15.50% ± 1.55% (13.95%–17.05%)</t>
+        </is>
+      </c>
+      <c r="L52" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M52" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N52" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O52" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="P52" s="30" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="Q52" s="50" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C53" s="42" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="D53" s="54" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>P060282</t>
+        </is>
+      </c>
+      <c r="F53" s="20" t="inlineStr">
+        <is>
+          <t>SCR112501</t>
+        </is>
+      </c>
+      <c r="G53" s="28" t="inlineStr">
+        <is>
+          <t>17.13%</t>
+        </is>
+      </c>
+      <c r="H53" s="22" t="inlineStr">
+        <is>
+          <t>17.13%</t>
+        </is>
+      </c>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K53" s="47" t="inlineStr">
+        <is>
+          <t>18.00% ± 1.79% (16.21%–19.79%)</t>
+        </is>
+      </c>
+      <c r="L53" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M53" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N53" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O53" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="P53" s="28" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Q53" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C54" s="40" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>P060082</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
+        <is>
+          <t>SJ092501</t>
+        </is>
+      </c>
+      <c r="G54" s="30" t="inlineStr">
+        <is>
+          <t>10.96%</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>10.96%</t>
+        </is>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K54" s="47" t="inlineStr">
+        <is>
+          <t>11.00% ± 1.10% (9.90%–12.10%)</t>
+        </is>
+      </c>
+      <c r="L54" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="M54" s="49" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="N54" s="49" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="O54" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="P54" s="30" t="n">
+        <v>26.93</v>
+      </c>
+      <c r="Q54" s="50" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
+        <is>
+          <t>Т2</t>
+        </is>
+      </c>
+      <c r="C55" s="42" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
+        </is>
+      </c>
+      <c r="D55" s="54" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>P060012</t>
+        </is>
+      </c>
+      <c r="F55" s="20" t="inlineStr">
+        <is>
+          <t>WC082501</t>
+        </is>
+      </c>
+      <c r="G55" s="28" t="inlineStr">
+        <is>
+          <t>21.67%</t>
+        </is>
+      </c>
+      <c r="H55" s="22" t="inlineStr">
+        <is>
+          <t>21.67%</t>
+        </is>
+      </c>
+      <c r="I55" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J55" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K55" s="47" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.20% (19.80%–24.20%)</t>
+        </is>
+      </c>
+      <c r="L55" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M55" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N55" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O55" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="P55" s="28" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="Q55" s="52" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="45" t="inlineStr">
+        <is>
+          <t>ТРАНША 3 | TRANCHE 3 — 29 серии | batches · 2814.430 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C57" s="40" t="inlineStr">
+        <is>
+          <t>Appels &amp; Bananas</t>
+        </is>
+      </c>
+      <c r="D57" s="46" t="inlineStr">
+        <is>
+          <t>Appels &amp; Bananas</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>P060052</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>AB092501</t>
+        </is>
+      </c>
+      <c r="G57" s="30" t="inlineStr">
+        <is>
+          <t>16.93%</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>16.93%</t>
+        </is>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K57" s="47" t="inlineStr">
+        <is>
+          <t>17.00% ± 1.70% (15.30%–18.70%)</t>
+        </is>
+      </c>
+      <c r="L57" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M57" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N57" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O57" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="P57" s="30" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="Q57" s="50" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C58" s="42" t="inlineStr">
+        <is>
+          <t>Blue Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="D58" s="51" t="inlineStr">
+        <is>
+          <t>Sunset Sherbet</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="inlineStr">
+        <is>
+          <t>P050122</t>
+        </is>
+      </c>
+      <c r="F58" s="20" t="inlineStr">
+        <is>
+          <t>BSS1024_01/1</t>
+        </is>
+      </c>
+      <c r="G58" s="28" t="inlineStr">
+        <is>
+          <t>23.42%</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="inlineStr">
+        <is>
+          <t>23.42%</t>
+        </is>
+      </c>
+      <c r="I58" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K58" s="47" t="inlineStr">
+        <is>
+          <t>24.50% ± 2.45% (22.05%–26.95%)</t>
+        </is>
+      </c>
+      <c r="L58" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="M58" s="49" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="N58" s="49" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="O58" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="P58" s="28" t="n">
+        <v>213.77</v>
+      </c>
+      <c r="Q58" s="52" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C59" s="40" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D59" s="51" t="inlineStr">
+        <is>
+          <t>OG Banana's</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>P050172</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>CJ052501/02</t>
+        </is>
+      </c>
+      <c r="G59" s="30" t="inlineStr">
+        <is>
+          <t>14.49%</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>14.93%</t>
+        </is>
+      </c>
+      <c r="I59" s="55" t="inlineStr">
+        <is>
+          <t>+0.44</t>
+        </is>
+      </c>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K59" s="47" t="inlineStr">
+        <is>
+          <t>16.00% ± 1.30% (14.70%–17.30%)</t>
+        </is>
+      </c>
+      <c r="L59" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M59" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N59" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O59" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="P59" s="30" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="Q59" s="50" t="inlineStr">
+        <is>
+          <t>листата: 14.49% ≠ наш: 14.93% | list vs ours</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C60" s="42" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D60" s="51" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="inlineStr">
+        <is>
+          <t>P050252</t>
+        </is>
+      </c>
+      <c r="F60" s="20" t="inlineStr">
+        <is>
+          <t>CJ072501</t>
+        </is>
+      </c>
+      <c r="G60" s="28" t="inlineStr">
+        <is>
+          <t>23.70%</t>
+        </is>
+      </c>
+      <c r="H60" s="22" t="inlineStr">
+        <is>
+          <t>23.70%</t>
+        </is>
+      </c>
+      <c r="I60" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K60" s="47" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.30% (20.70%–25.30%)</t>
+        </is>
+      </c>
+      <c r="L60" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="M60" s="49" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="N60" s="49" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="O60" s="25" t="n">
+        <v>26</v>
+      </c>
+      <c r="P60" s="28" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="Q60" s="52" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C61" s="40" t="inlineStr">
+        <is>
+          <t>Cap Junky</t>
+        </is>
+      </c>
+      <c r="D61" s="51" t="inlineStr">
+        <is>
+          <t>Cookie Kush</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>CJ1024</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>CJ1024</t>
+        </is>
+      </c>
+      <c r="G61" s="30" t="inlineStr">
+        <is>
+          <t>23.00%</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>23.00%</t>
+        </is>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K61" s="47" t="inlineStr">
+        <is>
+          <t>23.00% ± 2.30% (20.70%–25.30%)</t>
+        </is>
+      </c>
+      <c r="L61" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M61" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N61" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O61" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="P61" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="50" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="20" t="n">
+        <v>54</v>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C62" s="42" t="inlineStr">
+        <is>
+          <t>CashCow</t>
+        </is>
+      </c>
+      <c r="D62" s="51" t="inlineStr">
+        <is>
+          <t>Payday</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="inlineStr">
+        <is>
+          <t>P060272</t>
+        </is>
+      </c>
+      <c r="F62" s="20" t="inlineStr">
+        <is>
+          <t>CC112501</t>
+        </is>
+      </c>
+      <c r="G62" s="28" t="inlineStr">
+        <is>
+          <t>13.35%</t>
+        </is>
+      </c>
+      <c r="H62" s="22" t="inlineStr">
+        <is>
+          <t>13.35%</t>
+        </is>
+      </c>
+      <c r="I62" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K62" s="47" t="inlineStr">
+        <is>
+          <t>13.50% ± 1.34% (12.16%–14.84%)</t>
+        </is>
+      </c>
+      <c r="L62" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="M62" s="49" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="N62" s="49" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="O62" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="P62" s="28" t="n">
+        <v>13.12</v>
+      </c>
+      <c r="Q62" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C63" s="40" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="D63" s="51" t="inlineStr">
+        <is>
+          <t>Daywalker</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>P060432</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>FB012603</t>
+        </is>
+      </c>
+      <c r="G63" s="30" t="inlineStr">
+        <is>
+          <t>20.83%</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>20.83%</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K63" s="47" t="inlineStr">
+        <is>
+          <t>19.50% ± 1.95% (17.55%–21.45%)</t>
+        </is>
+      </c>
+      <c r="L63" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M63" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N63" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O63" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="P63" s="30" t="n">
+        <v>68.01000000000001</v>
+      </c>
+      <c r="Q63" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C64" s="42" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="D64" s="51" t="inlineStr">
+        <is>
+          <t>Daywalker</t>
+        </is>
+      </c>
+      <c r="E64" s="21" t="inlineStr">
+        <is>
+          <t>P060392</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="inlineStr">
+        <is>
+          <t>FB012603V</t>
+        </is>
+      </c>
+      <c r="G64" s="28" t="inlineStr">
+        <is>
+          <t>18.29%</t>
+        </is>
+      </c>
+      <c r="H64" s="22" t="inlineStr">
+        <is>
+          <t>18.29%</t>
+        </is>
+      </c>
+      <c r="I64" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J64" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K64" s="47" t="inlineStr">
+        <is>
+          <t>19.50% ± 1.95% (17.55%–21.45%)</t>
+        </is>
+      </c>
+      <c r="L64" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M64" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N64" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O64" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P64" s="28" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="Q64" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C65" s="40" t="inlineStr">
+        <is>
+          <t>Fat Bastard</t>
+        </is>
+      </c>
+      <c r="D65" s="51" t="inlineStr">
+        <is>
+          <t>Fat Sofa</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>P060292</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>FB112501</t>
+        </is>
+      </c>
+      <c r="G65" s="30" t="inlineStr">
+        <is>
+          <t>16.69%</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>16.69%</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K65" s="47" t="inlineStr">
+        <is>
+          <t>16.00% ± 1.54% (14.46%–17.54%)</t>
+        </is>
+      </c>
+      <c r="L65" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M65" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N65" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O65" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="P65" s="30" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="Q65" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="B66" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C66" s="42" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="D66" s="51" t="inlineStr">
+        <is>
+          <t>GG4</t>
+        </is>
+      </c>
+      <c r="E66" s="21" t="inlineStr">
+        <is>
+          <t>P060302</t>
+        </is>
+      </c>
+      <c r="F66" s="20" t="inlineStr">
+        <is>
+          <t>GG012601</t>
+        </is>
+      </c>
+      <c r="G66" s="28" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+      <c r="H66" s="22" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+      <c r="I66" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J66" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K66" s="47" t="inlineStr">
+        <is>
+          <t>14.50% ± 1.24% (13.26%–15.74%)</t>
+        </is>
+      </c>
+      <c r="L66" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M66" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N66" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O66" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="P66" s="28" t="n">
+        <v>76.18000000000001</v>
+      </c>
+      <c r="Q66" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C67" s="40" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="D67" s="51" t="inlineStr">
+        <is>
+          <t>Cherry Chocolate</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>P060252</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>GG112501</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>17.94%</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>17.94%</t>
+        </is>
+      </c>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K67" s="47" t="inlineStr">
+        <is>
+          <t>17.50% ± 1.75% (15.75%–19.25%)</t>
+        </is>
+      </c>
+      <c r="L67" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="M67" s="49" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="N67" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="O67" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="P67" s="30" t="n">
+        <v>55.26</v>
+      </c>
+      <c r="Q67" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="20" t="n">
+        <v>60</v>
+      </c>
+      <c r="B68" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C68" s="42" t="inlineStr">
+        <is>
+          <t>Gorilla Glue</t>
+        </is>
+      </c>
+      <c r="D68" s="51" t="inlineStr">
+        <is>
+          <t>Gorilla Gang</t>
+        </is>
+      </c>
+      <c r="E68" s="21" t="inlineStr">
+        <is>
+          <t>P050012</t>
+        </is>
+      </c>
+      <c r="F68" s="20" t="inlineStr">
+        <is>
+          <t>GG1024_02</t>
+        </is>
+      </c>
+      <c r="G68" s="28" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="H68" s="22" t="inlineStr">
+        <is>
+          <t>15.95%</t>
+        </is>
+      </c>
+      <c r="I68" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K68" s="47" t="inlineStr">
+        <is>
+          <t>17.50% ± 1.75% (15.75%–19.25%)</t>
+        </is>
+      </c>
+      <c r="L68" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M68" s="49" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="N68" s="49" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="O68" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="P68" s="28" t="n">
+        <v>182.14</v>
+      </c>
+      <c r="Q68" s="52" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C69" s="40" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D69" s="51" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>P050202</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>GP062501</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>22.89%</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>24.89%</t>
+        </is>
+      </c>
+      <c r="I69" s="55" t="inlineStr">
+        <is>
+          <t>+2.00</t>
+        </is>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K69" s="47" t="inlineStr">
+        <is>
+          <t>24.00% ± 2.40% (21.60%–26.40%)</t>
+        </is>
+      </c>
+      <c r="L69" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M69" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N69" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O69" s="57" t="n">
+        <v>26</v>
+      </c>
+      <c r="P69" s="30" t="n">
+        <v>292.96</v>
+      </c>
+      <c r="Q69" s="50" t="inlineStr">
+        <is>
+          <t>листата: 22.89% ≠ наш: 24.89% | list vs ours; по наш резултат: класа 26 | on our result: class 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="20" t="n">
+        <v>62</v>
+      </c>
+      <c r="B70" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C70" s="42" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D70" s="51" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="E70" s="21" t="inlineStr">
+        <is>
+          <t>P050292</t>
+        </is>
+      </c>
+      <c r="F70" s="20" t="inlineStr">
+        <is>
+          <t>GP072501/1</t>
+        </is>
+      </c>
+      <c r="G70" s="28" t="inlineStr">
+        <is>
+          <t>21.36%</t>
+        </is>
+      </c>
+      <c r="H70" s="22" t="inlineStr">
+        <is>
+          <t>21.36%</t>
+        </is>
+      </c>
+      <c r="I70" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K70" s="47" t="inlineStr">
+        <is>
+          <t>20.00% ± 1.59% (18.41%–21.59%)</t>
+        </is>
+      </c>
+      <c r="L70" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M70" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N70" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O70" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="P70" s="28" t="n">
+        <v>226.07</v>
+      </c>
+      <c r="Q70" s="52" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C71" s="40" t="inlineStr">
+        <is>
+          <t>Grapes and Cream</t>
+        </is>
+      </c>
+      <c r="D71" s="51" t="inlineStr">
+        <is>
+          <t>Plum Tarte</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>P060142</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>GRC102501/1</t>
+        </is>
+      </c>
+      <c r="G71" s="30" t="inlineStr">
+        <is>
+          <t>7.05%</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>7.05%</t>
+        </is>
+      </c>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K71" s="47" t="inlineStr">
+        <is>
+          <t>7.00% ± 0.70% (6.30%–7.70%)</t>
+        </is>
+      </c>
+      <c r="L71" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="M71" s="49" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="N71" s="49" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="O71" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="30" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="Q71" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence; под подот на класата 8 (7,20%) | below class 8's floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="n">
+        <v>64</v>
+      </c>
+      <c r="B72" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C72" s="42" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="D72" s="54" t="inlineStr">
+        <is>
+          <t>Jelly Donuts</t>
+        </is>
+      </c>
+      <c r="E72" s="21" t="inlineStr">
+        <is>
+          <t>P060312</t>
+        </is>
+      </c>
+      <c r="F72" s="20" t="inlineStr">
+        <is>
+          <t>JD012601</t>
+        </is>
+      </c>
+      <c r="G72" s="28" t="inlineStr">
+        <is>
+          <t>18.16%</t>
+        </is>
+      </c>
+      <c r="H72" s="22" t="inlineStr">
+        <is>
+          <t>18.16%</t>
+        </is>
+      </c>
+      <c r="I72" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J72" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K72" s="47" t="inlineStr">
+        <is>
+          <t>20.00% ± 2.00% (18.00%–22.00%)</t>
+        </is>
+      </c>
+      <c r="L72" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M72" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N72" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O72" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="P72" s="28" t="n">
+        <v>76.38</v>
+      </c>
+      <c r="Q72" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="D73" s="46" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>P060202</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="30" t="inlineStr">
+        <is>
+          <t>25.00%</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>нема декларирана класа | no declared grade</t>
+        </is>
+      </c>
+      <c r="L73" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="M73" s="49" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="N73" s="49" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="O73" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="30" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="Q73" s="50" t="inlineStr">
+        <is>
+          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="B74" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C74" s="42" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="D74" s="54" t="inlineStr">
+        <is>
+          <t>Jokerz 31</t>
+        </is>
+      </c>
+      <c r="E74" s="21" t="inlineStr">
+        <is>
+          <t>P060262</t>
+        </is>
+      </c>
+      <c r="F74" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="28" t="inlineStr">
+        <is>
+          <t>21.77%</t>
+        </is>
+      </c>
+      <c r="H74" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I74" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J74" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="inlineStr">
+        <is>
+          <t>нема декларирана класа | no declared grade</t>
+        </is>
+      </c>
+      <c r="L74" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M74" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N74" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O74" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="28" t="n">
+        <v>135.49</v>
+      </c>
+      <c r="Q74" s="52" t="inlineStr">
+        <is>
+          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C75" s="40" t="inlineStr">
+        <is>
+          <t>Motor Breath</t>
+        </is>
+      </c>
+      <c r="D75" s="51" t="inlineStr">
+        <is>
+          <t>NY Diesel</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>P050032</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>MB0824_04</t>
+        </is>
+      </c>
+      <c r="G75" s="30" t="inlineStr">
+        <is>
+          <t>18.67%</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>18.67%</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K75" s="47" t="inlineStr">
+        <is>
+          <t>18.00% ± 1.80% (16.20%–19.80%)</t>
+        </is>
+      </c>
+      <c r="L75" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M75" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N75" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O75" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="P75" s="30" t="n">
+        <v>169.29</v>
+      </c>
+      <c r="Q75" s="50" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="20" t="n">
+        <v>68</v>
+      </c>
+      <c r="B76" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C76" s="42" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D76" s="51" t="inlineStr">
+        <is>
+          <t>Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="E76" s="21" t="inlineStr">
+        <is>
+          <t>P050132</t>
+        </is>
+      </c>
+      <c r="F76" s="20" t="inlineStr">
+        <is>
+          <t>OPM052501</t>
+        </is>
+      </c>
+      <c r="G76" s="28" t="inlineStr">
+        <is>
+          <t>14.16%</t>
+        </is>
+      </c>
+      <c r="H76" s="22" t="inlineStr">
+        <is>
+          <t>14.16%</t>
+        </is>
+      </c>
+      <c r="I76" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J76" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-3</t>
+        </is>
+      </c>
+      <c r="K76" s="47" t="inlineStr">
+        <is>
+          <t>14.50% ± 1.05% (13.45%–15.55%)</t>
+        </is>
+      </c>
+      <c r="L76" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="M76" s="49" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="N76" s="49" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="O76" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="P76" s="28" t="n">
+        <v>289.08</v>
+      </c>
+      <c r="Q76" s="52" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C77" s="40" t="inlineStr">
+        <is>
+          <t>Orange Punch Mimosa</t>
+        </is>
+      </c>
+      <c r="D77" s="51" t="inlineStr">
+        <is>
+          <t>Soft Citrus Bloom</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>P060222</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>OPM112501</t>
+        </is>
+      </c>
+      <c r="G77" s="30" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>8.00%</t>
+        </is>
+      </c>
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J77" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K77" s="47" t="inlineStr">
+        <is>
+          <t>8.00% ± 0.54% (7.46%–8.54%)</t>
+        </is>
+      </c>
+      <c r="L77" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="M77" s="49" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="N77" s="49" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="O77" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P77" s="30" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="Q77" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="B78" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C78" s="42" t="inlineStr">
+        <is>
+          <t>Permanent Marker</t>
+        </is>
+      </c>
+      <c r="D78" s="51" t="inlineStr">
+        <is>
+          <t>Formula 1</t>
+        </is>
+      </c>
+      <c r="E78" s="21" t="inlineStr">
+        <is>
+          <t>P050272</t>
+        </is>
+      </c>
+      <c r="F78" s="20" t="inlineStr">
+        <is>
+          <t>PM072501</t>
+        </is>
+      </c>
+      <c r="G78" s="28" t="inlineStr">
+        <is>
+          <t>10.01%</t>
+        </is>
+      </c>
+      <c r="H78" s="22" t="inlineStr">
+        <is>
+          <t>10.01%</t>
+        </is>
+      </c>
+      <c r="I78" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J78" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K78" s="47" t="inlineStr">
+        <is>
+          <t>10.50% ± 0.74% (9.76%–11.24%)</t>
+        </is>
+      </c>
+      <c r="L78" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="M78" s="49" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="N78" s="49" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="O78" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P78" s="28" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="Q78" s="52" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C79" s="40" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="D79" s="46" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>P060342</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>SCR012601</t>
+        </is>
+      </c>
+      <c r="G79" s="30" t="inlineStr">
+        <is>
+          <t>18.07%</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>18.07%</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K79" s="47" t="inlineStr">
+        <is>
+          <t>18.00% ± 1.79% (16.21%–19.79%)</t>
+        </is>
+      </c>
+      <c r="L79" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="M79" s="49" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="N79" s="49" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="O79" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="P79" s="30" t="n">
+        <v>78.86</v>
+      </c>
+      <c r="Q79" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="B80" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C80" s="42" t="inlineStr">
+        <is>
+          <t>Scrambler</t>
+        </is>
+      </c>
+      <c r="D80" s="51" t="inlineStr">
+        <is>
+          <t>Rainbow Sherbet</t>
+        </is>
+      </c>
+      <c r="E80" s="21" t="inlineStr">
+        <is>
+          <t>P060442</t>
+        </is>
+      </c>
+      <c r="F80" s="20" t="inlineStr">
+        <is>
+          <t>SCR022601</t>
+        </is>
+      </c>
+      <c r="G80" s="28" t="inlineStr">
+        <is>
+          <t>21.92%</t>
+        </is>
+      </c>
+      <c r="H80" s="22" t="inlineStr">
+        <is>
+          <t>21.92%</t>
+        </is>
+      </c>
+      <c r="I80" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J80" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K80" s="47" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.20% (19.80%–24.20%)</t>
+        </is>
+      </c>
+      <c r="L80" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M80" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N80" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O80" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="P80" s="28" t="n">
+        <v>194.25</v>
+      </c>
+      <c r="Q80" s="52" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C81" s="40" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+      <c r="D81" s="46" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>P060162</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>SJ102501</t>
+        </is>
+      </c>
+      <c r="G81" s="30" t="inlineStr">
+        <is>
+          <t>11.20%</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>11.20%</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J81" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K81" s="47" t="inlineStr">
+        <is>
+          <t>11.00% ± 1.10% (9.90%–12.10%)</t>
+        </is>
+      </c>
+      <c r="L81" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="M81" s="49" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="N81" s="49" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="O81" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="P81" s="30" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="Q81" s="50" t="inlineStr">
+        <is>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="n">
+        <v>74</v>
+      </c>
+      <c r="B82" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C82" s="42" t="inlineStr">
+        <is>
+          <t>Sleepy Joe</t>
+        </is>
+      </c>
+      <c r="D82" s="51" t="inlineStr">
+        <is>
+          <t>Calmino</t>
+        </is>
+      </c>
+      <c r="E82" s="21" t="inlineStr">
+        <is>
+          <t>P060192</t>
+        </is>
+      </c>
+      <c r="F82" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="28" t="inlineStr">
+        <is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="H82" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="32" t="inlineStr">
+        <is>
+          <t>нема декларирана класа | no declared grade</t>
+        </is>
+      </c>
+      <c r="L82" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="M82" s="49" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="N82" s="49" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="O82" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="28" t="n">
+        <v>50.62</v>
+      </c>
+      <c r="Q82" s="52" t="inlineStr">
+        <is>
+          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="inlineStr">
+        <is>
+          <t>Wedding Cake</t>
+        </is>
+      </c>
+      <c r="D83" s="51" t="inlineStr">
+        <is>
+          <t>Tropic Cake</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>P060102</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>WED102501</t>
+        </is>
+      </c>
+      <c r="G83" s="30" t="inlineStr">
+        <is>
+          <t>22.05%</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>22.05%</t>
+        </is>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J83" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K83" s="47" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.20% (19.80%–24.20%)</t>
+        </is>
+      </c>
+      <c r="L83" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M83" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N83" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O83" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="P83" s="30" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="Q83" s="50" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="B84" s="20" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C84" s="42" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
+        </is>
+      </c>
+      <c r="D84" s="54" t="inlineStr">
+        <is>
+          <t>Wedding Crusher</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>P050262</t>
+        </is>
+      </c>
+      <c r="F84" s="20" t="inlineStr">
+        <is>
+          <t>WC072501</t>
+        </is>
+      </c>
+      <c r="G84" s="28" t="inlineStr">
+        <is>
+          <t>22.11%</t>
+        </is>
+      </c>
+      <c r="H84" s="22" t="inlineStr">
+        <is>
+          <t>22.11%</t>
+        </is>
+      </c>
+      <c r="I84" s="20" t="inlineStr">
+        <is>
+          <t>+0.00</t>
+        </is>
+      </c>
+      <c r="J84" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K84" s="47" t="inlineStr">
+        <is>
+          <t>22.00% ± 2.20% (19.80%–24.20%)</t>
+        </is>
+      </c>
+      <c r="L84" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="M84" s="49" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="N84" s="49" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="O84" s="25" t="n">
+        <v>24</v>
+      </c>
+      <c r="P84" s="28" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="Q84" s="52" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Т3</t>
+        </is>
+      </c>
+      <c r="C85" s="40" t="inlineStr">
+        <is>
+          <t>Grape Pie</t>
+        </is>
+      </c>
+      <c r="D85" s="51" t="inlineStr">
+        <is>
+          <t>Vanilla Grapes</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>P050102</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>GP0824_01</t>
+        </is>
+      </c>
+      <c r="G85" s="30" t="inlineStr">
+        <is>
+          <t>20.79%</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K85" s="32" t="inlineStr">
+        <is>
+          <t>нема декларирана класа | no declared grade</t>
+        </is>
+      </c>
+      <c r="L85" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="M85" s="49" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="N85" s="49" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="O85" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P85" s="30" t="n">
+        <v>223.31</v>
+      </c>
+      <c r="Q85" s="50" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A5:Q5"/>
+  <mergeCells count="6">
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A56:Q56"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A26:Q26"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="58" t="inlineStr">
+        <is>
+          <t>Количини по извозна класа: наша пресметка наспроти извозната листа | Quantity per export class: our recomputation vs the export list</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Секоја количина е збир на сериите распоредени по правилото погоре. Разликите не се израмнуваат — се прикажуваат. | Every quantity is the sum of the batches assigned by the rule above. Differences are shown, never silently reconciled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>ТРАНША 1 | TRANCHE 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>THC (%)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Долна −10% | Lower</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Горна +10% | Upper</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Количина (наша) | Quantity (ours)</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Количина (листа) | Quantity (list)</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Разлика | Difference</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Серии | Batches</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B6" s="59" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="C6" s="59" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>103</v>
+      </c>
+      <c r="E6" s="60" t="n">
+        <v>103</v>
+      </c>
+      <c r="F6" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" s="59" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C7" s="59" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" s="59" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="C8" s="59" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="E8" s="60" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="F8" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B9" s="59" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="C9" s="59" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B10" s="59" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="C10" s="59" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="60" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="B11" s="59" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="C11" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>179.07</v>
+      </c>
+      <c r="E11" s="60" t="n">
+        <v>179.07</v>
+      </c>
+      <c r="F11" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B12" s="59" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="C12" s="59" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>610.65</v>
+      </c>
+      <c r="E12" s="60" t="n">
+        <v>610.66</v>
+      </c>
+      <c r="F12" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="B13" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="C13" s="59" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>84.47</v>
+      </c>
+      <c r="E13" s="60" t="n">
+        <v>84.47</v>
+      </c>
+      <c r="F13" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="B14" s="59" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="C14" s="59" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="E14" s="60" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="F14" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="B15" s="59" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="C15" s="59" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E15" s="60" t="n">
+        <v>110</v>
+      </c>
+      <c r="F15" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="B16" s="59" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="C16" s="59" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="E16" s="60" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="F16" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="61" t="inlineStr">
+        <is>
+          <t>Вкупно | Total</t>
+        </is>
+      </c>
+      <c r="B17" s="62" t="n"/>
+      <c r="C17" s="62" t="n"/>
+      <c r="D17" s="61" t="n">
+        <v>1496.07</v>
+      </c>
+      <c r="E17" s="61" t="n">
+        <v>1496.079</v>
+      </c>
+      <c r="F17" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="64" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="45" t="inlineStr">
+        <is>
+          <t>ТРАНША 2 | TRANCHE 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>THC (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Долна −10% | Lower</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Горна +10% | Upper</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Количина (наша) | Quantity (ours)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Количина (листа) | Quantity (list)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Разлика | Difference</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Серии | Batches</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="59" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="C21" s="59" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="E21" s="60" t="n">
+        <v>27.05</v>
+      </c>
+      <c r="F21" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" s="59" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C22" s="59" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="E22" s="60" t="n">
+        <v>61.37</v>
+      </c>
+      <c r="F22" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" s="59" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="C23" s="59" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="E23" s="60" t="n">
+        <v>101.48</v>
+      </c>
+      <c r="F23" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B24" s="59" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="C24" s="59" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="E24" s="60" t="n">
+        <v>124.95</v>
+      </c>
+      <c r="F24" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="59" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="C25" s="59" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>277.78</v>
+      </c>
+      <c r="E25" s="60" t="n">
+        <v>277.78</v>
+      </c>
+      <c r="F25" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="B26" s="59" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="C26" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="E26" s="60" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="F26" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="59" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="C27" s="59" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="C28" s="59" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>923.13</v>
+      </c>
+      <c r="E28" s="60" t="n">
+        <v>923.12</v>
+      </c>
+      <c r="F28" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="59" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="59" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="C29" s="59" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>108.71</v>
+      </c>
+      <c r="E29" s="60" t="n">
+        <v>108.71</v>
+      </c>
+      <c r="F29" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="59" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="C30" s="59" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="E30" s="60" t="n">
+        <v>113.39</v>
+      </c>
+      <c r="F30" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="59" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="C31" s="59" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="E31" s="60" t="n">
+        <v>386.47</v>
+      </c>
+      <c r="F31" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="61" t="inlineStr">
+        <is>
+          <t>Вкупно | Total</t>
+        </is>
+      </c>
+      <c r="B32" s="62" t="n"/>
+      <c r="C32" s="62" t="n"/>
+      <c r="D32" s="61" t="n">
+        <v>2668.44</v>
+      </c>
+      <c r="E32" s="61" t="n">
+        <v>2668.417</v>
+      </c>
+      <c r="F32" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="64" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
+        <is>
+          <t>ТРАНША 3 | TRANCHE 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>THC (%)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Долна −10% | Lower</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Горна +10% | Upper</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Количина (наша) | Quantity (ours)</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Количина (листа) | Quantity (list)</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Разлика | Difference</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Серии | Batches</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="59" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="C36" s="59" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="E36" s="60" t="n">
+        <v>48.42</v>
+      </c>
+      <c r="F36" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="59" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C37" s="59" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>76.61</v>
+      </c>
+      <c r="E37" s="60" t="n">
+        <v>76.61</v>
+      </c>
+      <c r="F37" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" s="59" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="C38" s="59" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="E38" s="60" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="F38" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B39" s="59" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="C39" s="59" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="E39" s="60" t="n">
+        <v>302.19</v>
+      </c>
+      <c r="F39" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="59" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B40" s="59" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="C40" s="59" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>301.52</v>
+      </c>
+      <c r="E40" s="60" t="n">
+        <v>301.52</v>
+      </c>
+      <c r="F40" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="B41" s="59" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="C41" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>119.28</v>
+      </c>
+      <c r="E41" s="60" t="n">
+        <v>119.28</v>
+      </c>
+      <c r="F41" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B42" s="59" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="C42" s="59" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="E42" s="60" t="n">
+        <v>340.12</v>
+      </c>
+      <c r="F42" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="B43" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="C43" s="59" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n">
+        <v>517.39</v>
+      </c>
+      <c r="E43" s="60" t="n">
+        <v>517.39</v>
+      </c>
+      <c r="F43" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="B44" s="59" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="C44" s="59" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>706</v>
+      </c>
+      <c r="E44" s="60" t="n">
+        <v>706</v>
+      </c>
+      <c r="F44" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="59" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="B45" s="59" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="C45" s="59" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>337.55</v>
+      </c>
+      <c r="E45" s="60" t="n">
+        <v>337.55</v>
+      </c>
+      <c r="F45" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="B46" s="59" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="C46" s="59" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>Вкупно | Total</t>
+        </is>
+      </c>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="61" t="n">
+        <v>2814.43</v>
+      </c>
+      <c r="E47" s="61" t="n">
+        <v>2814.407</v>
+      </c>
+      <c r="F47" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G47" s="64" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>СИТЕ ТРАНШИ | ALL TRANCHES</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>THC (%)</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Долна −10% | Lower</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Горна +10% | Upper</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Количина (наша) | Quantity (ours)</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Количина (листа) | Quantity (list)</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>Разлика | Difference</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>Серии | Batches</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="59" t="inlineStr">
+        <is>
+          <t>7.20</t>
+        </is>
+      </c>
+      <c r="C51" s="59" t="inlineStr">
+        <is>
+          <t>8.80</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>178.47</v>
+      </c>
+      <c r="E51" s="60" t="n">
+        <v>178.46</v>
+      </c>
+      <c r="F51" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G51" s="59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" s="59" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C52" s="59" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="n">
+        <v>137.98</v>
+      </c>
+      <c r="E52" s="60" t="n">
+        <v>137.98</v>
+      </c>
+      <c r="F52" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G52" s="59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B53" s="59" t="inlineStr">
+        <is>
+          <t>10.80</t>
+        </is>
+      </c>
+      <c r="C53" s="59" t="inlineStr">
+        <is>
+          <t>13.20</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="n">
+        <v>186.2</v>
+      </c>
+      <c r="E53" s="60" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="F53" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G53" s="59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B54" s="59" t="inlineStr">
+        <is>
+          <t>12.60</t>
+        </is>
+      </c>
+      <c r="C54" s="59" t="inlineStr">
+        <is>
+          <t>15.40</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n">
+        <v>427.15</v>
+      </c>
+      <c r="E54" s="60" t="n">
+        <v>427.14</v>
+      </c>
+      <c r="F54" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G54" s="59" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="n">
+        <v>16</v>
+      </c>
+      <c r="B55" s="59" t="inlineStr">
+        <is>
+          <t>14.40</t>
+        </is>
+      </c>
+      <c r="C55" s="59" t="inlineStr">
+        <is>
+          <t>17.60</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="n">
+        <v>601.3</v>
+      </c>
+      <c r="E55" s="60" t="n">
+        <v>601.29</v>
+      </c>
+      <c r="F55" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G55" s="59" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48" t="n">
+        <v>18</v>
+      </c>
+      <c r="B56" s="59" t="inlineStr">
+        <is>
+          <t>16.20</t>
+        </is>
+      </c>
+      <c r="C56" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="n">
+        <v>842.46</v>
+      </c>
+      <c r="E56" s="60" t="n">
+        <v>842.46</v>
+      </c>
+      <c r="F56" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G56" s="59" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="48" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" s="59" t="inlineStr">
+        <is>
+          <t>18.00</t>
+        </is>
+      </c>
+      <c r="C57" s="59" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="n">
+        <v>950.77</v>
+      </c>
+      <c r="E57" s="60" t="n">
+        <v>950.778</v>
+      </c>
+      <c r="F57" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="59" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="n">
+        <v>22</v>
+      </c>
+      <c r="B58" s="59" t="inlineStr">
+        <is>
+          <t>19.80</t>
+        </is>
+      </c>
+      <c r="C58" s="59" t="inlineStr">
+        <is>
+          <t>24.20</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="n">
+        <v>1524.99</v>
+      </c>
+      <c r="E58" s="60" t="n">
+        <v>1524.98</v>
+      </c>
+      <c r="F58" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="59" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="48" t="n">
+        <v>24</v>
+      </c>
+      <c r="B59" s="59" t="inlineStr">
+        <is>
+          <t>21.60</t>
+        </is>
+      </c>
+      <c r="C59" s="59" t="inlineStr">
+        <is>
+          <t>26.40</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="n">
+        <v>1145.01</v>
+      </c>
+      <c r="E59" s="60" t="n">
+        <v>1145.009</v>
+      </c>
+      <c r="F59" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="59" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="48" t="n">
+        <v>26</v>
+      </c>
+      <c r="B60" s="59" t="inlineStr">
+        <is>
+          <t>23.40</t>
+        </is>
+      </c>
+      <c r="C60" s="59" t="inlineStr">
+        <is>
+          <t>28.60</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>560.9400000000001</v>
+      </c>
+      <c r="E60" s="60" t="n">
+        <v>560.9400000000001</v>
+      </c>
+      <c r="F60" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="59" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="48" t="n">
+        <v>28</v>
+      </c>
+      <c r="B61" s="59" t="inlineStr">
+        <is>
+          <t>25.20</t>
+        </is>
+      </c>
+      <c r="C61" s="59" t="inlineStr">
+        <is>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="n">
+        <v>423.67</v>
+      </c>
+      <c r="E61" s="60" t="n">
+        <v>423.673</v>
+      </c>
+      <c r="F61" s="59" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="61" t="inlineStr">
+        <is>
+          <t>Вкупно | Total</t>
+        </is>
+      </c>
+      <c r="B62" s="62" t="n"/>
+      <c r="C62" s="62" t="n"/>
+      <c r="D62" s="61" t="n">
+        <v>6978.94</v>
+      </c>
+      <c r="E62" s="61" t="n">
+        <v>6978.9</v>
+      </c>
+      <c r="F62" s="63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="64" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="38" t="inlineStr">
+        <is>
+          <t>* These are the initial THC levels, the THC levels for tranche one are those in the table, while for tranches 2 and 3 they will be confirmed/updated once we receive the reanalysis results, as well as the exact quantities from all tranches.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A49:G49"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/deliverables/potency_study/Potency_Specs_and_Results.xlsx
+++ b/deliverables/potency_study/Potency_Specs_and_Results.xlsx
@@ -440,10 +440,10 @@
     <xf numFmtId="0" fontId="28" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KC102501</t>
         </is>
       </c>
       <c r="G46" s="26" t="inlineStr">
@@ -10667,22 +10667,22 @@
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K46" s="28" t="inlineStr">
-        <is>
-          <t>нема декларирана класа | no declared grade</t>
+          <t>17.04%</t>
+        </is>
+      </c>
+      <c r="I46" s="48" t="inlineStr">
+        <is>
+          <t>-0.36</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K46" s="40" t="inlineStr">
+        <is>
+          <t>17.00% ± 1.70% (15.30%–18.70%)</t>
         </is>
       </c>
       <c r="L46" s="41" t="n">
@@ -10698,17 +10698,15 @@
           <t>19.80</t>
         </is>
       </c>
-      <c r="O46" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O46" s="29" t="n">
+        <v>18</v>
       </c>
       <c r="P46" s="26" t="n">
         <v>16</v>
       </c>
       <c r="Q46" s="43" t="inlineStr">
         <is>
-          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence; листата: 17.40% ≠ наш: 17.04% | list vs ours</t>
         </is>
       </c>
     </row>
@@ -11038,7 +11036,7 @@
       </c>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PM112501</t>
         </is>
       </c>
       <c r="G51" s="24" t="inlineStr">
@@ -11048,22 +11046,22 @@
       </c>
       <c r="H51" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K51" s="28" t="inlineStr">
-        <is>
-          <t>нема декларирана класа | no declared grade</t>
+          <t>13.33%</t>
+        </is>
+      </c>
+      <c r="I51" s="46" t="inlineStr">
+        <is>
+          <t>+0.33</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K51" s="40" t="inlineStr">
+        <is>
+          <t>12.50% ± 1.25% (11.25%–13.75%)</t>
         </is>
       </c>
       <c r="L51" s="41" t="n">
@@ -11079,17 +11077,15 @@
           <t>15.40</t>
         </is>
       </c>
-      <c r="O51" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O51" s="22" t="n">
+        <v>14</v>
       </c>
       <c r="P51" s="24" t="n">
         <v>48</v>
       </c>
       <c r="Q51" s="45" t="inlineStr">
         <is>
-          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence; листата: 13.00% ≠ наш: 13.33% | list vs ours</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12395,7 @@
           <t>26.40</t>
         </is>
       </c>
-      <c r="O69" s="50" t="n">
+      <c r="O69" s="49" t="n">
         <v>26</v>
       </c>
       <c r="P69" s="26" t="n">
@@ -12553,7 +12549,7 @@
           <t>8.80</t>
         </is>
       </c>
-      <c r="O71" s="50" t="inlineStr">
+      <c r="O71" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -12672,7 +12668,7 @@
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>J31112501</t>
         </is>
       </c>
       <c r="G73" s="26" t="inlineStr">
@@ -12682,22 +12678,22 @@
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J73" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="28" t="inlineStr">
-        <is>
-          <t>нема декларирана класа | no declared grade</t>
+          <t>20.21%</t>
+        </is>
+      </c>
+      <c r="I73" s="48" t="inlineStr">
+        <is>
+          <t>-4.79</t>
+        </is>
+      </c>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K73" s="40" t="inlineStr">
+        <is>
+          <t>21.00% ± 2.10% (18.90%–23.10%)</t>
         </is>
       </c>
       <c r="L73" s="41" t="n">
@@ -12713,17 +12709,15 @@
           <t>28.60</t>
         </is>
       </c>
-      <c r="O73" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O73" s="49" t="n">
+        <v>22</v>
       </c>
       <c r="P73" s="26" t="n">
         <v>85.09999999999999</v>
       </c>
       <c r="Q73" s="43" t="inlineStr">
         <is>
-          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence; листата: 25.00% ≠ наш: 20.21% | list vs ours; по наш резултат: класа 22 | on our result: class 22</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12747,7 @@
       </c>
       <c r="F74" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>J31122501</t>
         </is>
       </c>
       <c r="G74" s="24" t="inlineStr">
@@ -12763,22 +12757,22 @@
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J74" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="28" t="inlineStr">
-        <is>
-          <t>нема декларирана класа | no declared grade</t>
+          <t>21.84%</t>
+        </is>
+      </c>
+      <c r="I74" s="46" t="inlineStr">
+        <is>
+          <t>+0.07</t>
+        </is>
+      </c>
+      <c r="J74" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-2</t>
+        </is>
+      </c>
+      <c r="K74" s="40" t="inlineStr">
+        <is>
+          <t>21.00% ± 2.10% (18.90%–23.10%)</t>
         </is>
       </c>
       <c r="L74" s="41" t="n">
@@ -12794,17 +12788,15 @@
           <t>26.40</t>
         </is>
       </c>
-      <c r="O74" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O74" s="22" t="n">
+        <v>24</v>
       </c>
       <c r="P74" s="24" t="n">
         <v>135.49</v>
       </c>
       <c r="Q74" s="45" t="inlineStr">
         <is>
-          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence; листата: 21.77% ≠ наш: 21.84% | list vs ours</t>
         </is>
       </c>
     </row>
@@ -13375,7 +13367,7 @@
       </c>
       <c r="F82" s="17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SJ112501</t>
         </is>
       </c>
       <c r="G82" s="24" t="inlineStr">
@@ -13385,22 +13377,22 @@
       </c>
       <c r="H82" s="19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I82" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J82" s="49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K82" s="28" t="inlineStr">
-        <is>
-          <t>нема декларирана класа | no declared grade</t>
+          <t>9.20%</t>
+        </is>
+      </c>
+      <c r="I82" s="46" t="inlineStr">
+        <is>
+          <t>+0.20</t>
+        </is>
+      </c>
+      <c r="J82" s="13" t="inlineStr">
+        <is>
+          <t>Pot.-1</t>
+        </is>
+      </c>
+      <c r="K82" s="40" t="inlineStr">
+        <is>
+          <t>9.00% ± 0.89% (8.11%–9.89%)</t>
         </is>
       </c>
       <c r="L82" s="41" t="n">
@@ -13416,17 +13408,15 @@
           <t>11.00</t>
         </is>
       </c>
-      <c r="O82" s="50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="O82" s="22" t="n">
+        <v>10</v>
       </c>
       <c r="P82" s="24" t="n">
         <v>50.62</v>
       </c>
       <c r="Q82" s="45" t="inlineStr">
         <is>
-          <t>нема во регистарот/Атласот | not in register/Atlas</t>
+          <t>серијата е спарена по доказ (сорта + вредност) | batch paired by evidence; листата: 9.00% ≠ наш: 9.20% | list vs ours</t>
         </is>
       </c>
     </row>
@@ -13624,7 +13614,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="J85" s="49" t="inlineStr">
+      <c r="J85" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -13647,7 +13637,7 @@
           <t>24.20</t>
         </is>
       </c>
-      <c r="O85" s="50" t="inlineStr">
+      <c r="O85" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
